--- a/ABT.xlsx
+++ b/ABT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D79E949F-9639-4520-8D35-3EE4261740D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{115521DB-81AE-43D2-87A9-FDEFBAA21501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40830" yWindow="2720" windowWidth="28980" windowHeight="14360" xr2:uid="{1DFF4005-BD0C-4C09-A1C4-CA5C3CA974D5}"/>
+    <workbookView xWindow="13260" yWindow="3250" windowWidth="22360" windowHeight="16580" xr2:uid="{1DFF4005-BD0C-4C09-A1C4-CA5C3CA974D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
     <author>tc={DEC28CAE-3B18-448E-9B03-42CBC7D02E25}</author>
   </authors>
   <commentList>
-    <comment ref="AN19" authorId="0" shapeId="0" xr:uid="{DEC28CAE-3B18-448E-9B03-42CBC7D02E25}">
+    <comment ref="AR19" authorId="0" shapeId="0" xr:uid="{DEC28CAE-3B18-448E-9B03-42CBC7D02E25}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="149">
   <si>
     <t>Price</t>
   </si>
@@ -486,6 +486,21 @@
   </si>
   <si>
     <t>Share</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Cancer Diagnostics</t>
   </si>
 </sst>
 </file>
@@ -587,14 +602,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>63927</xdr:colOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>44388</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>63927</xdr:colOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>44388</xdr:colOff>
       <xdr:row>81</xdr:row>
       <xdr:rowOff>102821</xdr:rowOff>
     </xdr:to>
@@ -611,8 +626,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14414927" y="0"/>
-          <a:ext cx="0" cy="12890744"/>
+          <a:off x="17257773" y="0"/>
+          <a:ext cx="0" cy="13169167"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -637,13 +652,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>47</xdr:col>
+      <xdr:col>51</xdr:col>
       <xdr:colOff>33307</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>47</xdr:col>
+      <xdr:col>51</xdr:col>
       <xdr:colOff>33307</xdr:colOff>
       <xdr:row>75</xdr:row>
       <xdr:rowOff>151424</xdr:rowOff>
@@ -991,7 +1006,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="AN19" dT="2023-01-07T00:44:46.14" personId="{2F949183-79EC-44FB-BA6D-BE13BEB03E9C}" id="{DEC28CAE-3B18-448E-9B03-42CBC7D02E25}">
+  <threadedComment ref="AR19" dT="2023-01-07T00:44:46.14" personId="{2F949183-79EC-44FB-BA6D-BE13BEB03E9C}" id="{DEC28CAE-3B18-448E-9B03-42CBC7D02E25}">
     <text>STJ acquisition</text>
   </threadedComment>
 </ThreadedComments>
@@ -1000,13 +1015,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B945650F-BB24-4124-8C12-116214A91726}">
   <dimension ref="B2:M55"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>20</v>
       </c>
@@ -1014,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>72</v>
       </c>
@@ -1025,13 +1040,13 @@
         <v>1</v>
       </c>
       <c r="L3" s="2">
-        <v>1747</v>
+        <v>1741.8124290000001</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
         <v>73</v>
       </c>
@@ -1040,10 +1055,10 @@
       </c>
       <c r="L4" s="2">
         <f>+L2*L3</f>
-        <v>230604</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+        <v>175923.055329</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>27</v>
       </c>
@@ -1051,13 +1066,14 @@
         <v>3</v>
       </c>
       <c r="L5" s="2">
-        <v>7751</v>
+        <f>6803+492+1090</f>
+        <v>8385</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>74</v>
       </c>
@@ -1065,13 +1081,14 @@
         <v>4</v>
       </c>
       <c r="L6" s="2">
-        <v>13242</v>
+        <f>4409+29638</f>
+        <v>34047</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>75</v>
       </c>
@@ -1080,20 +1097,20 @@
       </c>
       <c r="L7" s="2">
         <f>+L4-L5+L6</f>
-        <v>236095</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
+        <v>201585.055329</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
         <v>77</v>
       </c>
@@ -1104,27 +1121,27 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>81</v>
       </c>
@@ -1132,142 +1149,142 @@
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C38" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C46" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C49" t="s">
         <v>107</v>
       </c>
@@ -1275,7 +1292,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C50" t="s">
         <v>109</v>
       </c>
@@ -1283,7 +1300,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C51" t="s">
         <v>111</v>
       </c>
@@ -1291,7 +1308,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C52" t="s">
         <v>113</v>
       </c>
@@ -1299,12 +1316,12 @@
         <v>114</v>
       </c>
     </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C55" t="s">
         <v>116</v>
       </c>
@@ -1317,1061 +1334,1167 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85BD345-0DC4-47FD-B223-F1519D82AF4D}">
-  <dimension ref="A1:DU81"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:DY81"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" customWidth="1"/>
-    <col min="3" max="14" width="9.140625" style="3"/>
-    <col min="54" max="58" width="8.85546875" customWidth="1"/>
-    <col min="61" max="61" width="9" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" customWidth="1"/>
+    <col min="3" max="14" width="9.1796875" style="3"/>
+    <col min="58" max="62" width="8.81640625" customWidth="1"/>
+    <col min="65" max="65" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:58" x14ac:dyDescent="0.2">
-      <c r="C3" s="3" t="s">
+    <row r="2" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="R2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="T2" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="U3" s="3" t="s">
+      <c r="U2" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="V3" s="3" t="s">
+      <c r="V2" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="W3" s="3" t="s">
+      <c r="W2" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="X3" s="3" t="s">
+      <c r="X2" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="Y3" s="3" t="s">
+      <c r="Y2" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="Z3" s="3" t="s">
+      <c r="Z2" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="AA3" s="3"/>
-      <c r="AB3">
+      <c r="AA2" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="AE2" s="3"/>
+      <c r="AF2">
         <v>2005</v>
       </c>
-      <c r="AC3">
-        <f>+AB3+1</f>
+      <c r="AG2">
+        <f>+AF2+1</f>
         <v>2006</v>
       </c>
-      <c r="AD3">
-        <f t="shared" ref="AD3:AT3" si="0">+AC3+1</f>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AX2" si="0">+AG2+1</f>
         <v>2007</v>
       </c>
-      <c r="AE3">
+      <c r="AI2">
         <f t="shared" si="0"/>
         <v>2008</v>
       </c>
-      <c r="AF3">
+      <c r="AJ2">
         <f t="shared" si="0"/>
         <v>2009</v>
       </c>
-      <c r="AG3">
+      <c r="AK2">
         <f t="shared" si="0"/>
         <v>2010</v>
       </c>
-      <c r="AH3">
+      <c r="AL2">
         <f t="shared" si="0"/>
         <v>2011</v>
       </c>
-      <c r="AI3">
+      <c r="AM2">
         <f t="shared" si="0"/>
         <v>2012</v>
       </c>
-      <c r="AJ3">
+      <c r="AN2">
         <f t="shared" si="0"/>
         <v>2013</v>
       </c>
-      <c r="AK3">
+      <c r="AO2">
         <f t="shared" si="0"/>
         <v>2014</v>
       </c>
-      <c r="AL3">
+      <c r="AP2">
         <f t="shared" si="0"/>
         <v>2015</v>
       </c>
-      <c r="AM3">
+      <c r="AQ2">
         <f t="shared" si="0"/>
         <v>2016</v>
       </c>
-      <c r="AN3">
+      <c r="AR2">
         <f t="shared" si="0"/>
         <v>2017</v>
       </c>
-      <c r="AO3">
+      <c r="AS2">
         <f t="shared" si="0"/>
         <v>2018</v>
       </c>
-      <c r="AP3">
+      <c r="AT2">
         <f t="shared" si="0"/>
         <v>2019</v>
       </c>
-      <c r="AQ3">
+      <c r="AU2">
         <f t="shared" si="0"/>
         <v>2020</v>
       </c>
-      <c r="AR3">
+      <c r="AV2">
         <f t="shared" si="0"/>
         <v>2021</v>
       </c>
-      <c r="AS3">
+      <c r="AW2">
         <f t="shared" si="0"/>
         <v>2022</v>
       </c>
-      <c r="AT3">
+      <c r="AX2">
         <f t="shared" si="0"/>
         <v>2023</v>
       </c>
-      <c r="AU3">
-        <f t="shared" ref="AU3:BA3" si="1">+AT3+1</f>
+      <c r="AY2">
+        <f t="shared" ref="AY2:BE2" si="1">+AX2+1</f>
         <v>2024</v>
       </c>
-      <c r="AV3">
+      <c r="AZ2">
         <f t="shared" si="1"/>
         <v>2025</v>
       </c>
-      <c r="AW3">
+      <c r="BA2">
         <f t="shared" si="1"/>
         <v>2026</v>
       </c>
-      <c r="AX3">
+      <c r="BB2">
         <f t="shared" si="1"/>
         <v>2027</v>
       </c>
-      <c r="AY3">
+      <c r="BC2">
         <f t="shared" si="1"/>
         <v>2028</v>
       </c>
-      <c r="AZ3">
+      <c r="BD2">
         <f t="shared" si="1"/>
         <v>2029</v>
       </c>
-      <c r="BA3">
+      <c r="BE2">
         <f t="shared" si="1"/>
         <v>2030</v>
       </c>
-      <c r="BB3">
-        <f t="shared" ref="BB3:BF3" si="2">+BA3+1</f>
+      <c r="BF2">
+        <f t="shared" ref="BF2:BJ2" si="2">+BE2+1</f>
         <v>2031</v>
       </c>
-      <c r="BC3">
+      <c r="BG2">
         <f t="shared" si="2"/>
         <v>2032</v>
       </c>
-      <c r="BD3">
+      <c r="BH2">
         <f t="shared" si="2"/>
         <v>2033</v>
       </c>
-      <c r="BE3">
+      <c r="BI2">
         <f t="shared" si="2"/>
         <v>2034</v>
       </c>
-      <c r="BF3">
+      <c r="BJ2">
         <f t="shared" si="2"/>
         <v>2035</v>
       </c>
     </row>
-    <row r="4" spans="1:58" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4">
+        <v>16</v>
+      </c>
+      <c r="H3" s="4">
+        <v>22</v>
+      </c>
+      <c r="I3" s="4">
+        <v>11</v>
+      </c>
+      <c r="J3" s="4">
+        <v>3</v>
+      </c>
+      <c r="K3" s="4">
+        <v>3</v>
+      </c>
+      <c r="L3" s="4">
+        <v>2</v>
+      </c>
+      <c r="M3" s="4">
+        <v>3</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="V3" s="2">
+        <v>5</v>
+      </c>
+      <c r="W3" s="2">
+        <v>3</v>
+      </c>
+      <c r="X3" s="2">
+        <v>5</v>
+      </c>
+      <c r="Y3" s="2">
+        <v>4</v>
+      </c>
+      <c r="Z3" s="2">
+        <f t="shared" ref="Z3:Z6" si="3">+V3</f>
+        <v>5</v>
+      </c>
+      <c r="AA3" s="2">
+        <v>2</v>
+      </c>
+      <c r="AB3" s="2">
+        <f t="shared" ref="AB3" si="4">+X3</f>
+        <v>5</v>
+      </c>
+      <c r="AC3" s="2">
+        <f t="shared" ref="AC3" si="5">+Y3</f>
+        <v>4</v>
+      </c>
+      <c r="AD3" s="2">
+        <f t="shared" ref="AD3" si="6">+Z3</f>
+        <v>5</v>
+      </c>
+      <c r="AT3" s="2">
+        <f>31904-31847</f>
+        <v>57</v>
+      </c>
+      <c r="AU3" s="2">
+        <f>34608-34542</f>
+        <v>66</v>
+      </c>
+      <c r="AV3" s="2">
+        <f>SUM(G3:J3)</f>
+        <v>52</v>
+      </c>
+      <c r="AW3" s="2">
+        <f>SUM(K3:N3)</f>
+        <v>8</v>
+      </c>
+      <c r="AX3" s="2">
+        <f t="shared" ref="AX3:AX18" si="7">SUM(O3:R3)</f>
+        <v>0</v>
+      </c>
+      <c r="AY3" s="2">
+        <f>SUM(S3:V3)</f>
+        <v>5</v>
+      </c>
+      <c r="AZ3" s="2">
+        <f>SUM(W3:Z3)</f>
+        <v>17</v>
+      </c>
+      <c r="BA3" s="2">
+        <f t="shared" ref="BA3:BE3" si="8">+AZ3*1.03</f>
+        <v>17.510000000000002</v>
+      </c>
+      <c r="BB3" s="2">
+        <f t="shared" si="8"/>
+        <v>18.035300000000003</v>
+      </c>
+      <c r="BC3" s="2">
+        <f t="shared" si="8"/>
+        <v>18.576359000000004</v>
+      </c>
+      <c r="BD3" s="2">
+        <f t="shared" si="8"/>
+        <v>19.133649770000005</v>
+      </c>
+      <c r="BE3" s="2">
+        <f t="shared" si="8"/>
+        <v>19.707659263100005</v>
+      </c>
+      <c r="BF3" s="2">
+        <f t="shared" ref="BF3:BJ3" si="9">+BE3*1.03</f>
+        <v>20.298889040993007</v>
+      </c>
+      <c r="BG3" s="2">
+        <f t="shared" si="9"/>
+        <v>20.907855712222798</v>
+      </c>
+      <c r="BH3" s="2">
+        <f t="shared" si="9"/>
+        <v>21.535091383589481</v>
+      </c>
+      <c r="BI3" s="2">
+        <f t="shared" si="9"/>
+        <v>22.181144125097166</v>
+      </c>
+      <c r="BJ3" s="2">
+        <f t="shared" si="9"/>
+        <v>22.846578448850082</v>
+      </c>
+    </row>
+    <row r="4" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4">
-        <v>16</v>
+        <v>1070</v>
       </c>
       <c r="H4" s="4">
-        <v>22</v>
+        <v>1180</v>
       </c>
       <c r="I4" s="4">
-        <v>11</v>
+        <v>1265</v>
       </c>
       <c r="J4" s="4">
-        <v>3</v>
+        <v>1203</v>
       </c>
       <c r="K4" s="4">
-        <v>3</v>
+        <v>1147</v>
       </c>
       <c r="L4" s="4">
-        <v>2</v>
+        <v>1223</v>
       </c>
       <c r="M4" s="4">
-        <v>3</v>
-      </c>
-      <c r="N4" s="4"/>
-      <c r="V4" s="2">
-        <v>5</v>
+        <v>1326</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1216</v>
+      </c>
+      <c r="O4" s="2">
+        <v>1189</v>
+      </c>
+      <c r="P4" s="2">
+        <v>1287</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>1368</v>
+      </c>
+      <c r="R4" s="2">
+        <v>1222</v>
+      </c>
+      <c r="S4" s="2">
+        <v>1226.4000000000001</v>
+      </c>
+      <c r="T4" s="2">
+        <v>1294</v>
+      </c>
+      <c r="U4" s="4">
+        <v>1406</v>
+      </c>
+      <c r="V4" s="4">
+        <v>1268</v>
       </c>
       <c r="W4" s="2">
-        <v>3</v>
+        <v>1260</v>
       </c>
       <c r="X4" s="2">
-        <f t="shared" ref="X4:X7" si="3">+T4</f>
-        <v>0</v>
+        <v>1383</v>
       </c>
       <c r="Y4" s="2">
-        <f t="shared" ref="Y4:Y7" si="4">+U4</f>
-        <v>0</v>
+        <v>1511</v>
       </c>
       <c r="Z4" s="2">
-        <f t="shared" ref="Z4:Z7" si="5">+V4</f>
-        <v>5</v>
-      </c>
-      <c r="AP4" s="2">
-        <f>31904-31847</f>
-        <v>57</v>
-      </c>
-      <c r="AQ4" s="2">
-        <f>34608-34542</f>
-        <v>66</v>
+        <f>4167+1369-Y4-X4-W4</f>
+        <v>1382</v>
+      </c>
+      <c r="AA4" s="2">
+        <v>1426</v>
+      </c>
+      <c r="AB4" s="2">
+        <f t="shared" ref="AB4" si="10">+X4</f>
+        <v>1383</v>
+      </c>
+      <c r="AC4" s="2">
+        <f t="shared" ref="AC4" si="11">+Y4</f>
+        <v>1511</v>
+      </c>
+      <c r="AD4" s="2">
+        <f t="shared" ref="AD4" si="12">+Z4</f>
+        <v>1382</v>
       </c>
       <c r="AR4" s="2">
-        <f>SUM(G4:J4)</f>
-        <v>52</v>
+        <f>3307+980</f>
+        <v>4287</v>
       </c>
       <c r="AS4" s="2">
-        <f>SUM(K4:N4)</f>
-        <v>8</v>
+        <f>3363+1059</f>
+        <v>4422</v>
       </c>
       <c r="AT4" s="2">
-        <f t="shared" ref="AT4:AT18" si="6">SUM(O4:R4)</f>
-        <v>0</v>
+        <f>3392+1094</f>
+        <v>4486</v>
       </c>
       <c r="AU4" s="2">
-        <f>SUM(S4:V4)</f>
-        <v>5</v>
+        <f>3209+1094</f>
+        <v>4303</v>
       </c>
       <c r="AV4" s="2">
-        <f>SUM(W4:Z4)</f>
-        <v>8</v>
+        <f t="shared" ref="AV4:AV20" si="13">SUM(G4:J4)</f>
+        <v>4718</v>
       </c>
       <c r="AW4" s="2">
-        <f t="shared" ref="AW4:BA4" si="7">+AV4*1.03</f>
-        <v>8.24</v>
+        <f t="shared" ref="AW4:AW20" si="14">SUM(K4:N4)</f>
+        <v>4912</v>
       </c>
       <c r="AX4" s="2">
         <f t="shared" si="7"/>
-        <v>8.4871999999999996</v>
+        <v>5066</v>
       </c>
       <c r="AY4" s="2">
-        <f t="shared" si="7"/>
-        <v>8.741816</v>
+        <f>SUM(S4:V4)</f>
+        <v>5194.3999999999996</v>
       </c>
       <c r="AZ4" s="2">
-        <f t="shared" si="7"/>
-        <v>9.0040704800000011</v>
+        <f t="shared" ref="AZ4:AZ23" si="15">SUM(W4:Z4)</f>
+        <v>5536</v>
       </c>
       <c r="BA4" s="2">
-        <f t="shared" si="7"/>
-        <v>9.2741925944000005</v>
+        <f t="shared" ref="BA4:BE4" si="16">+AZ4*1.03</f>
+        <v>5702.08</v>
       </c>
       <c r="BB4" s="2">
-        <f t="shared" ref="BB4:BF4" si="8">+BA4*1.03</f>
-        <v>9.5524183722320011</v>
+        <f t="shared" si="16"/>
+        <v>5873.1423999999997</v>
       </c>
       <c r="BC4" s="2">
-        <f t="shared" si="8"/>
-        <v>9.8389909233989616</v>
+        <f t="shared" si="16"/>
+        <v>6049.3366719999995</v>
       </c>
       <c r="BD4" s="2">
-        <f t="shared" si="8"/>
-        <v>10.134160651100931</v>
+        <f t="shared" si="16"/>
+        <v>6230.8167721599993</v>
       </c>
       <c r="BE4" s="2">
-        <f t="shared" si="8"/>
-        <v>10.438185470633959</v>
+        <f t="shared" si="16"/>
+        <v>6417.7412753247991</v>
       </c>
       <c r="BF4" s="2">
-        <f t="shared" si="8"/>
-        <v>10.751331034752978</v>
-      </c>
-    </row>
-    <row r="5" spans="1:58" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF4:BJ4" si="17">+BE4*1.03</f>
+        <v>6610.2735135845433</v>
+      </c>
+      <c r="BG4" s="2">
+        <f t="shared" si="17"/>
+        <v>6808.5817189920799</v>
+      </c>
+      <c r="BH4" s="2">
+        <f t="shared" si="17"/>
+        <v>7012.8391705618424</v>
+      </c>
+      <c r="BI4" s="2">
+        <f t="shared" si="17"/>
+        <v>7223.2243456786982</v>
+      </c>
+      <c r="BJ4" s="2">
+        <f t="shared" si="17"/>
+        <v>7439.9210760490596</v>
+      </c>
+    </row>
+    <row r="5" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4">
-        <v>1070</v>
+        <v>129</v>
       </c>
       <c r="H5" s="4">
-        <v>1180</v>
+        <v>137</v>
       </c>
       <c r="I5" s="4">
-        <v>1265</v>
+        <v>135</v>
       </c>
       <c r="J5" s="4">
-        <v>1203</v>
+        <v>135</v>
       </c>
       <c r="K5" s="4">
-        <v>1147</v>
+        <v>128</v>
       </c>
       <c r="L5" s="4">
-        <v>1223</v>
+        <v>139</v>
       </c>
       <c r="M5" s="4">
-        <v>1326</v>
+        <v>127</v>
       </c>
       <c r="N5" s="4">
-        <v>1216</v>
+        <v>131</v>
       </c>
       <c r="O5" s="2">
-        <v>1189</v>
+        <v>134</v>
       </c>
       <c r="P5" s="2">
-        <v>1287</v>
+        <v>142</v>
       </c>
       <c r="Q5" s="2">
-        <v>1368</v>
+        <v>140</v>
       </c>
       <c r="R5" s="2">
-        <v>1222</v>
+        <v>149</v>
       </c>
       <c r="S5" s="2">
-        <v>1226.4000000000001</v>
+        <v>139.4</v>
       </c>
       <c r="T5" s="2">
-        <v>1294</v>
+        <v>156</v>
       </c>
       <c r="U5" s="4">
-        <v>1406</v>
+        <v>146</v>
       </c>
       <c r="V5" s="4">
-        <v>1268</v>
+        <v>147</v>
       </c>
       <c r="W5" s="2">
-        <v>1260</v>
+        <v>142</v>
       </c>
       <c r="X5" s="2">
-        <f t="shared" si="3"/>
-        <v>1294</v>
+        <v>148</v>
       </c>
       <c r="Y5" s="2">
-        <f t="shared" si="4"/>
-        <v>1406</v>
+        <v>158</v>
       </c>
       <c r="Z5" s="2">
-        <f t="shared" si="5"/>
-        <v>1268</v>
-      </c>
-      <c r="AN5" s="2">
-        <f>3307+980</f>
-        <v>4287</v>
-      </c>
-      <c r="AO5" s="2">
-        <f>3363+1059</f>
-        <v>4422</v>
-      </c>
-      <c r="AP5" s="2">
-        <f>3392+1094</f>
-        <v>4486</v>
-      </c>
-      <c r="AQ5" s="2">
-        <f>3209+1094</f>
-        <v>4303</v>
+        <f>606-Y5-X5-W5</f>
+        <v>158</v>
       </c>
       <c r="AR5" s="2">
-        <f t="shared" ref="AR5:AR20" si="9">SUM(G5:J5)</f>
-        <v>4718</v>
+        <v>550</v>
       </c>
       <c r="AS5" s="2">
-        <f t="shared" ref="AS5:AS20" si="10">SUM(K5:N5)</f>
-        <v>4912</v>
+        <v>553</v>
       </c>
       <c r="AT5" s="2">
-        <f t="shared" si="6"/>
-        <v>5066</v>
+        <v>561</v>
       </c>
       <c r="AU5" s="2">
-        <f>SUM(S5:V5)</f>
-        <v>5194.3999999999996</v>
+        <v>516</v>
       </c>
       <c r="AV5" s="2">
-        <f t="shared" ref="AV5:AV23" si="11">SUM(W5:Z5)</f>
-        <v>5228</v>
+        <f t="shared" si="13"/>
+        <v>536</v>
       </c>
       <c r="AW5" s="2">
-        <f t="shared" ref="AW5:BA5" si="12">+AV5*1.03</f>
-        <v>5384.84</v>
+        <f t="shared" si="14"/>
+        <v>525</v>
       </c>
       <c r="AX5" s="2">
-        <f t="shared" si="12"/>
-        <v>5546.3852000000006</v>
+        <f t="shared" si="7"/>
+        <v>565</v>
       </c>
       <c r="AY5" s="2">
-        <f t="shared" si="12"/>
-        <v>5712.7767560000011</v>
+        <f t="shared" ref="AY5:AY20" si="18">SUM(S5:V5)</f>
+        <v>588.4</v>
       </c>
       <c r="AZ5" s="2">
-        <f t="shared" si="12"/>
-        <v>5884.1600586800014</v>
+        <f t="shared" si="15"/>
+        <v>606</v>
       </c>
       <c r="BA5" s="2">
-        <f t="shared" si="12"/>
-        <v>6060.6848604404013</v>
+        <f t="shared" ref="BA5:BE5" si="19">+AZ5*1.03</f>
+        <v>624.18000000000006</v>
       </c>
       <c r="BB5" s="2">
-        <f t="shared" ref="BB5:BF5" si="13">+BA5*1.03</f>
-        <v>6242.5054062536137</v>
+        <f t="shared" si="19"/>
+        <v>642.9054000000001</v>
       </c>
       <c r="BC5" s="2">
-        <f t="shared" si="13"/>
-        <v>6429.7805684412224</v>
+        <f t="shared" si="19"/>
+        <v>662.19256200000007</v>
       </c>
       <c r="BD5" s="2">
-        <f t="shared" si="13"/>
-        <v>6622.673985494459</v>
+        <f t="shared" si="19"/>
+        <v>682.05833886000005</v>
       </c>
       <c r="BE5" s="2">
-        <f t="shared" si="13"/>
-        <v>6821.3542050592932</v>
+        <f t="shared" si="19"/>
+        <v>702.52008902580008</v>
       </c>
       <c r="BF5" s="2">
-        <f t="shared" si="13"/>
-        <v>7025.9948312110719</v>
-      </c>
-    </row>
-    <row r="6" spans="1:58" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF5:BJ5" si="20">+BE5*1.03</f>
+        <v>723.59569169657414</v>
+      </c>
+      <c r="BG5" s="2">
+        <f t="shared" si="20"/>
+        <v>745.30356244747134</v>
+      </c>
+      <c r="BH5" s="2">
+        <f t="shared" si="20"/>
+        <v>767.66266932089547</v>
+      </c>
+      <c r="BI5" s="2">
+        <f t="shared" si="20"/>
+        <v>790.69254940052235</v>
+      </c>
+      <c r="BJ5" s="2">
+        <f t="shared" si="20"/>
+        <v>814.41332588253806</v>
+      </c>
+    </row>
+    <row r="6" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4">
-        <v>129</v>
+        <v>447</v>
       </c>
       <c r="H6" s="4">
+        <v>290</v>
+      </c>
+      <c r="I6" s="4">
+        <v>345</v>
+      </c>
+      <c r="J6" s="4">
+        <v>345</v>
+      </c>
+      <c r="K6" s="4">
+        <v>420</v>
+      </c>
+      <c r="L6" s="4">
+        <v>212</v>
+      </c>
+      <c r="M6" s="4">
+        <v>183</v>
+      </c>
+      <c r="N6" s="4">
+        <v>180</v>
+      </c>
+      <c r="O6" s="2">
+        <v>147</v>
+      </c>
+      <c r="P6" s="2">
+        <v>141</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>133</v>
+      </c>
+      <c r="R6" s="2">
+        <v>153</v>
+      </c>
+      <c r="S6" s="2">
+        <v>129.4</v>
+      </c>
+      <c r="T6" s="2">
+        <v>127</v>
+      </c>
+      <c r="U6" s="4">
+        <v>128</v>
+      </c>
+      <c r="V6" s="4">
         <v>137</v>
       </c>
-      <c r="I6" s="4">
-        <v>135</v>
-      </c>
-      <c r="J6" s="4">
-        <v>135</v>
-      </c>
-      <c r="K6" s="4">
-        <v>128</v>
-      </c>
-      <c r="L6" s="4">
-        <v>139</v>
-      </c>
-      <c r="M6" s="4">
-        <v>127</v>
-      </c>
-      <c r="N6" s="4">
+      <c r="W6" s="2">
+        <v>122</v>
+      </c>
+      <c r="X6" s="2">
+        <v>123</v>
+      </c>
+      <c r="Y6" s="2">
         <v>131</v>
       </c>
-      <c r="O6" s="2">
-        <v>134</v>
-      </c>
-      <c r="P6" s="2">
-        <v>142</v>
-      </c>
-      <c r="Q6" s="2">
-        <v>140</v>
-      </c>
-      <c r="R6" s="2">
-        <v>149</v>
-      </c>
-      <c r="S6" s="2">
-        <v>139.4</v>
-      </c>
-      <c r="T6" s="2">
-        <v>156</v>
-      </c>
-      <c r="U6" s="4">
-        <v>146</v>
-      </c>
-      <c r="V6" s="4">
-        <v>147</v>
-      </c>
-      <c r="W6" s="2">
-        <v>142</v>
-      </c>
-      <c r="X6" s="2">
-        <f t="shared" si="3"/>
-        <v>156</v>
-      </c>
-      <c r="Y6" s="2">
-        <f t="shared" si="4"/>
-        <v>146</v>
-      </c>
       <c r="Z6" s="2">
-        <f t="shared" si="5"/>
-        <v>147</v>
-      </c>
-      <c r="AN6" s="2">
-        <v>550</v>
-      </c>
-      <c r="AO6" s="2">
-        <v>553</v>
-      </c>
-      <c r="AP6" s="2">
-        <v>561</v>
-      </c>
-      <c r="AQ6" s="2">
-        <v>516</v>
+        <f>517-Y6-X6-W6</f>
+        <v>141</v>
       </c>
       <c r="AR6" s="2">
-        <f t="shared" si="9"/>
-        <v>536</v>
+        <v>463</v>
       </c>
       <c r="AS6" s="2">
-        <f t="shared" si="10"/>
-        <v>525</v>
+        <v>484</v>
       </c>
       <c r="AT6" s="2">
-        <f t="shared" si="6"/>
-        <v>565</v>
+        <v>442</v>
       </c>
       <c r="AU6" s="2">
-        <f t="shared" ref="AU6:AU20" si="14">SUM(S6:V6)</f>
-        <v>588.4</v>
+        <v>1438</v>
       </c>
       <c r="AV6" s="2">
-        <f t="shared" si="11"/>
-        <v>591</v>
+        <f t="shared" si="13"/>
+        <v>1427</v>
       </c>
       <c r="AW6" s="2">
-        <f t="shared" ref="AW6:BA6" si="15">+AV6*1.03</f>
-        <v>608.73</v>
+        <f t="shared" si="14"/>
+        <v>995</v>
       </c>
       <c r="AX6" s="2">
-        <f t="shared" si="15"/>
-        <v>626.99189999999999</v>
+        <f t="shared" si="7"/>
+        <v>574</v>
       </c>
       <c r="AY6" s="2">
-        <f t="shared" si="15"/>
-        <v>645.80165699999998</v>
+        <f t="shared" si="18"/>
+        <v>521.4</v>
       </c>
       <c r="AZ6" s="2">
         <f t="shared" si="15"/>
-        <v>665.17570670999999</v>
+        <v>517</v>
       </c>
       <c r="BA6" s="2">
-        <f t="shared" si="15"/>
-        <v>685.13097791129996</v>
+        <f t="shared" ref="BA6:BE6" si="21">+AZ6*1.03</f>
+        <v>532.51</v>
       </c>
       <c r="BB6" s="2">
-        <f t="shared" ref="BB6:BF6" si="16">+BA6*1.03</f>
-        <v>705.68490724863898</v>
+        <f t="shared" si="21"/>
+        <v>548.48530000000005</v>
       </c>
       <c r="BC6" s="2">
-        <f t="shared" si="16"/>
-        <v>726.85545446609819</v>
+        <f t="shared" si="21"/>
+        <v>564.93985900000007</v>
       </c>
       <c r="BD6" s="2">
-        <f t="shared" si="16"/>
-        <v>748.66111810008113</v>
+        <f t="shared" si="21"/>
+        <v>581.88805477000005</v>
       </c>
       <c r="BE6" s="2">
-        <f t="shared" si="16"/>
-        <v>771.12095164308357</v>
+        <f t="shared" si="21"/>
+        <v>599.34469641310011</v>
       </c>
       <c r="BF6" s="2">
-        <f t="shared" si="16"/>
-        <v>794.25458019237612</v>
-      </c>
-    </row>
-    <row r="7" spans="1:58" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF6:BJ6" si="22">+BE6*1.03</f>
+        <v>617.32503730549308</v>
+      </c>
+      <c r="BG6" s="2">
+        <f t="shared" si="22"/>
+        <v>635.84478842465785</v>
+      </c>
+      <c r="BH6" s="2">
+        <f t="shared" si="22"/>
+        <v>654.92013207739762</v>
+      </c>
+      <c r="BI6" s="2">
+        <f t="shared" si="22"/>
+        <v>674.56773603971953</v>
+      </c>
+      <c r="BJ6" s="2">
+        <f t="shared" si="22"/>
+        <v>694.80476812091115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4">
-        <v>447</v>
+        <v>1182</v>
       </c>
       <c r="H7" s="4">
-        <v>290</v>
+        <v>1306</v>
       </c>
       <c r="I7" s="4">
-        <v>345</v>
+        <v>1292</v>
       </c>
       <c r="J7" s="4">
-        <v>345</v>
+        <v>1348</v>
       </c>
       <c r="K7" s="4">
-        <v>420</v>
+        <v>1184</v>
       </c>
       <c r="L7" s="4">
-        <v>212</v>
+        <v>1221</v>
       </c>
       <c r="M7" s="4">
-        <v>183</v>
+        <v>1219</v>
       </c>
       <c r="N7" s="4">
-        <v>180</v>
+        <v>1264</v>
       </c>
       <c r="O7" s="2">
-        <v>147</v>
+        <v>1182</v>
       </c>
       <c r="P7" s="2">
-        <v>141</v>
+        <v>1293</v>
       </c>
       <c r="Q7" s="2">
-        <v>133</v>
+        <v>1314</v>
       </c>
       <c r="R7" s="2">
-        <v>153</v>
+        <v>1370</v>
       </c>
       <c r="S7" s="2">
-        <v>129.4</v>
+        <v>1205.4000000000001</v>
       </c>
       <c r="T7" s="2">
-        <v>127</v>
+        <v>1329</v>
       </c>
       <c r="U7" s="4">
-        <v>128</v>
+        <v>1314</v>
       </c>
       <c r="V7" s="4">
-        <v>137</v>
+        <v>1387</v>
       </c>
       <c r="W7" s="2">
-        <v>122</v>
+        <v>1177</v>
       </c>
       <c r="X7" s="2">
-        <f t="shared" si="3"/>
-        <v>127</v>
+        <v>1358</v>
       </c>
       <c r="Y7" s="2">
-        <f t="shared" si="4"/>
-        <v>128</v>
+        <v>1364</v>
       </c>
       <c r="Z7" s="2">
-        <f t="shared" si="5"/>
-        <v>137</v>
-      </c>
-      <c r="AN7" s="2">
-        <v>463</v>
-      </c>
-      <c r="AO7" s="2">
-        <v>484</v>
-      </c>
-      <c r="AP7" s="2">
-        <v>442</v>
-      </c>
-      <c r="AQ7" s="2">
-        <v>1438</v>
+        <f>5360-Y7-X7-W7</f>
+        <v>1461</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>1272</v>
+      </c>
+      <c r="AB7" s="2">
+        <f t="shared" ref="AB7" si="23">+X7</f>
+        <v>1358</v>
+      </c>
+      <c r="AC7" s="2">
+        <f t="shared" ref="AC7" si="24">+Y7</f>
+        <v>1364</v>
+      </c>
+      <c r="AD7" s="2">
+        <f t="shared" ref="AD7" si="25">+Z7</f>
+        <v>1461</v>
       </c>
       <c r="AR7" s="2">
-        <f t="shared" si="9"/>
-        <v>1427</v>
+        <v>4063</v>
       </c>
       <c r="AS7" s="2">
-        <f t="shared" si="10"/>
-        <v>995</v>
+        <v>4386</v>
       </c>
       <c r="AT7" s="2">
-        <f t="shared" si="6"/>
-        <v>574</v>
+        <v>4656</v>
       </c>
       <c r="AU7" s="2">
+        <v>4475</v>
+      </c>
+      <c r="AV7" s="2">
+        <f t="shared" si="13"/>
+        <v>5128</v>
+      </c>
+      <c r="AW7" s="2">
         <f t="shared" si="14"/>
-        <v>521.4</v>
-      </c>
-      <c r="AV7" s="2">
-        <f t="shared" si="11"/>
-        <v>514</v>
-      </c>
-      <c r="AW7" s="2">
-        <f t="shared" ref="AW7:BA7" si="17">+AV7*1.03</f>
-        <v>529.41999999999996</v>
+        <v>4888</v>
       </c>
       <c r="AX7" s="2">
-        <f t="shared" si="17"/>
-        <v>545.30259999999998</v>
+        <f t="shared" si="7"/>
+        <v>5159</v>
       </c>
       <c r="AY7" s="2">
-        <f t="shared" si="17"/>
-        <v>561.66167800000005</v>
+        <f t="shared" si="18"/>
+        <v>5235.3999999999996</v>
       </c>
       <c r="AZ7" s="2">
-        <f t="shared" si="17"/>
-        <v>578.51152834000004</v>
+        <f t="shared" si="15"/>
+        <v>5360</v>
       </c>
       <c r="BA7" s="2">
-        <f t="shared" si="17"/>
-        <v>595.86687419020006</v>
+        <f t="shared" ref="BA7:BE7" si="26">+AZ7*1.03</f>
+        <v>5520.8</v>
       </c>
       <c r="BB7" s="2">
-        <f t="shared" ref="BB7:BF7" si="18">+BA7*1.03</f>
-        <v>613.74288041590603</v>
+        <f t="shared" si="26"/>
+        <v>5686.424</v>
       </c>
       <c r="BC7" s="2">
-        <f t="shared" si="18"/>
-        <v>632.15516682838324</v>
+        <f t="shared" si="26"/>
+        <v>5857.0167200000005</v>
       </c>
       <c r="BD7" s="2">
-        <f t="shared" si="18"/>
-        <v>651.11982183323471</v>
+        <f t="shared" si="26"/>
+        <v>6032.727221600001</v>
       </c>
       <c r="BE7" s="2">
-        <f t="shared" si="18"/>
-        <v>670.65341648823176</v>
+        <f t="shared" si="26"/>
+        <v>6213.709038248001</v>
       </c>
       <c r="BF7" s="2">
-        <f t="shared" si="18"/>
-        <v>690.77301898287874</v>
-      </c>
-    </row>
-    <row r="8" spans="1:58" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF7:BJ7" si="27">+BE7*1.03</f>
+        <v>6400.1203093954409</v>
+      </c>
+      <c r="BG7" s="2">
+        <f t="shared" si="27"/>
+        <v>6592.1239186773046</v>
+      </c>
+      <c r="BH7" s="2">
+        <f t="shared" si="27"/>
+        <v>6789.8876362376241</v>
+      </c>
+      <c r="BI7" s="2">
+        <f t="shared" si="27"/>
+        <v>6993.5842653247528</v>
+      </c>
+      <c r="BJ7" s="2">
+        <f t="shared" si="27"/>
+        <v>7203.3917932844952</v>
+      </c>
+    </row>
+    <row r="8" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4">
-        <v>1182</v>
+        <v>2256</v>
       </c>
       <c r="H8" s="4">
-        <v>1306</v>
+        <v>1514</v>
       </c>
       <c r="I8" s="4">
-        <v>1292</v>
+        <v>2140</v>
       </c>
       <c r="J8" s="4">
-        <v>1348</v>
+        <v>2643</v>
       </c>
       <c r="K8" s="4">
-        <v>1184</v>
+        <v>3554</v>
       </c>
       <c r="L8" s="4">
-        <v>1221</v>
+        <v>2750</v>
       </c>
       <c r="M8" s="4">
-        <v>1219</v>
+        <v>2142</v>
       </c>
       <c r="N8" s="4">
-        <v>1264</v>
+        <v>1730</v>
       </c>
       <c r="O8" s="2">
-        <v>1182</v>
+        <v>1225</v>
       </c>
       <c r="P8" s="2">
-        <v>1293</v>
+        <v>741</v>
       </c>
       <c r="Q8" s="2">
-        <v>1314</v>
+        <v>862</v>
       </c>
       <c r="R8" s="2">
-        <v>1370</v>
+        <v>862</v>
       </c>
       <c r="S8" s="2">
-        <v>1205.4000000000001</v>
+        <v>741.4</v>
       </c>
       <c r="T8" s="2">
-        <v>1329</v>
+        <v>583</v>
       </c>
       <c r="U8" s="4">
-        <v>1314</v>
+        <v>824</v>
       </c>
       <c r="V8" s="4">
-        <v>1387</v>
+        <v>849</v>
       </c>
       <c r="W8" s="2">
-        <v>1177</v>
+        <v>613</v>
       </c>
       <c r="X8" s="2">
-        <f t="shared" ref="X8:X9" si="19">+T8</f>
-        <v>1329</v>
+        <v>544</v>
       </c>
       <c r="Y8" s="2">
-        <f t="shared" ref="Y8:Y9" si="20">+U8</f>
-        <v>1314</v>
+        <v>600</v>
       </c>
       <c r="Z8" s="2">
-        <f t="shared" ref="Z8:Z9" si="21">+V8</f>
-        <v>1387</v>
-      </c>
-      <c r="AN8" s="2">
-        <v>4063</v>
-      </c>
-      <c r="AO8" s="2">
-        <v>4386</v>
-      </c>
-      <c r="AP8" s="2">
-        <v>4656</v>
-      </c>
-      <c r="AQ8" s="2">
-        <v>4475</v>
+        <f>2454-Y8-X8-W8</f>
+        <v>697</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>812</v>
+      </c>
+      <c r="AB8" s="2">
+        <f t="shared" ref="AB8" si="28">+X8</f>
+        <v>544</v>
+      </c>
+      <c r="AC8" s="2">
+        <f t="shared" ref="AC8" si="29">+Y8</f>
+        <v>600</v>
+      </c>
+      <c r="AD8" s="2">
+        <f t="shared" ref="AD8" si="30">+Z8</f>
+        <v>697</v>
       </c>
       <c r="AR8" s="2">
-        <f t="shared" si="9"/>
-        <v>5128</v>
+        <v>540</v>
       </c>
       <c r="AS8" s="2">
-        <f t="shared" si="10"/>
-        <v>4888</v>
+        <v>2072</v>
       </c>
       <c r="AT8" s="2">
-        <f t="shared" si="6"/>
-        <v>5159</v>
+        <v>2054</v>
       </c>
       <c r="AU8" s="2">
+        <v>4376</v>
+      </c>
+      <c r="AV8" s="2">
+        <f t="shared" si="13"/>
+        <v>8553</v>
+      </c>
+      <c r="AW8" s="2">
         <f t="shared" si="14"/>
-        <v>5235.3999999999996</v>
-      </c>
-      <c r="AV8" s="2">
-        <f t="shared" si="11"/>
-        <v>5207</v>
-      </c>
-      <c r="AW8" s="2">
-        <f t="shared" ref="AW8:BA8" si="22">+AV8*1.03</f>
-        <v>5363.21</v>
+        <v>10176</v>
       </c>
       <c r="AX8" s="2">
-        <f t="shared" si="22"/>
-        <v>5524.1063000000004</v>
+        <f t="shared" si="7"/>
+        <v>3690</v>
       </c>
       <c r="AY8" s="2">
-        <f t="shared" si="22"/>
-        <v>5689.8294890000006</v>
+        <f t="shared" si="18"/>
+        <v>2997.4</v>
       </c>
       <c r="AZ8" s="2">
-        <f t="shared" si="22"/>
-        <v>5860.5243736700004</v>
+        <f t="shared" si="15"/>
+        <v>2454</v>
       </c>
       <c r="BA8" s="2">
-        <f t="shared" si="22"/>
-        <v>6036.3401048801006</v>
+        <f t="shared" ref="BA8:BE8" si="31">+AZ8*1.03</f>
+        <v>2527.62</v>
       </c>
       <c r="BB8" s="2">
-        <f t="shared" ref="BB8:BF8" si="23">+BA8*1.03</f>
-        <v>6217.4303080265036</v>
+        <f t="shared" si="31"/>
+        <v>2603.4486000000002</v>
       </c>
       <c r="BC8" s="2">
-        <f t="shared" si="23"/>
-        <v>6403.9532172672989</v>
+        <f t="shared" si="31"/>
+        <v>2681.5520580000002</v>
       </c>
       <c r="BD8" s="2">
-        <f t="shared" si="23"/>
-        <v>6596.0718137853182</v>
+        <f t="shared" si="31"/>
+        <v>2761.9986197400003</v>
       </c>
       <c r="BE8" s="2">
-        <f t="shared" si="23"/>
-        <v>6793.9539681988781</v>
+        <f t="shared" si="31"/>
+        <v>2844.8585783322005</v>
       </c>
       <c r="BF8" s="2">
-        <f t="shared" si="23"/>
-        <v>6997.7725872448445</v>
-      </c>
-    </row>
-    <row r="9" spans="1:58" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF8:BJ8" si="32">+BE8*1.03</f>
+        <v>2930.2043356821664</v>
+      </c>
+      <c r="BG8" s="2">
+        <f t="shared" si="32"/>
+        <v>3018.1104657526316</v>
+      </c>
+      <c r="BH8" s="2">
+        <f t="shared" si="32"/>
+        <v>3108.6537797252108</v>
+      </c>
+      <c r="BI8" s="2">
+        <f t="shared" si="32"/>
+        <v>3201.9133931169672</v>
+      </c>
+      <c r="BJ8" s="2">
+        <f t="shared" si="32"/>
+        <v>3297.9707949104763</v>
+      </c>
+    </row>
+    <row r="9" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
-      <c r="G9" s="4">
-        <v>2256</v>
-      </c>
-      <c r="H9" s="4">
-        <v>1514</v>
-      </c>
-      <c r="I9" s="4">
-        <v>2140</v>
-      </c>
-      <c r="J9" s="4">
-        <v>2643</v>
-      </c>
-      <c r="K9" s="4">
-        <v>3554</v>
-      </c>
-      <c r="L9" s="4">
-        <v>2750</v>
-      </c>
-      <c r="M9" s="4">
-        <v>2142</v>
-      </c>
-      <c r="N9" s="4">
-        <v>1730</v>
-      </c>
-      <c r="O9" s="2">
-        <v>1225</v>
-      </c>
-      <c r="P9" s="2">
-        <v>741</v>
-      </c>
-      <c r="Q9" s="2">
-        <v>862</v>
-      </c>
-      <c r="R9" s="2">
-        <v>862</v>
-      </c>
-      <c r="S9" s="2">
-        <v>741.4</v>
-      </c>
-      <c r="T9" s="2">
-        <v>583</v>
-      </c>
-      <c r="U9" s="4">
-        <v>824</v>
-      </c>
-      <c r="V9" s="4">
-        <v>849</v>
-      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
       <c r="W9" s="2">
-        <v>613</v>
+        <v>0</v>
       </c>
       <c r="X9" s="2">
-        <f t="shared" si="19"/>
-        <v>583</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="2">
-        <f t="shared" si="20"/>
-        <v>824</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="2">
-        <f t="shared" si="21"/>
-        <v>849</v>
-      </c>
-      <c r="AN9" s="2">
-        <v>540</v>
-      </c>
-      <c r="AO9" s="2">
-        <v>2072</v>
-      </c>
-      <c r="AP9" s="2">
-        <v>2054</v>
-      </c>
-      <c r="AQ9" s="2">
-        <v>4376</v>
-      </c>
-      <c r="AR9" s="2">
-        <f t="shared" si="9"/>
-        <v>8553</v>
-      </c>
-      <c r="AS9" s="2">
-        <f t="shared" si="10"/>
-        <v>10176</v>
-      </c>
-      <c r="AT9" s="2">
-        <f t="shared" si="6"/>
-        <v>3690</v>
-      </c>
-      <c r="AU9" s="2">
-        <f t="shared" si="14"/>
-        <v>2997.4</v>
-      </c>
-      <c r="AV9" s="2">
-        <f t="shared" si="11"/>
-        <v>2869</v>
-      </c>
-      <c r="AW9" s="2">
-        <f t="shared" ref="AW9:BA9" si="24">+AV9*1.03</f>
-        <v>2955.07</v>
-      </c>
-      <c r="AX9" s="2">
-        <f t="shared" si="24"/>
-        <v>3043.7221000000004</v>
-      </c>
-      <c r="AY9" s="2">
-        <f t="shared" si="24"/>
-        <v>3135.0337630000004</v>
-      </c>
-      <c r="AZ9" s="2">
-        <f t="shared" si="24"/>
-        <v>3229.0847758900004</v>
-      </c>
-      <c r="BA9" s="2">
-        <f t="shared" si="24"/>
-        <v>3325.9573191667005</v>
-      </c>
-      <c r="BB9" s="2">
-        <f t="shared" ref="BB9:BF9" si="25">+BA9*1.03</f>
-        <v>3425.7360387417016</v>
-      </c>
-      <c r="BC9" s="2">
-        <f t="shared" si="25"/>
-        <v>3528.5081199039528</v>
-      </c>
-      <c r="BD9" s="2">
-        <f t="shared" si="25"/>
-        <v>3634.3633635010715</v>
-      </c>
-      <c r="BE9" s="2">
-        <f t="shared" si="25"/>
-        <v>3743.394264406104</v>
-      </c>
-      <c r="BF9" s="2">
-        <f t="shared" si="25"/>
-        <v>3855.6960923382871</v>
-      </c>
-    </row>
-    <row r="10" spans="1:58" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>96</v>
+      </c>
+      <c r="AB9" s="2">
+        <f>+AA9</f>
+        <v>96</v>
+      </c>
+      <c r="AC9" s="2">
+        <f>+AB9</f>
+        <v>96</v>
+      </c>
+      <c r="AD9" s="2">
+        <f>+AC9</f>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>32</v>
       </c>
@@ -2431,95 +2554,108 @@
         <v>1041</v>
       </c>
       <c r="X10" s="2">
-        <f>+T10</f>
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="Y10" s="2">
-        <f t="shared" ref="Y10:Y11" si="26">+U10</f>
-        <v>955</v>
+        <v>977</v>
       </c>
       <c r="Z10" s="2">
-        <f t="shared" ref="Z10:Z11" si="27">+V10</f>
-        <v>1000</v>
-      </c>
-      <c r="AN10" s="2">
+        <f>2158+1816-Y10-X10-W10</f>
+        <v>902</v>
+      </c>
+      <c r="AA10" s="2">
+        <v>953</v>
+      </c>
+      <c r="AB10" s="2">
+        <f t="shared" ref="AB10:AB11" si="33">+X10</f>
+        <v>1054</v>
+      </c>
+      <c r="AC10" s="2">
+        <f t="shared" ref="AC10:AC11" si="34">+Y10</f>
+        <v>977</v>
+      </c>
+      <c r="AD10" s="2">
+        <f t="shared" ref="AD10:AD11" si="35">+Z10</f>
+        <v>902</v>
+      </c>
+      <c r="AR10" s="2">
         <f>2112+1777</f>
         <v>3889</v>
       </c>
-      <c r="AO10" s="2">
+      <c r="AS10" s="2">
         <f>1843+2254</f>
         <v>4097</v>
       </c>
-      <c r="AP10" s="2">
+      <c r="AT10" s="2">
         <f>1879+2282</f>
         <v>4161</v>
       </c>
-      <c r="AQ10" s="2">
+      <c r="AU10" s="2">
         <f>2140+1987</f>
         <v>4127</v>
       </c>
-      <c r="AR10" s="2">
+      <c r="AV10" s="2">
         <f>SUM(G10:J10)</f>
         <v>4298</v>
       </c>
-      <c r="AS10" s="2">
+      <c r="AW10" s="2">
         <f>SUM(K10:N10)</f>
         <v>3481</v>
       </c>
-      <c r="AT10" s="2">
-        <f t="shared" si="6"/>
+      <c r="AX10" s="2">
+        <f t="shared" si="7"/>
         <v>3934</v>
       </c>
-      <c r="AU10" s="2">
-        <f t="shared" si="14"/>
+      <c r="AY10" s="2">
+        <f t="shared" si="18"/>
         <v>4023.4</v>
       </c>
-      <c r="AV10" s="2">
-        <f t="shared" si="11"/>
-        <v>4055</v>
-      </c>
-      <c r="AW10" s="2">
-        <f t="shared" ref="AW10:BA10" si="28">+AV10*1.03</f>
-        <v>4176.6500000000005</v>
-      </c>
-      <c r="AX10" s="2">
-        <f t="shared" si="28"/>
-        <v>4301.9495000000006</v>
-      </c>
-      <c r="AY10" s="2">
-        <f t="shared" si="28"/>
-        <v>4431.0079850000011</v>
-      </c>
       <c r="AZ10" s="2">
-        <f t="shared" si="28"/>
-        <v>4563.938224550001</v>
+        <f t="shared" si="15"/>
+        <v>3974</v>
       </c>
       <c r="BA10" s="2">
-        <f t="shared" si="28"/>
-        <v>4700.8563712865016</v>
+        <f t="shared" ref="BA10:BE10" si="36">+AZ10*1.03</f>
+        <v>4093.2200000000003</v>
       </c>
       <c r="BB10" s="2">
-        <f t="shared" ref="BB10:BF10" si="29">+BA10*1.03</f>
-        <v>4841.8820624250966</v>
+        <f t="shared" si="36"/>
+        <v>4216.0165999999999</v>
       </c>
       <c r="BC10" s="2">
-        <f t="shared" si="29"/>
-        <v>4987.1385242978495</v>
+        <f t="shared" si="36"/>
+        <v>4342.4970979999998</v>
       </c>
       <c r="BD10" s="2">
-        <f t="shared" si="29"/>
-        <v>5136.7526800267851</v>
+        <f t="shared" si="36"/>
+        <v>4472.7720109399997</v>
       </c>
       <c r="BE10" s="2">
-        <f t="shared" si="29"/>
-        <v>5290.8552604275892</v>
+        <f t="shared" si="36"/>
+        <v>4606.9551712681996</v>
       </c>
       <c r="BF10" s="2">
-        <f t="shared" si="29"/>
-        <v>5449.5809182404173</v>
-      </c>
-    </row>
-    <row r="11" spans="1:58" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF10:BJ10" si="37">+BE10*1.03</f>
+        <v>4745.1638264062458</v>
+      </c>
+      <c r="BG10" s="2">
+        <f t="shared" si="37"/>
+        <v>4887.5187411984334</v>
+      </c>
+      <c r="BH10" s="2">
+        <f t="shared" si="37"/>
+        <v>5034.1443034343865</v>
+      </c>
+      <c r="BI10" s="2">
+        <f t="shared" si="37"/>
+        <v>5185.1686325374185</v>
+      </c>
+      <c r="BJ10" s="2">
+        <f t="shared" si="37"/>
+        <v>5340.7236915135409</v>
+      </c>
+    </row>
+    <row r="11" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>31</v>
       </c>
@@ -2579,95 +2715,108 @@
         <v>1105</v>
       </c>
       <c r="X11" s="2">
-        <f t="shared" ref="X11" si="30">+T11</f>
-        <v>1091</v>
+        <v>1158</v>
       </c>
       <c r="Y11" s="2">
-        <f t="shared" si="26"/>
-        <v>1111</v>
+        <v>1176</v>
       </c>
       <c r="Z11" s="2">
-        <f t="shared" si="27"/>
-        <v>1129</v>
-      </c>
-      <c r="AN11" s="2">
+        <f>3029+1448-Y11-X11-W11</f>
+        <v>1038</v>
+      </c>
+      <c r="AA11" s="2">
+        <v>1064</v>
+      </c>
+      <c r="AB11" s="2">
+        <f>+X11</f>
+        <v>1158</v>
+      </c>
+      <c r="AC11" s="2">
+        <f t="shared" si="34"/>
+        <v>1176</v>
+      </c>
+      <c r="AD11" s="2">
+        <f t="shared" si="35"/>
+        <v>1038</v>
+      </c>
+      <c r="AR11" s="2">
         <f>1782+1254</f>
         <v>3036</v>
       </c>
-      <c r="AO11" s="2">
+      <c r="AS11" s="2">
         <f>1900+1232</f>
         <v>3132</v>
       </c>
-      <c r="AP11" s="2">
+      <c r="AT11" s="2">
         <f>1231+2017</f>
         <v>3248</v>
       </c>
-      <c r="AQ11" s="2">
+      <c r="AU11" s="2">
         <f>1292+2228</f>
         <v>3520</v>
       </c>
-      <c r="AR11" s="2">
-        <f t="shared" si="9"/>
+      <c r="AV11" s="2">
+        <f t="shared" si="13"/>
         <v>3996</v>
       </c>
-      <c r="AS11" s="2">
-        <f t="shared" si="10"/>
+      <c r="AW11" s="2">
+        <f t="shared" si="14"/>
         <v>3978</v>
       </c>
-      <c r="AT11" s="2">
-        <f t="shared" si="6"/>
+      <c r="AX11" s="2">
+        <f t="shared" si="7"/>
         <v>4220</v>
       </c>
-      <c r="AU11" s="2">
-        <f t="shared" si="14"/>
+      <c r="AY11" s="2">
+        <f t="shared" si="18"/>
         <v>4390.3999999999996</v>
       </c>
-      <c r="AV11" s="2">
-        <f t="shared" si="11"/>
-        <v>4436</v>
-      </c>
-      <c r="AW11" s="2">
-        <f t="shared" ref="AW11:BA11" si="31">+AV11*1.03</f>
-        <v>4569.08</v>
-      </c>
-      <c r="AX11" s="2">
-        <f t="shared" si="31"/>
-        <v>4706.1523999999999</v>
-      </c>
-      <c r="AY11" s="2">
-        <f t="shared" si="31"/>
-        <v>4847.3369720000001</v>
-      </c>
       <c r="AZ11" s="2">
-        <f t="shared" si="31"/>
-        <v>4992.7570811599999</v>
+        <f t="shared" si="15"/>
+        <v>4477</v>
       </c>
       <c r="BA11" s="2">
-        <f t="shared" si="31"/>
-        <v>5142.5397935948004</v>
+        <f t="shared" ref="BA11:BE11" si="38">+AZ11*1.03</f>
+        <v>4611.3100000000004</v>
       </c>
       <c r="BB11" s="2">
-        <f t="shared" ref="BB11:BF11" si="32">+BA11*1.03</f>
-        <v>5296.8159874026442</v>
+        <f t="shared" si="38"/>
+        <v>4749.6493000000009</v>
       </c>
       <c r="BC11" s="2">
-        <f t="shared" si="32"/>
-        <v>5455.7204670247238</v>
+        <f t="shared" si="38"/>
+        <v>4892.1387790000008</v>
       </c>
       <c r="BD11" s="2">
-        <f t="shared" si="32"/>
-        <v>5619.3920810354657</v>
+        <f t="shared" si="38"/>
+        <v>5038.9029423700013</v>
       </c>
       <c r="BE11" s="2">
-        <f t="shared" si="32"/>
-        <v>5787.9738434665296</v>
+        <f t="shared" si="38"/>
+        <v>5190.0700306411018</v>
       </c>
       <c r="BF11" s="2">
-        <f t="shared" si="32"/>
-        <v>5961.6130587705256</v>
-      </c>
-    </row>
-    <row r="12" spans="1:58" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF11:BJ11" si="39">+BE11*1.03</f>
+        <v>5345.7721315603349</v>
+      </c>
+      <c r="BG11" s="2">
+        <f t="shared" si="39"/>
+        <v>5506.1452955071454</v>
+      </c>
+      <c r="BH11" s="2">
+        <f t="shared" si="39"/>
+        <v>5671.32965437236</v>
+      </c>
+      <c r="BI11" s="2">
+        <f t="shared" si="39"/>
+        <v>5841.4695440035312</v>
+      </c>
+      <c r="BJ11" s="2">
+        <f t="shared" si="39"/>
+        <v>6016.7136303236375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>25</v>
       </c>
@@ -2727,91 +2876,104 @@
         <v>228</v>
       </c>
       <c r="X12" s="2">
-        <f>+T12</f>
+        <v>254</v>
+      </c>
+      <c r="Y12" s="2">
+        <v>254</v>
+      </c>
+      <c r="Z12" s="2">
+        <f>1010-Y12-X12-W12</f>
+        <v>274</v>
+      </c>
+      <c r="AA12" s="2">
         <v>243</v>
       </c>
-      <c r="Y12" s="2">
-        <f>+U12</f>
-        <v>236</v>
-      </c>
-      <c r="Z12" s="2">
-        <f>+V12</f>
-        <v>257</v>
-      </c>
-      <c r="AN12" s="2">
+      <c r="AB12" s="2">
+        <f t="shared" ref="AB12:AB18" si="40">+X12*1.05</f>
+        <v>266.7</v>
+      </c>
+      <c r="AC12" s="2">
+        <f t="shared" ref="AC12:AC18" si="41">+Y12*1.05</f>
+        <v>266.7</v>
+      </c>
+      <c r="AD12" s="2">
+        <f t="shared" ref="AD12:AD18" si="42">+Z12*1.05</f>
+        <v>287.7</v>
+      </c>
+      <c r="AR12" s="2">
         <v>808</v>
       </c>
-      <c r="AO12" s="2">
+      <c r="AS12" s="2">
         <v>864</v>
       </c>
-      <c r="AP12" s="2">
+      <c r="AT12" s="2">
         <v>831</v>
       </c>
-      <c r="AQ12" s="2">
+      <c r="AU12" s="2">
         <v>702</v>
       </c>
-      <c r="AR12" s="2">
-        <f t="shared" si="9"/>
+      <c r="AV12" s="2">
+        <f t="shared" si="13"/>
         <v>781</v>
       </c>
-      <c r="AS12" s="2">
-        <f t="shared" si="10"/>
+      <c r="AW12" s="2">
+        <f t="shared" si="14"/>
         <v>770</v>
       </c>
-      <c r="AT12" s="2">
-        <f t="shared" si="6"/>
+      <c r="AX12" s="2">
+        <f t="shared" si="7"/>
         <v>890</v>
       </c>
-      <c r="AU12" s="2">
-        <f t="shared" si="14"/>
+      <c r="AY12" s="2">
+        <f t="shared" si="18"/>
         <v>962</v>
       </c>
-      <c r="AV12" s="2">
-        <f t="shared" si="11"/>
-        <v>964</v>
-      </c>
-      <c r="AW12" s="2">
-        <f t="shared" ref="AW12:BA12" si="33">+AV12*1.03</f>
-        <v>992.92000000000007</v>
-      </c>
-      <c r="AX12" s="2">
-        <f t="shared" si="33"/>
-        <v>1022.7076000000001</v>
-      </c>
-      <c r="AY12" s="2">
-        <f t="shared" si="33"/>
-        <v>1053.3888280000001</v>
-      </c>
       <c r="AZ12" s="2">
-        <f t="shared" si="33"/>
-        <v>1084.9904928400001</v>
+        <f t="shared" si="15"/>
+        <v>1010</v>
       </c>
       <c r="BA12" s="2">
-        <f t="shared" si="33"/>
-        <v>1117.5402076252001</v>
+        <f t="shared" ref="BA12:BE12" si="43">+AZ12*1.03</f>
+        <v>1040.3</v>
       </c>
       <c r="BB12" s="2">
-        <f t="shared" ref="BB12:BF12" si="34">+BA12*1.03</f>
-        <v>1151.0664138539562</v>
+        <f t="shared" si="43"/>
+        <v>1071.509</v>
       </c>
       <c r="BC12" s="2">
-        <f t="shared" si="34"/>
-        <v>1185.598406269575</v>
+        <f t="shared" si="43"/>
+        <v>1103.65427</v>
       </c>
       <c r="BD12" s="2">
-        <f t="shared" si="34"/>
-        <v>1221.1663584576622</v>
+        <f t="shared" si="43"/>
+        <v>1136.7638981</v>
       </c>
       <c r="BE12" s="2">
-        <f t="shared" si="34"/>
-        <v>1257.8013492113921</v>
+        <f t="shared" si="43"/>
+        <v>1170.8668150430001</v>
       </c>
       <c r="BF12" s="2">
-        <f t="shared" si="34"/>
-        <v>1295.5353896877339</v>
-      </c>
-    </row>
-    <row r="13" spans="1:58" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF12:BJ12" si="44">+BE12*1.03</f>
+        <v>1205.9928194942902</v>
+      </c>
+      <c r="BG12" s="2">
+        <f t="shared" si="44"/>
+        <v>1242.1726040791189</v>
+      </c>
+      <c r="BH12" s="2">
+        <f t="shared" si="44"/>
+        <v>1279.4377822014924</v>
+      </c>
+      <c r="BI12" s="2">
+        <f t="shared" si="44"/>
+        <v>1317.8209156675373</v>
+      </c>
+      <c r="BJ12" s="2">
+        <f t="shared" si="44"/>
+        <v>1357.3555431375635</v>
+      </c>
+    </row>
+    <row r="13" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>28</v>
       </c>
@@ -2871,91 +3033,104 @@
         <v>339</v>
       </c>
       <c r="X13" s="2">
-        <f>+T13*1.1</f>
-        <v>353.1</v>
+        <v>368</v>
       </c>
       <c r="Y13" s="2">
-        <f>+U13*1.1</f>
-        <v>354.20000000000005</v>
+        <v>366</v>
       </c>
       <c r="Z13" s="2">
-        <f>+V13*1.1</f>
-        <v>364.1</v>
-      </c>
-      <c r="AN13" s="2">
+        <f>1448-Y13-X13-W13</f>
+        <v>375</v>
+      </c>
+      <c r="AA13" s="2">
+        <v>389</v>
+      </c>
+      <c r="AB13" s="2">
+        <f t="shared" si="40"/>
+        <v>386.40000000000003</v>
+      </c>
+      <c r="AC13" s="2">
+        <f t="shared" si="41"/>
+        <v>384.3</v>
+      </c>
+      <c r="AD13" s="2">
+        <f t="shared" si="42"/>
+        <v>393.75</v>
+      </c>
+      <c r="AR13" s="2">
         <v>643</v>
       </c>
-      <c r="AO13" s="2">
+      <c r="AS13" s="2">
         <v>646</v>
       </c>
-      <c r="AP13" s="2">
+      <c r="AT13" s="2">
         <v>769</v>
       </c>
-      <c r="AQ13" s="2">
+      <c r="AU13" s="2">
         <v>740</v>
       </c>
-      <c r="AR13" s="2">
-        <f t="shared" si="9"/>
+      <c r="AV13" s="2">
+        <f t="shared" si="13"/>
         <v>889</v>
       </c>
-      <c r="AS13" s="2">
-        <f t="shared" si="10"/>
+      <c r="AW13" s="2">
+        <f t="shared" si="14"/>
         <v>920</v>
       </c>
-      <c r="AT13" s="2">
-        <f t="shared" si="6"/>
+      <c r="AX13" s="2">
+        <f t="shared" si="7"/>
         <v>1161</v>
       </c>
-      <c r="AU13" s="2">
-        <f t="shared" si="14"/>
+      <c r="AY13" s="2">
+        <f t="shared" si="18"/>
         <v>1279</v>
       </c>
-      <c r="AV13" s="2">
-        <f t="shared" si="11"/>
-        <v>1410.4</v>
-      </c>
-      <c r="AW13" s="2">
-        <f t="shared" ref="AW13:BA13" si="35">+AV13*1.03</f>
-        <v>1452.7120000000002</v>
-      </c>
-      <c r="AX13" s="2">
-        <f t="shared" si="35"/>
-        <v>1496.2933600000003</v>
-      </c>
-      <c r="AY13" s="2">
-        <f t="shared" si="35"/>
-        <v>1541.1821608000005</v>
-      </c>
       <c r="AZ13" s="2">
-        <f t="shared" si="35"/>
-        <v>1587.4176256240005</v>
+        <f t="shared" si="15"/>
+        <v>1448</v>
       </c>
       <c r="BA13" s="2">
-        <f t="shared" si="35"/>
-        <v>1635.0401543927205</v>
+        <f t="shared" ref="BA13:BE13" si="45">+AZ13*1.03</f>
+        <v>1491.44</v>
       </c>
       <c r="BB13" s="2">
-        <f t="shared" ref="BB13:BF13" si="36">+BA13*1.03</f>
-        <v>1684.0913590245023</v>
+        <f t="shared" si="45"/>
+        <v>1536.1832000000002</v>
       </c>
       <c r="BC13" s="2">
-        <f t="shared" si="36"/>
-        <v>1734.6140997952373</v>
+        <f t="shared" si="45"/>
+        <v>1582.2686960000003</v>
       </c>
       <c r="BD13" s="2">
-        <f t="shared" si="36"/>
-        <v>1786.6525227890945</v>
+        <f t="shared" si="45"/>
+        <v>1629.7367568800003</v>
       </c>
       <c r="BE13" s="2">
-        <f t="shared" si="36"/>
-        <v>1840.2520984727673</v>
+        <f t="shared" si="45"/>
+        <v>1678.6288595864003</v>
       </c>
       <c r="BF13" s="2">
-        <f t="shared" si="36"/>
-        <v>1895.4596614269503</v>
-      </c>
-    </row>
-    <row r="14" spans="1:58" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF13:BJ13" si="46">+BE13*1.03</f>
+        <v>1728.9877253739924</v>
+      </c>
+      <c r="BG13" s="2">
+        <f t="shared" si="46"/>
+        <v>1780.8573571352122</v>
+      </c>
+      <c r="BH13" s="2">
+        <f t="shared" si="46"/>
+        <v>1834.2830778492687</v>
+      </c>
+      <c r="BI13" s="2">
+        <f t="shared" si="46"/>
+        <v>1889.3115701847469</v>
+      </c>
+      <c r="BJ13" s="2">
+        <f t="shared" si="46"/>
+        <v>1945.9909172902894</v>
+      </c>
+    </row>
+    <row r="14" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>26</v>
       </c>
@@ -3015,91 +3190,104 @@
         <v>577</v>
       </c>
       <c r="X14" s="2">
-        <f>+T14*1.2</f>
-        <v>676.8</v>
+        <v>636</v>
       </c>
       <c r="Y14" s="2">
-        <f>+U14*1.2</f>
-        <v>669.6</v>
+        <v>635</v>
       </c>
       <c r="Z14" s="2">
-        <f>+V14*1.2</f>
-        <v>730.8</v>
-      </c>
-      <c r="AN14" s="2">
+        <f>2523-Y14-X14-W14</f>
+        <v>675</v>
+      </c>
+      <c r="AA14" s="2">
+        <v>578</v>
+      </c>
+      <c r="AB14" s="2">
+        <f t="shared" si="40"/>
+        <v>667.80000000000007</v>
+      </c>
+      <c r="AC14" s="2">
+        <f t="shared" si="41"/>
+        <v>666.75</v>
+      </c>
+      <c r="AD14" s="2">
+        <f t="shared" si="42"/>
+        <v>708.75</v>
+      </c>
+      <c r="AR14" s="2">
         <v>1083</v>
       </c>
-      <c r="AO14" s="2">
+      <c r="AS14" s="2">
         <v>1239</v>
       </c>
-      <c r="AP14" s="2">
+      <c r="AT14" s="2">
         <v>1400</v>
       </c>
-      <c r="AQ14" s="2">
+      <c r="AU14" s="2">
         <v>1247</v>
       </c>
-      <c r="AR14" s="2">
-        <f t="shared" si="9"/>
+      <c r="AV14" s="2">
+        <f t="shared" si="13"/>
         <v>1610</v>
       </c>
-      <c r="AS14" s="2">
-        <f t="shared" si="10"/>
+      <c r="AW14" s="2">
+        <f t="shared" si="14"/>
         <v>1712</v>
       </c>
-      <c r="AT14" s="2">
-        <f t="shared" si="6"/>
+      <c r="AX14" s="2">
+        <f t="shared" si="7"/>
         <v>1944</v>
       </c>
-      <c r="AU14" s="2">
-        <f t="shared" si="14"/>
+      <c r="AY14" s="2">
+        <f t="shared" si="18"/>
         <v>2246</v>
       </c>
-      <c r="AV14" s="2">
-        <f t="shared" si="11"/>
-        <v>2654.2</v>
-      </c>
-      <c r="AW14" s="2">
-        <f t="shared" ref="AW14:BA14" si="37">+AV14*1.03</f>
-        <v>2733.826</v>
-      </c>
-      <c r="AX14" s="2">
-        <f t="shared" si="37"/>
-        <v>2815.84078</v>
-      </c>
-      <c r="AY14" s="2">
-        <f t="shared" si="37"/>
-        <v>2900.3160034000002</v>
-      </c>
       <c r="AZ14" s="2">
-        <f t="shared" si="37"/>
-        <v>2987.3254835020002</v>
+        <f t="shared" si="15"/>
+        <v>2523</v>
       </c>
       <c r="BA14" s="2">
-        <f t="shared" si="37"/>
-        <v>3076.9452480070604</v>
+        <f t="shared" ref="BA14:BE14" si="47">+AZ14*1.03</f>
+        <v>2598.69</v>
       </c>
       <c r="BB14" s="2">
-        <f t="shared" ref="BB14:BF14" si="38">+BA14*1.03</f>
-        <v>3169.2536054472721</v>
+        <f t="shared" si="47"/>
+        <v>2676.6507000000001</v>
       </c>
       <c r="BC14" s="2">
-        <f t="shared" si="38"/>
-        <v>3264.3312136106902</v>
+        <f t="shared" si="47"/>
+        <v>2756.9502210000001</v>
       </c>
       <c r="BD14" s="2">
-        <f t="shared" si="38"/>
-        <v>3362.261150019011</v>
+        <f t="shared" si="47"/>
+        <v>2839.6587276300002</v>
       </c>
       <c r="BE14" s="2">
-        <f t="shared" si="38"/>
-        <v>3463.1289845195815</v>
+        <f t="shared" si="47"/>
+        <v>2924.8484894589001</v>
       </c>
       <c r="BF14" s="2">
-        <f t="shared" si="38"/>
-        <v>3567.0228540551689</v>
-      </c>
-    </row>
-    <row r="15" spans="1:58" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF14:BJ14" si="48">+BE14*1.03</f>
+        <v>3012.5939441426672</v>
+      </c>
+      <c r="BG14" s="2">
+        <f t="shared" si="48"/>
+        <v>3102.9717624669474</v>
+      </c>
+      <c r="BH14" s="2">
+        <f t="shared" si="48"/>
+        <v>3196.0609153409559</v>
+      </c>
+      <c r="BI14" s="2">
+        <f t="shared" si="48"/>
+        <v>3291.9427428011845</v>
+      </c>
+      <c r="BJ14" s="2">
+        <f t="shared" si="48"/>
+        <v>3390.70102508522</v>
+      </c>
+    </row>
+    <row r="15" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
@@ -3159,91 +3347,104 @@
         <v>629</v>
       </c>
       <c r="X15" s="2">
-        <f>+T15*1.03</f>
-        <v>645.81000000000006</v>
+        <v>700</v>
       </c>
       <c r="Y15" s="2">
-        <f>+U15*1.03</f>
-        <v>628.30000000000007</v>
+        <v>705</v>
       </c>
       <c r="Z15" s="2">
-        <f>+V15*1.03</f>
-        <v>662.29</v>
-      </c>
-      <c r="AN15" s="2">
+        <f>2764-Y15-X15-W15</f>
+        <v>730</v>
+      </c>
+      <c r="AA15" s="2">
+        <v>788</v>
+      </c>
+      <c r="AB15" s="2">
+        <f t="shared" si="40"/>
+        <v>735</v>
+      </c>
+      <c r="AC15" s="2">
+        <f t="shared" si="41"/>
+        <v>740.25</v>
+      </c>
+      <c r="AD15" s="2">
+        <f t="shared" si="42"/>
+        <v>766.5</v>
+      </c>
+      <c r="AR15" s="2">
         <v>1382</v>
       </c>
-      <c r="AO15" s="2">
+      <c r="AS15" s="2">
         <v>1561</v>
       </c>
-      <c r="AP15" s="2">
+      <c r="AT15" s="2">
         <v>1721</v>
       </c>
-      <c r="AQ15" s="2">
+      <c r="AU15" s="2">
         <v>1578</v>
       </c>
-      <c r="AR15" s="2">
-        <f t="shared" si="9"/>
+      <c r="AV15" s="2">
+        <f t="shared" si="13"/>
         <v>1907</v>
       </c>
-      <c r="AS15" s="2">
-        <f t="shared" si="10"/>
+      <c r="AW15" s="2">
+        <f t="shared" si="14"/>
         <v>1927</v>
       </c>
-      <c r="AT15" s="2">
-        <f t="shared" si="6"/>
+      <c r="AX15" s="2">
+        <f t="shared" si="7"/>
         <v>2195</v>
       </c>
-      <c r="AU15" s="2">
-        <f t="shared" si="14"/>
+      <c r="AY15" s="2">
+        <f t="shared" si="18"/>
         <v>2467</v>
       </c>
-      <c r="AV15" s="2">
-        <f t="shared" si="11"/>
-        <v>2565.4</v>
-      </c>
-      <c r="AW15" s="2">
-        <f t="shared" ref="AW15:BA15" si="39">+AV15*1.03</f>
-        <v>2642.3620000000001</v>
-      </c>
-      <c r="AX15" s="2">
-        <f t="shared" si="39"/>
-        <v>2721.6328600000002</v>
-      </c>
-      <c r="AY15" s="2">
-        <f t="shared" si="39"/>
-        <v>2803.2818458000002</v>
-      </c>
       <c r="AZ15" s="2">
-        <f t="shared" si="39"/>
-        <v>2887.3803011740001</v>
+        <f t="shared" si="15"/>
+        <v>2764</v>
       </c>
       <c r="BA15" s="2">
-        <f t="shared" si="39"/>
-        <v>2974.0017102092202</v>
+        <f t="shared" ref="BA15:BE15" si="49">+AZ15*1.03</f>
+        <v>2846.92</v>
       </c>
       <c r="BB15" s="2">
-        <f t="shared" ref="BB15:BF15" si="40">+BA15*1.03</f>
-        <v>3063.2217615154968</v>
+        <f t="shared" si="49"/>
+        <v>2932.3276000000001</v>
       </c>
       <c r="BC15" s="2">
-        <f t="shared" si="40"/>
-        <v>3155.1184143609617</v>
+        <f t="shared" si="49"/>
+        <v>3020.2974280000003</v>
       </c>
       <c r="BD15" s="2">
-        <f t="shared" si="40"/>
-        <v>3249.7719667917904</v>
+        <f t="shared" si="49"/>
+        <v>3110.9063508400004</v>
       </c>
       <c r="BE15" s="2">
-        <f t="shared" si="40"/>
-        <v>3347.265125795544</v>
+        <f t="shared" si="49"/>
+        <v>3204.2335413652004</v>
       </c>
       <c r="BF15" s="2">
-        <f t="shared" si="40"/>
-        <v>3447.6830795694104</v>
-      </c>
-    </row>
-    <row r="16" spans="1:58" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF15:BJ15" si="50">+BE15*1.03</f>
+        <v>3300.3605476061566</v>
+      </c>
+      <c r="BG15" s="2">
+        <f t="shared" si="50"/>
+        <v>3399.3713640343412</v>
+      </c>
+      <c r="BH15" s="2">
+        <f t="shared" si="50"/>
+        <v>3501.3525049553714</v>
+      </c>
+      <c r="BI15" s="2">
+        <f t="shared" si="50"/>
+        <v>3606.3930801040328</v>
+      </c>
+      <c r="BJ15" s="2">
+        <f t="shared" si="50"/>
+        <v>3714.5848725071537</v>
+      </c>
+    </row>
+    <row r="16" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>30</v>
       </c>
@@ -3303,91 +3504,104 @@
         <v>585</v>
       </c>
       <c r="X16" s="2">
-        <f>+T16*1.05</f>
-        <v>637.35</v>
+        <v>673</v>
       </c>
       <c r="Y16" s="2">
-        <f>+U16*1.05</f>
-        <v>626.85</v>
+        <v>686</v>
       </c>
       <c r="Z16" s="2">
-        <f>+V16*1.05</f>
-        <v>655.20000000000005</v>
-      </c>
-      <c r="AN16" s="2">
+        <f>2649-Y16-X16-W16</f>
+        <v>705</v>
+      </c>
+      <c r="AA16" s="2">
+        <v>684</v>
+      </c>
+      <c r="AB16" s="2">
+        <f t="shared" si="40"/>
+        <v>706.65</v>
+      </c>
+      <c r="AC16" s="2">
+        <f t="shared" si="41"/>
+        <v>720.30000000000007</v>
+      </c>
+      <c r="AD16" s="2">
+        <f t="shared" si="42"/>
+        <v>740.25</v>
+      </c>
+      <c r="AR16" s="2">
         <v>2103</v>
       </c>
-      <c r="AO16" s="2">
+      <c r="AS16" s="2">
         <v>2198</v>
       </c>
-      <c r="AP16" s="2">
+      <c r="AT16" s="2">
         <v>2144</v>
       </c>
-      <c r="AQ16" s="2">
+      <c r="AU16" s="2">
         <v>1914</v>
       </c>
-      <c r="AR16" s="2">
-        <f t="shared" si="9"/>
+      <c r="AV16" s="2">
+        <f t="shared" si="13"/>
         <v>2198</v>
       </c>
-      <c r="AS16" s="2">
-        <f t="shared" si="10"/>
+      <c r="AW16" s="2">
+        <f t="shared" si="14"/>
         <v>2119</v>
       </c>
-      <c r="AT16" s="2">
-        <f t="shared" si="6"/>
+      <c r="AX16" s="2">
+        <f t="shared" si="7"/>
         <v>2255</v>
       </c>
-      <c r="AU16" s="2">
-        <f t="shared" si="14"/>
+      <c r="AY16" s="2">
+        <f t="shared" si="18"/>
         <v>2390</v>
       </c>
-      <c r="AV16" s="2">
-        <f t="shared" si="11"/>
-        <v>2504.3999999999996</v>
-      </c>
-      <c r="AW16" s="2">
-        <f t="shared" ref="AW16:BA16" si="41">+AV16*1.03</f>
-        <v>2579.5319999999997</v>
-      </c>
-      <c r="AX16" s="2">
-        <f t="shared" si="41"/>
-        <v>2656.9179599999998</v>
-      </c>
-      <c r="AY16" s="2">
-        <f t="shared" si="41"/>
-        <v>2736.6254987999996</v>
-      </c>
       <c r="AZ16" s="2">
-        <f t="shared" si="41"/>
-        <v>2818.7242637639997</v>
+        <f t="shared" si="15"/>
+        <v>2649</v>
       </c>
       <c r="BA16" s="2">
-        <f t="shared" si="41"/>
-        <v>2903.2859916769198</v>
+        <f t="shared" ref="BA16:BE16" si="51">+AZ16*1.03</f>
+        <v>2728.4700000000003</v>
       </c>
       <c r="BB16" s="2">
-        <f t="shared" ref="BB16:BF16" si="42">+BA16*1.03</f>
-        <v>2990.3845714272275</v>
+        <f t="shared" si="51"/>
+        <v>2810.3241000000003</v>
       </c>
       <c r="BC16" s="2">
-        <f t="shared" si="42"/>
-        <v>3080.0961085700442</v>
+        <f t="shared" si="51"/>
+        <v>2894.6338230000006</v>
       </c>
       <c r="BD16" s="2">
-        <f t="shared" si="42"/>
-        <v>3172.4989918271458</v>
+        <f t="shared" si="51"/>
+        <v>2981.4728376900007</v>
       </c>
       <c r="BE16" s="2">
-        <f t="shared" si="42"/>
-        <v>3267.6739615819602</v>
+        <f t="shared" si="51"/>
+        <v>3070.9170228207008</v>
       </c>
       <c r="BF16" s="2">
-        <f t="shared" si="42"/>
-        <v>3365.704180429419</v>
-      </c>
-    </row>
-    <row r="17" spans="2:125" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF16:BJ16" si="52">+BE16*1.03</f>
+        <v>3163.0445335053219</v>
+      </c>
+      <c r="BG16" s="2">
+        <f t="shared" si="52"/>
+        <v>3257.9358695104816</v>
+      </c>
+      <c r="BH16" s="2">
+        <f t="shared" si="52"/>
+        <v>3355.6739455957959</v>
+      </c>
+      <c r="BI16" s="2">
+        <f t="shared" si="52"/>
+        <v>3456.3441639636699</v>
+      </c>
+      <c r="BJ16" s="2">
+        <f t="shared" si="52"/>
+        <v>3560.0344888825803</v>
+      </c>
+    </row>
+    <row r="17" spans="2:129" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>27</v>
       </c>
@@ -3447,91 +3661,104 @@
         <v>710</v>
       </c>
       <c r="X17" s="2">
-        <f>+T17*1.03</f>
-        <v>745.72</v>
+        <v>757</v>
       </c>
       <c r="Y17" s="2">
-        <f>+U17*1.03</f>
-        <v>719.97</v>
+        <v>745</v>
       </c>
       <c r="Z17" s="2">
-        <f>+V17*1.03</f>
-        <v>746.75</v>
-      </c>
-      <c r="AN17" s="2">
+        <f>2995-Y17-X17-W17</f>
+        <v>783</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>777</v>
+      </c>
+      <c r="AB17" s="2">
+        <f t="shared" si="40"/>
+        <v>794.85</v>
+      </c>
+      <c r="AC17" s="2">
+        <f t="shared" si="41"/>
+        <v>782.25</v>
+      </c>
+      <c r="AD17" s="2">
+        <f t="shared" si="42"/>
+        <v>822.15000000000009</v>
+      </c>
+      <c r="AR17" s="2">
         <v>2892</v>
       </c>
-      <c r="AO17" s="2">
+      <c r="AS17" s="2">
         <v>2929</v>
       </c>
-      <c r="AP17" s="2">
+      <c r="AT17" s="2">
         <v>2850</v>
       </c>
-      <c r="AQ17" s="2">
+      <c r="AU17" s="2">
         <v>2339</v>
       </c>
-      <c r="AR17" s="2">
-        <f t="shared" si="9"/>
+      <c r="AV17" s="2">
+        <f t="shared" si="13"/>
         <v>2654</v>
       </c>
-      <c r="AS17" s="2">
-        <f t="shared" si="10"/>
+      <c r="AW17" s="2">
+        <f t="shared" si="14"/>
         <v>2483</v>
       </c>
-      <c r="AT17" s="2">
-        <f t="shared" si="6"/>
+      <c r="AX17" s="2">
+        <f t="shared" si="7"/>
         <v>2681</v>
       </c>
-      <c r="AU17" s="2">
-        <f t="shared" si="14"/>
+      <c r="AY17" s="2">
+        <f t="shared" si="18"/>
         <v>2837</v>
       </c>
-      <c r="AV17" s="2">
-        <f t="shared" si="11"/>
-        <v>2922.44</v>
-      </c>
-      <c r="AW17" s="2">
-        <f>+AV17*1.07</f>
-        <v>3127.0108</v>
-      </c>
-      <c r="AX17" s="2">
-        <f>+AW17*1.07</f>
-        <v>3345.9015560000003</v>
-      </c>
-      <c r="AY17" s="2">
-        <f>+AX17*1.05</f>
-        <v>3513.1966338000002</v>
-      </c>
       <c r="AZ17" s="2">
-        <f t="shared" ref="AZ17:BA17" si="43">+AY17*1.03</f>
-        <v>3618.5925328140002</v>
+        <f t="shared" si="15"/>
+        <v>2995</v>
       </c>
       <c r="BA17" s="2">
-        <f t="shared" si="43"/>
-        <v>3727.1503087984202</v>
+        <f>+AZ17*1.07</f>
+        <v>3204.65</v>
       </c>
       <c r="BB17" s="2">
-        <f t="shared" ref="BB17:BF17" si="44">+BA17*1.03</f>
-        <v>3838.9648180623731</v>
+        <f>+BA17*1.07</f>
+        <v>3428.9755000000005</v>
       </c>
       <c r="BC17" s="2">
-        <f t="shared" si="44"/>
-        <v>3954.1337626042446</v>
+        <f>+BB17*1.05</f>
+        <v>3600.4242750000008</v>
       </c>
       <c r="BD17" s="2">
-        <f t="shared" si="44"/>
-        <v>4072.7577754823719</v>
+        <f t="shared" ref="BD17:BE17" si="53">+BC17*1.03</f>
+        <v>3708.437003250001</v>
       </c>
       <c r="BE17" s="2">
-        <f t="shared" si="44"/>
-        <v>4194.9405087468431</v>
+        <f t="shared" si="53"/>
+        <v>3819.6901133475012</v>
       </c>
       <c r="BF17" s="2">
-        <f t="shared" si="44"/>
-        <v>4320.7887240092487</v>
-      </c>
-    </row>
-    <row r="18" spans="2:125" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF17:BJ17" si="54">+BE17*1.03</f>
+        <v>3934.2808167479266</v>
+      </c>
+      <c r="BG17" s="2">
+        <f t="shared" si="54"/>
+        <v>4052.3092412503643</v>
+      </c>
+      <c r="BH17" s="2">
+        <f t="shared" si="54"/>
+        <v>4173.8785184878752</v>
+      </c>
+      <c r="BI17" s="2">
+        <f t="shared" si="54"/>
+        <v>4299.0948740425119</v>
+      </c>
+      <c r="BJ17" s="2">
+        <f t="shared" si="54"/>
+        <v>4428.0677202637871</v>
+      </c>
+    </row>
+    <row r="18" spans="2:129" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>20</v>
       </c>
@@ -3591,88 +3818,101 @@
         <v>1827</v>
       </c>
       <c r="X18" s="2">
-        <f>+T18*1.15</f>
-        <v>1895.1999999999998</v>
+        <v>1981</v>
       </c>
       <c r="Y18" s="2">
-        <f>+U18*1.15</f>
-        <v>1983.7499999999998</v>
+        <v>2057</v>
       </c>
       <c r="Z18" s="2">
-        <f>+V18*1.15</f>
-        <v>2142.4499999999998</v>
-      </c>
-      <c r="AO18" s="2">
+        <f>7998-Y18-X18-W18</f>
+        <v>2133</v>
+      </c>
+      <c r="AA18" s="2">
+        <v>2080</v>
+      </c>
+      <c r="AB18" s="2">
+        <f>+X18*1.05</f>
+        <v>2080.0500000000002</v>
+      </c>
+      <c r="AC18" s="2">
+        <f t="shared" si="41"/>
+        <v>2159.85</v>
+      </c>
+      <c r="AD18" s="2">
+        <f t="shared" si="42"/>
+        <v>2239.65</v>
+      </c>
+      <c r="AS18" s="2">
         <v>1933</v>
       </c>
-      <c r="AP18" s="2">
+      <c r="AT18" s="2">
         <v>2524</v>
       </c>
-      <c r="AQ18" s="2">
+      <c r="AU18" s="2">
         <v>3267</v>
       </c>
-      <c r="AR18" s="2">
-        <f t="shared" si="9"/>
+      <c r="AV18" s="2">
+        <f t="shared" si="13"/>
         <v>4328</v>
       </c>
-      <c r="AS18" s="2">
-        <f t="shared" si="10"/>
+      <c r="AW18" s="2">
+        <f t="shared" si="14"/>
         <v>4756</v>
       </c>
-      <c r="AT18" s="2">
-        <f t="shared" si="6"/>
+      <c r="AX18" s="2">
+        <f t="shared" si="7"/>
         <v>5761</v>
       </c>
-      <c r="AU18" s="2">
-        <f t="shared" si="14"/>
+      <c r="AY18" s="2">
+        <f t="shared" si="18"/>
         <v>6805</v>
       </c>
-      <c r="AV18" s="2">
-        <f t="shared" si="11"/>
-        <v>7848.4</v>
-      </c>
-      <c r="AW18" s="2">
-        <f>+AV18*1.1</f>
-        <v>8633.24</v>
-      </c>
-      <c r="AX18" s="2">
-        <f>+AW18*1.1</f>
-        <v>9496.5640000000003</v>
-      </c>
-      <c r="AY18" s="2">
-        <f>+AX18*1.1</f>
-        <v>10446.220400000002</v>
-      </c>
       <c r="AZ18" s="2">
-        <f>+AY18*1.05</f>
-        <v>10968.531420000003</v>
+        <f t="shared" si="15"/>
+        <v>7998</v>
       </c>
       <c r="BA18" s="2">
-        <f>+AZ18*1.05</f>
-        <v>11516.957991000003</v>
+        <f>+AZ18*1.1</f>
+        <v>8797.8000000000011</v>
       </c>
       <c r="BB18" s="2">
-        <f t="shared" ref="BB18:BF18" si="45">+BA18*1.05</f>
-        <v>12092.805890550004</v>
+        <f>+BA18*1.1</f>
+        <v>9677.5800000000017</v>
       </c>
       <c r="BC18" s="2">
-        <f t="shared" si="45"/>
-        <v>12697.446185077504</v>
+        <f>+BB18*1.1</f>
+        <v>10645.338000000003</v>
       </c>
       <c r="BD18" s="2">
-        <f t="shared" si="45"/>
-        <v>13332.318494331381</v>
+        <f>+BC18*1.05</f>
+        <v>11177.604900000004</v>
       </c>
       <c r="BE18" s="2">
-        <f t="shared" si="45"/>
-        <v>13998.93441904795</v>
+        <f>+BD18*1.05</f>
+        <v>11736.485145000004</v>
       </c>
       <c r="BF18" s="2">
-        <f t="shared" si="45"/>
-        <v>14698.881140000347</v>
-      </c>
-    </row>
-    <row r="19" spans="2:125" s="5" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF18:BJ18" si="55">+BE18*1.05</f>
+        <v>12323.309402250004</v>
+      </c>
+      <c r="BG18" s="2">
+        <f t="shared" si="55"/>
+        <v>12939.474872362505</v>
+      </c>
+      <c r="BH18" s="2">
+        <f t="shared" si="55"/>
+        <v>13586.448615980631</v>
+      </c>
+      <c r="BI18" s="2">
+        <f t="shared" si="55"/>
+        <v>14265.771046779662</v>
+      </c>
+      <c r="BJ18" s="2">
+        <f t="shared" si="55"/>
+        <v>14979.059599118646</v>
+      </c>
+    </row>
+    <row r="19" spans="2:129" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
@@ -3681,59 +3921,59 @@
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6">
-        <f t="shared" ref="G19:J19" si="46">SUM(G4:G18)</f>
+        <f t="shared" ref="G19:J19" si="56">SUM(G3:G18)</f>
         <v>10456</v>
       </c>
       <c r="H19" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="56"/>
         <v>10223</v>
       </c>
       <c r="I19" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="56"/>
         <v>10928</v>
       </c>
       <c r="J19" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="56"/>
         <v>11468</v>
       </c>
       <c r="K19" s="6">
-        <f>SUM(K4:K18)</f>
+        <f>SUM(K3:K18)</f>
         <v>11895</v>
       </c>
       <c r="L19" s="6">
-        <f>SUM(L4:L18)</f>
+        <f>SUM(L3:L18)</f>
         <v>11257</v>
       </c>
       <c r="M19" s="6">
-        <f t="shared" ref="M19:T19" si="47">SUM(M5:M18)</f>
+        <f t="shared" ref="M19:T19" si="57">SUM(M4:M18)</f>
         <v>10407</v>
       </c>
       <c r="N19" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="57"/>
         <v>10088</v>
       </c>
       <c r="O19" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="57"/>
         <v>9744</v>
       </c>
       <c r="P19" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="57"/>
         <v>9975</v>
       </c>
       <c r="Q19" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="57"/>
         <v>10139</v>
       </c>
       <c r="R19" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="57"/>
         <v>10237</v>
       </c>
       <c r="S19" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="57"/>
         <v>9963.8000000000011</v>
       </c>
       <c r="T19" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="57"/>
         <v>10373</v>
       </c>
       <c r="U19" s="6">
@@ -3741,110 +3981,126 @@
         <v>10240.39</v>
       </c>
       <c r="V19" s="6">
-        <f>SUM(V4:V18)</f>
+        <f>SUM(V3:V18)</f>
         <v>10974</v>
       </c>
       <c r="W19" s="6">
-        <f>SUM(W4:W18)</f>
+        <f>SUM(W3:W18)</f>
         <v>10358</v>
       </c>
       <c r="X19" s="6">
-        <f t="shared" ref="X19:Z19" si="48">SUM(X4:X18)</f>
-        <v>10835.98</v>
+        <f t="shared" ref="X19:AD19" si="58">SUM(X3:X18)</f>
+        <v>11142</v>
       </c>
       <c r="Y19" s="6">
-        <f t="shared" si="48"/>
-        <v>11102.67</v>
+        <f t="shared" si="58"/>
+        <v>11369</v>
       </c>
       <c r="Z19" s="6">
-        <f t="shared" si="48"/>
-        <v>11480.59</v>
-      </c>
-      <c r="AK19" s="5">
+        <f t="shared" si="58"/>
+        <v>11459</v>
+      </c>
+      <c r="AA19" s="6">
+        <f t="shared" si="58"/>
+        <v>11164</v>
+      </c>
+      <c r="AB19" s="6">
+        <f t="shared" si="58"/>
+        <v>11235.45</v>
+      </c>
+      <c r="AC19" s="6">
+        <f t="shared" si="58"/>
+        <v>11448.4</v>
+      </c>
+      <c r="AD19" s="6">
+        <f t="shared" si="58"/>
+        <v>11539.75</v>
+      </c>
+      <c r="AO19" s="5">
         <v>20247</v>
       </c>
-      <c r="AL19" s="5">
+      <c r="AP19" s="5">
         <v>20405</v>
       </c>
-      <c r="AM19" s="5">
+      <c r="AQ19" s="5">
         <v>20853</v>
       </c>
-      <c r="AN19" s="5">
+      <c r="AR19" s="5">
         <v>27390</v>
       </c>
-      <c r="AO19" s="5">
+      <c r="AS19" s="5">
         <v>30578</v>
       </c>
-      <c r="AP19" s="5">
-        <f t="shared" ref="AP19:AV19" si="49">SUM(AP4:AP18)</f>
+      <c r="AT19" s="5">
+        <f t="shared" ref="AT19:AZ19" si="59">SUM(AT3:AT18)</f>
         <v>31904</v>
       </c>
-      <c r="AQ19" s="5">
-        <f t="shared" si="49"/>
+      <c r="AU19" s="5">
+        <f t="shared" si="59"/>
         <v>34608</v>
       </c>
-      <c r="AR19" s="5">
-        <f t="shared" si="49"/>
+      <c r="AV19" s="5">
+        <f t="shared" si="59"/>
         <v>43075</v>
       </c>
-      <c r="AS19" s="5">
-        <f t="shared" si="49"/>
+      <c r="AW19" s="5">
+        <f t="shared" si="59"/>
         <v>43650</v>
       </c>
-      <c r="AT19" s="5">
-        <f t="shared" si="49"/>
+      <c r="AX19" s="5">
+        <f t="shared" si="59"/>
         <v>40095</v>
       </c>
-      <c r="AU19" s="5">
-        <f t="shared" si="49"/>
+      <c r="AY19" s="5">
+        <f t="shared" si="59"/>
         <v>41941.799999999996</v>
       </c>
-      <c r="AV19" s="5">
-        <f t="shared" si="49"/>
-        <v>43777.240000000005</v>
-      </c>
-      <c r="AW19" s="5">
-        <f t="shared" ref="AW19" si="50">SUM(AW4:AW18)</f>
-        <v>45756.842799999991</v>
-      </c>
-      <c r="AX19" s="5">
-        <f t="shared" ref="AX19" si="51">SUM(AX4:AX18)</f>
-        <v>47858.955316</v>
-      </c>
-      <c r="AY19" s="5">
-        <f t="shared" ref="AY19" si="52">SUM(AY4:AY18)</f>
-        <v>50026.401486599992</v>
-      </c>
       <c r="AZ19" s="5">
-        <f t="shared" ref="AZ19" si="53">SUM(AZ4:AZ18)</f>
-        <v>51736.117939198011</v>
+        <f t="shared" si="59"/>
+        <v>44328</v>
       </c>
       <c r="BA19" s="5">
-        <f t="shared" ref="BA19" si="54">SUM(BA4:BA18)</f>
-        <v>53507.572105773943</v>
+        <f t="shared" ref="BA19" si="60">SUM(BA3:BA18)</f>
+        <v>46337.500000000007</v>
       </c>
       <c r="BB19" s="5">
-        <f t="shared" ref="BB19" si="55">SUM(BB4:BB18)</f>
-        <v>55343.138428767168</v>
+        <f t="shared" ref="BB19" si="61">SUM(BB3:BB18)</f>
+        <v>48471.656999999999</v>
       </c>
       <c r="BC19" s="5">
-        <f t="shared" ref="BC19" si="56">SUM(BC4:BC18)</f>
-        <v>57245.288699441189</v>
+        <f t="shared" ref="BC19" si="62">SUM(BC3:BC18)</f>
+        <v>50671.81682</v>
       </c>
       <c r="BD19" s="5">
-        <f t="shared" ref="BD19" si="57">SUM(BD4:BD18)</f>
-        <v>59216.596284125975</v>
+        <f t="shared" ref="BD19" si="63">SUM(BD3:BD18)</f>
+        <v>52404.878084600008</v>
       </c>
       <c r="BE19" s="5">
-        <f t="shared" ref="BE19" si="58">SUM(BE4:BE18)</f>
-        <v>61259.740542536383</v>
+        <f t="shared" ref="BE19" si="64">SUM(BE3:BE18)</f>
+        <v>54200.576525138014</v>
       </c>
       <c r="BF19" s="5">
-        <f t="shared" ref="BF19" si="59">SUM(BF4:BF18)</f>
-        <v>63377.511447193428</v>
-      </c>
-    </row>
-    <row r="20" spans="2:125" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF19" si="65">SUM(BF3:BF18)</f>
+        <v>56061.323523792147</v>
+      </c>
+      <c r="BG19" s="5">
+        <f t="shared" ref="BG19" si="66">SUM(BG3:BG18)</f>
+        <v>57989.62941755091</v>
+      </c>
+      <c r="BH19" s="5">
+        <f t="shared" ref="BH19" si="67">SUM(BH3:BH18)</f>
+        <v>59988.107797524695</v>
+      </c>
+      <c r="BI19" s="5">
+        <f t="shared" ref="BI19" si="68">SUM(BI3:BI18)</f>
+        <v>62059.480003770055</v>
+      </c>
+      <c r="BJ19" s="5">
+        <f t="shared" ref="BJ19" si="69">SUM(BJ3:BJ18)</f>
+        <v>64206.579824818749</v>
+      </c>
+    </row>
+    <row r="20" spans="2:129" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>37</v>
       </c>
@@ -3874,31 +4130,31 @@
         <v>4629</v>
       </c>
       <c r="N20" s="4">
-        <f t="shared" ref="N20:T20" si="60">+N19-N21</f>
+        <f t="shared" ref="N20:T20" si="70">+N19-N21</f>
         <v>4474</v>
       </c>
       <c r="O20" s="2">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>4299</v>
       </c>
       <c r="P20" s="2">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>4449</v>
       </c>
       <c r="Q20" s="2">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>4555</v>
       </c>
       <c r="R20" s="2">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>4515</v>
       </c>
       <c r="S20" s="2">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>4416.8000000000011</v>
       </c>
       <c r="T20" s="2">
-        <f t="shared" si="60"/>
+        <f t="shared" si="70"/>
         <v>4564</v>
       </c>
       <c r="U20" s="2">
@@ -3911,94 +4167,107 @@
         <v>4468</v>
       </c>
       <c r="X20" s="2">
-        <f>+X19-X21</f>
-        <v>4659.4714000000004</v>
+        <v>4854</v>
       </c>
       <c r="Y20" s="2">
-        <f>+Y19-Y21</f>
-        <v>4774.1481000000003</v>
+        <v>5075</v>
       </c>
       <c r="Z20" s="2">
-        <f>+Z19-Z21</f>
-        <v>4936.6537000000008</v>
-      </c>
-      <c r="AM20" s="2">
+        <f>19319-Y20-X20-W20</f>
+        <v>4922</v>
+      </c>
+      <c r="AA20" s="2">
+        <v>4890</v>
+      </c>
+      <c r="AB20" s="2">
+        <f>+AB19-AB21</f>
+        <v>4831.2435000000005</v>
+      </c>
+      <c r="AC20" s="2">
+        <f>+AC19-AC21</f>
+        <v>4922.8120000000008</v>
+      </c>
+      <c r="AD20" s="2">
+        <f>+AD19-AD21</f>
+        <v>4962.0925000000007</v>
+      </c>
+      <c r="AQ20" s="2">
         <v>9094</v>
       </c>
-      <c r="AN20" s="2">
+      <c r="AR20" s="2">
         <v>12409</v>
       </c>
-      <c r="AO20" s="2">
+      <c r="AS20" s="2">
         <v>12706</v>
       </c>
-      <c r="AP20" s="2">
+      <c r="AT20" s="2">
         <v>13231</v>
       </c>
-      <c r="AQ20" s="2">
+      <c r="AU20" s="2">
         <v>15003</v>
       </c>
-      <c r="AR20" s="2">
-        <f t="shared" si="9"/>
+      <c r="AV20" s="2">
+        <f t="shared" si="13"/>
         <v>18537</v>
       </c>
-      <c r="AS20" s="2">
-        <f t="shared" si="10"/>
+      <c r="AW20" s="2">
+        <f t="shared" si="14"/>
         <v>19023</v>
       </c>
-      <c r="AT20" s="2">
+      <c r="AX20" s="2">
         <f>SUM(O20:R20)</f>
         <v>17818</v>
       </c>
-      <c r="AU20" s="2">
-        <f t="shared" si="14"/>
+      <c r="AY20" s="2">
+        <f t="shared" si="18"/>
         <v>18620.800000000003</v>
       </c>
-      <c r="AV20" s="2">
-        <f t="shared" si="11"/>
-        <v>18838.273200000003</v>
-      </c>
-      <c r="AW20" s="2">
-        <f>+AW19-AW21</f>
-        <v>19675.442403999998</v>
-      </c>
-      <c r="AX20" s="2">
-        <f>+AX19-AX21</f>
-        <v>20579.350785880004</v>
-      </c>
-      <c r="AY20" s="2">
-        <f>+AY19-AY21</f>
-        <v>21511.352639238001</v>
-      </c>
       <c r="AZ20" s="2">
-        <f>+AZ19-AZ21</f>
-        <v>22246.530713855147</v>
+        <f t="shared" si="15"/>
+        <v>19319</v>
       </c>
       <c r="BA20" s="2">
         <f>+BA19-BA21</f>
-        <v>23008.256005482799</v>
+        <v>19925.125000000004</v>
       </c>
       <c r="BB20" s="2">
-        <f t="shared" ref="BB20:BF20" si="61">+BB19-BB21</f>
-        <v>23797.549524369886</v>
+        <f>+BB19-BB21</f>
+        <v>20842.812510000003</v>
       </c>
       <c r="BC20" s="2">
-        <f t="shared" si="61"/>
-        <v>24615.474140759714</v>
+        <f>+BC19-BC21</f>
+        <v>21788.881232600004</v>
       </c>
       <c r="BD20" s="2">
-        <f t="shared" si="61"/>
-        <v>25463.136402174176</v>
+        <f>+BD19-BD21</f>
+        <v>22534.097576378004</v>
       </c>
       <c r="BE20" s="2">
-        <f t="shared" si="61"/>
-        <v>26341.688433290648</v>
+        <f>+BE19-BE21</f>
+        <v>23306.247905809349</v>
       </c>
       <c r="BF20" s="2">
-        <f t="shared" si="61"/>
-        <v>27252.329922293175</v>
-      </c>
-    </row>
-    <row r="21" spans="2:125" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF20:BJ20" si="71">+BF19-BF21</f>
+        <v>24106.369115230627</v>
+      </c>
+      <c r="BG20" s="2">
+        <f t="shared" si="71"/>
+        <v>24935.540649546892</v>
+      </c>
+      <c r="BH20" s="2">
+        <f t="shared" si="71"/>
+        <v>25794.886352935624</v>
+      </c>
+      <c r="BI20" s="2">
+        <f t="shared" si="71"/>
+        <v>26685.576401621125</v>
+      </c>
+      <c r="BJ20" s="2">
+        <f t="shared" si="71"/>
+        <v>27608.829324672064</v>
+      </c>
+    </row>
+    <row r="21" spans="2:129" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>38</v>
       </c>
@@ -4007,19 +4276,19 @@
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4">
-        <f t="shared" ref="G21:J21" si="62">+G19-G20</f>
+        <f t="shared" ref="G21:J21" si="72">+G19-G20</f>
         <v>6055</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="72"/>
         <v>5276</v>
       </c>
       <c r="I21" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="72"/>
         <v>6505</v>
       </c>
       <c r="J21" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="72"/>
         <v>6702</v>
       </c>
       <c r="K21" s="4">
@@ -4068,99 +4337,115 @@
         <v>5890</v>
       </c>
       <c r="X21" s="2">
-        <f>+X19*0.57</f>
-        <v>6176.5085999999992</v>
+        <f>+X19-X20</f>
+        <v>6288</v>
       </c>
       <c r="Y21" s="2">
-        <f>+Y19*0.57</f>
-        <v>6328.5218999999997</v>
+        <f>+Y19-Y20</f>
+        <v>6294</v>
       </c>
       <c r="Z21" s="2">
-        <f>+Z19*0.57</f>
-        <v>6543.9362999999994</v>
-      </c>
-      <c r="AM21" s="2">
-        <f t="shared" ref="AM21:AS21" si="63">+AM19-AM20</f>
+        <f>+Z19-Z20</f>
+        <v>6537</v>
+      </c>
+      <c r="AA21" s="2">
+        <f>+AA19*0.57</f>
+        <v>6363.48</v>
+      </c>
+      <c r="AB21" s="2">
+        <f>+AB19*0.57</f>
+        <v>6404.2065000000002</v>
+      </c>
+      <c r="AC21" s="2">
+        <f>+AC19*0.57</f>
+        <v>6525.5879999999988</v>
+      </c>
+      <c r="AD21" s="2">
+        <f>+AD19*0.57</f>
+        <v>6577.6574999999993</v>
+      </c>
+      <c r="AQ21" s="2">
+        <f t="shared" ref="AQ21:AW21" si="73">+AQ19-AQ20</f>
         <v>11759</v>
       </c>
-      <c r="AN21" s="2">
-        <f t="shared" si="63"/>
+      <c r="AR21" s="2">
+        <f t="shared" si="73"/>
         <v>14981</v>
       </c>
-      <c r="AO21" s="2">
-        <f t="shared" si="63"/>
+      <c r="AS21" s="2">
+        <f t="shared" si="73"/>
         <v>17872</v>
       </c>
-      <c r="AP21" s="2">
-        <f t="shared" si="63"/>
+      <c r="AT21" s="2">
+        <f t="shared" si="73"/>
         <v>18673</v>
       </c>
-      <c r="AQ21" s="2">
-        <f t="shared" si="63"/>
+      <c r="AU21" s="2">
+        <f t="shared" si="73"/>
         <v>19605</v>
       </c>
-      <c r="AR21" s="2">
-        <f t="shared" si="63"/>
+      <c r="AV21" s="2">
+        <f t="shared" si="73"/>
         <v>24538</v>
       </c>
-      <c r="AS21" s="2">
-        <f t="shared" si="63"/>
+      <c r="AW21" s="2">
+        <f t="shared" si="73"/>
         <v>24627</v>
       </c>
-      <c r="AT21" s="2">
-        <f>+AT19-AT20</f>
+      <c r="AX21" s="2">
+        <f>+AX19-AX20</f>
         <v>22277</v>
       </c>
-      <c r="AU21" s="2">
-        <f>+AU19-AU20</f>
+      <c r="AY21" s="2">
+        <f>+AY19-AY20</f>
         <v>23320.999999999993</v>
       </c>
-      <c r="AV21" s="2">
-        <f>+AV19-AV20</f>
-        <v>24938.966800000002</v>
-      </c>
-      <c r="AW21" s="2">
-        <f>+AW19*0.57</f>
-        <v>26081.400395999994</v>
-      </c>
-      <c r="AX21" s="2">
-        <f>+AX19*0.57</f>
-        <v>27279.604530119996</v>
-      </c>
-      <c r="AY21" s="2">
-        <f>+AY19*0.57</f>
-        <v>28515.048847361992</v>
-      </c>
       <c r="AZ21" s="2">
-        <f>+AZ19*0.57</f>
-        <v>29489.587225342864</v>
+        <f>+AZ19-AZ20</f>
+        <v>25009</v>
       </c>
       <c r="BA21" s="2">
         <f>+BA19*0.57</f>
-        <v>30499.316100291144</v>
+        <v>26412.375000000004</v>
       </c>
       <c r="BB21" s="2">
-        <f t="shared" ref="BB21:BF21" si="64">+BB19*0.57</f>
-        <v>31545.588904397282</v>
+        <f>+BB19*0.57</f>
+        <v>27628.844489999996</v>
       </c>
       <c r="BC21" s="2">
-        <f t="shared" si="64"/>
-        <v>32629.814558681475</v>
+        <f>+BC19*0.57</f>
+        <v>28882.935587399996</v>
       </c>
       <c r="BD21" s="2">
-        <f t="shared" si="64"/>
-        <v>33753.4598819518</v>
+        <f>+BD19*0.57</f>
+        <v>29870.780508222004</v>
       </c>
       <c r="BE21" s="2">
-        <f t="shared" si="64"/>
-        <v>34918.052109245735</v>
+        <f>+BE19*0.57</f>
+        <v>30894.328619328666</v>
       </c>
       <c r="BF21" s="2">
-        <f t="shared" si="64"/>
-        <v>36125.181524900254</v>
-      </c>
-    </row>
-    <row r="22" spans="2:125" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF21:BJ21" si="74">+BF19*0.57</f>
+        <v>31954.95440856152</v>
+      </c>
+      <c r="BG21" s="2">
+        <f t="shared" si="74"/>
+        <v>33054.088768004018</v>
+      </c>
+      <c r="BH21" s="2">
+        <f t="shared" si="74"/>
+        <v>34193.221444589071</v>
+      </c>
+      <c r="BI21" s="2">
+        <f t="shared" si="74"/>
+        <v>35373.90360214893</v>
+      </c>
+      <c r="BJ21" s="2">
+        <f t="shared" si="74"/>
+        <v>36597.750500146685</v>
+      </c>
+    </row>
+    <row r="22" spans="2:129" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
         <v>39</v>
       </c>
@@ -4220,94 +4505,107 @@
         <v>3061</v>
       </c>
       <c r="X22" s="2">
-        <f>+T22*1.02</f>
-        <v>2936.58</v>
+        <v>3091</v>
       </c>
       <c r="Y22" s="2">
-        <f t="shared" ref="Y22:Y23" si="65">+U22*1.02</f>
-        <v>2952.9</v>
+        <v>3051</v>
       </c>
       <c r="Z22" s="2">
-        <f t="shared" ref="Z22:Z23" si="66">+V22*1.02</f>
-        <v>2965.14</v>
-      </c>
-      <c r="AM22" s="2">
+        <f>12332-Y22-X22-W22</f>
+        <v>3129</v>
+      </c>
+      <c r="AA22" s="2">
+        <v>3740</v>
+      </c>
+      <c r="AB22" s="2">
+        <f>+X22</f>
+        <v>3091</v>
+      </c>
+      <c r="AC22" s="2">
+        <f t="shared" ref="AC22:AC23" si="75">+Y22</f>
+        <v>3051</v>
+      </c>
+      <c r="AD22" s="2">
+        <f t="shared" ref="AD22:AD23" si="76">+Z22</f>
+        <v>3129</v>
+      </c>
+      <c r="AQ22" s="2">
         <v>6736</v>
       </c>
-      <c r="AN22" s="2">
+      <c r="AR22" s="2">
         <v>9182</v>
       </c>
-      <c r="AO22" s="2">
+      <c r="AS22" s="2">
         <v>9744</v>
       </c>
-      <c r="AP22" s="2">
+      <c r="AT22" s="2">
         <v>9765</v>
       </c>
-      <c r="AQ22" s="2">
+      <c r="AU22" s="2">
         <v>9696</v>
       </c>
-      <c r="AR22" s="2">
-        <f t="shared" ref="AR22:AR23" si="67">SUM(G22:J22)</f>
+      <c r="AV22" s="2">
+        <f t="shared" ref="AV22:AV23" si="77">SUM(G22:J22)</f>
         <v>11324</v>
       </c>
-      <c r="AS22" s="2">
-        <f t="shared" ref="AS22:AS23" si="68">SUM(K22:N22)</f>
+      <c r="AW22" s="2">
+        <f t="shared" ref="AW22:AW23" si="78">SUM(K22:N22)</f>
         <v>11104</v>
       </c>
-      <c r="AT22" s="2">
+      <c r="AX22" s="2">
         <f>SUM(O22:R22)</f>
         <v>10849</v>
       </c>
-      <c r="AU22" s="2">
-        <f t="shared" ref="AU22:AU23" si="69">SUM(S22:V22)</f>
+      <c r="AY22" s="2">
+        <f t="shared" ref="AY22:AY23" si="79">SUM(S22:V22)</f>
         <v>11606</v>
       </c>
-      <c r="AV22" s="2">
-        <f t="shared" si="11"/>
-        <v>11915.619999999999</v>
-      </c>
-      <c r="AW22" s="2">
-        <f t="shared" ref="AW22:BA22" si="70">+AV22*1.03</f>
-        <v>12273.088599999999</v>
-      </c>
-      <c r="AX22" s="2">
-        <f t="shared" si="70"/>
-        <v>12641.281257999999</v>
-      </c>
-      <c r="AY22" s="2">
-        <f t="shared" si="70"/>
-        <v>13020.519695739998</v>
-      </c>
       <c r="AZ22" s="2">
-        <f t="shared" si="70"/>
-        <v>13411.1352866122</v>
+        <f t="shared" si="15"/>
+        <v>12332</v>
       </c>
       <c r="BA22" s="2">
-        <f t="shared" si="70"/>
-        <v>13813.469345210566</v>
+        <f t="shared" ref="BA22:BE22" si="80">+AZ22*1.03</f>
+        <v>12701.960000000001</v>
       </c>
       <c r="BB22" s="2">
-        <f t="shared" ref="BB22:BF22" si="71">+BA22*1.03</f>
-        <v>14227.873425566882</v>
+        <f t="shared" si="80"/>
+        <v>13083.018800000002</v>
       </c>
       <c r="BC22" s="2">
-        <f t="shared" si="71"/>
-        <v>14654.709628333889</v>
+        <f t="shared" si="80"/>
+        <v>13475.509364000001</v>
       </c>
       <c r="BD22" s="2">
-        <f t="shared" si="71"/>
-        <v>15094.350917183905</v>
+        <f t="shared" si="80"/>
+        <v>13879.774644920002</v>
       </c>
       <c r="BE22" s="2">
-        <f t="shared" si="71"/>
-        <v>15547.181444699423</v>
+        <f t="shared" si="80"/>
+        <v>14296.167884267603</v>
       </c>
       <c r="BF22" s="2">
-        <f t="shared" si="71"/>
-        <v>16013.596888040407</v>
-      </c>
-    </row>
-    <row r="23" spans="2:125" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF22:BJ22" si="81">+BE22*1.03</f>
+        <v>14725.052920795632</v>
+      </c>
+      <c r="BG22" s="2">
+        <f t="shared" si="81"/>
+        <v>15166.8045084195</v>
+      </c>
+      <c r="BH22" s="2">
+        <f t="shared" si="81"/>
+        <v>15621.808643672086</v>
+      </c>
+      <c r="BI22" s="2">
+        <f t="shared" si="81"/>
+        <v>16090.462902982248</v>
+      </c>
+      <c r="BJ22" s="2">
+        <f t="shared" si="81"/>
+        <v>16573.176790071717</v>
+      </c>
+    </row>
+    <row r="23" spans="2:129" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>40</v>
       </c>
@@ -4367,94 +4665,107 @@
         <v>716</v>
       </c>
       <c r="X23" s="2">
-        <f t="shared" ref="X23" si="72">+T23*1.02</f>
-        <v>670.14</v>
+        <v>725</v>
       </c>
       <c r="Y23" s="2">
-        <f t="shared" si="65"/>
-        <v>727.26</v>
+        <v>756</v>
       </c>
       <c r="Z23" s="2">
-        <f t="shared" si="66"/>
-        <v>763.98</v>
-      </c>
-      <c r="AM23" s="2">
+        <f>2942-Y23-X23-W23</f>
+        <v>745</v>
+      </c>
+      <c r="AA23" s="2">
+        <v>767</v>
+      </c>
+      <c r="AB23" s="2">
+        <f t="shared" ref="AB23" si="82">+X23</f>
+        <v>725</v>
+      </c>
+      <c r="AC23" s="2">
+        <f t="shared" si="75"/>
+        <v>756</v>
+      </c>
+      <c r="AD23" s="2">
+        <f t="shared" si="76"/>
+        <v>745</v>
+      </c>
+      <c r="AQ23" s="2">
         <v>1447</v>
       </c>
-      <c r="AN23" s="2">
+      <c r="AR23" s="2">
         <v>2260</v>
       </c>
-      <c r="AO23" s="2">
+      <c r="AS23" s="2">
         <v>2300</v>
       </c>
-      <c r="AP23" s="2">
+      <c r="AT23" s="2">
         <v>2440</v>
       </c>
-      <c r="AQ23" s="2">
+      <c r="AU23" s="2">
         <v>2420</v>
       </c>
-      <c r="AR23" s="2">
-        <f t="shared" si="67"/>
+      <c r="AV23" s="2">
+        <f t="shared" si="77"/>
         <v>2742</v>
       </c>
-      <c r="AS23" s="2">
-        <f t="shared" si="68"/>
+      <c r="AW23" s="2">
+        <f t="shared" si="78"/>
         <v>2817</v>
       </c>
-      <c r="AT23" s="2">
+      <c r="AX23" s="2">
         <f>SUM(O23:R23)</f>
         <v>2519</v>
       </c>
-      <c r="AU23" s="2">
-        <f t="shared" si="69"/>
+      <c r="AY23" s="2">
+        <f t="shared" si="79"/>
         <v>2782</v>
       </c>
-      <c r="AV23" s="2">
-        <f t="shared" si="11"/>
-        <v>2877.3799999999997</v>
-      </c>
-      <c r="AW23" s="2">
-        <f>+AV23*1.03</f>
-        <v>2963.7013999999999</v>
-      </c>
-      <c r="AX23" s="2">
-        <f t="shared" ref="AX23:BA23" si="73">+AW23*1.03</f>
-        <v>3052.6124420000001</v>
-      </c>
-      <c r="AY23" s="2">
-        <f t="shared" si="73"/>
-        <v>3144.1908152600004</v>
-      </c>
       <c r="AZ23" s="2">
-        <f t="shared" si="73"/>
-        <v>3238.5165397178002</v>
+        <f t="shared" si="15"/>
+        <v>2942</v>
       </c>
       <c r="BA23" s="2">
-        <f t="shared" si="73"/>
-        <v>3335.6720359093342</v>
+        <f>+AZ23*1.03</f>
+        <v>3030.26</v>
       </c>
       <c r="BB23" s="2">
-        <f t="shared" ref="BB23:BF23" si="74">+BA23*1.03</f>
-        <v>3435.7421969866145</v>
+        <f t="shared" ref="BB23:BE23" si="83">+BA23*1.03</f>
+        <v>3121.1678000000002</v>
       </c>
       <c r="BC23" s="2">
-        <f t="shared" si="74"/>
-        <v>3538.8144628962132</v>
+        <f t="shared" si="83"/>
+        <v>3214.8028340000001</v>
       </c>
       <c r="BD23" s="2">
-        <f t="shared" si="74"/>
-        <v>3644.9788967830996</v>
+        <f t="shared" si="83"/>
+        <v>3311.24691902</v>
       </c>
       <c r="BE23" s="2">
-        <f t="shared" si="74"/>
-        <v>3754.3282636865924</v>
+        <f t="shared" si="83"/>
+        <v>3410.5843265906001</v>
       </c>
       <c r="BF23" s="2">
-        <f t="shared" si="74"/>
-        <v>3866.9581115971905</v>
-      </c>
-    </row>
-    <row r="24" spans="2:125" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF23:BJ23" si="84">+BE23*1.03</f>
+        <v>3512.9018563883183</v>
+      </c>
+      <c r="BG23" s="2">
+        <f t="shared" si="84"/>
+        <v>3618.2889120799678</v>
+      </c>
+      <c r="BH23" s="2">
+        <f t="shared" si="84"/>
+        <v>3726.8375794423669</v>
+      </c>
+      <c r="BI23" s="2">
+        <f t="shared" si="84"/>
+        <v>3838.642706825638</v>
+      </c>
+      <c r="BJ23" s="2">
+        <f t="shared" si="84"/>
+        <v>3953.8019880304073</v>
+      </c>
+    </row>
+    <row r="24" spans="2:129" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>35</v>
       </c>
@@ -4463,19 +4774,19 @@
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4">
-        <f t="shared" ref="G24:J24" si="75">+G22+G23</f>
+        <f t="shared" ref="G24:J24" si="85">+G22+G23</f>
         <v>3437</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="85"/>
         <v>3380</v>
       </c>
       <c r="I24" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="85"/>
         <v>3439</v>
       </c>
       <c r="J24" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="85"/>
         <v>3810</v>
       </c>
       <c r="K24" s="4">
@@ -4495,135 +4806,151 @@
         <v>3483</v>
       </c>
       <c r="O24" s="4">
-        <f t="shared" ref="O24" si="76">+O22+O23</f>
+        <f t="shared" ref="O24" si="86">+O22+O23</f>
         <v>3390</v>
       </c>
       <c r="P24" s="2">
-        <f t="shared" ref="P24:X24" si="77">+P22+P23</f>
+        <f t="shared" ref="P24:X24" si="87">+P22+P23</f>
         <v>3361</v>
       </c>
       <c r="Q24" s="2">
-        <f t="shared" si="77"/>
+        <f t="shared" si="87"/>
         <v>3306</v>
       </c>
       <c r="R24" s="2">
-        <f t="shared" si="77"/>
+        <f t="shared" si="87"/>
         <v>3311</v>
       </c>
       <c r="S24" s="2">
-        <f t="shared" si="77"/>
+        <f t="shared" si="87"/>
         <v>3588</v>
       </c>
       <c r="T24" s="2">
-        <f t="shared" si="77"/>
+        <f t="shared" si="87"/>
         <v>3536</v>
       </c>
       <c r="U24" s="2">
-        <f t="shared" si="77"/>
+        <f t="shared" si="87"/>
         <v>3608</v>
       </c>
       <c r="V24" s="2">
-        <f t="shared" si="77"/>
+        <f t="shared" si="87"/>
         <v>3656</v>
       </c>
       <c r="W24" s="2">
-        <f t="shared" si="77"/>
+        <f t="shared" si="87"/>
         <v>3777</v>
       </c>
       <c r="X24" s="2">
-        <f t="shared" si="77"/>
-        <v>3606.72</v>
+        <f t="shared" si="87"/>
+        <v>3816</v>
       </c>
       <c r="Y24" s="2">
-        <f t="shared" ref="Y24" si="78">+Y22+Y23</f>
-        <v>3680.16</v>
+        <f t="shared" ref="Y24" si="88">+Y22+Y23</f>
+        <v>3807</v>
       </c>
       <c r="Z24" s="2">
-        <f t="shared" ref="Z24" si="79">+Z22+Z23</f>
-        <v>3729.12</v>
-      </c>
-      <c r="AM24" s="4">
-        <f>+AM22+AM23</f>
+        <f t="shared" ref="Z24:AA24" si="89">+Z22+Z23</f>
+        <v>3874</v>
+      </c>
+      <c r="AA24" s="2">
+        <f t="shared" si="89"/>
+        <v>4507</v>
+      </c>
+      <c r="AB24" s="2">
+        <f t="shared" ref="AB24:AD24" si="90">+AB22+AB23</f>
+        <v>3816</v>
+      </c>
+      <c r="AC24" s="2">
+        <f t="shared" si="90"/>
+        <v>3807</v>
+      </c>
+      <c r="AD24" s="2">
+        <f t="shared" si="90"/>
+        <v>3874</v>
+      </c>
+      <c r="AQ24" s="4">
+        <f>+AQ22+AQ23</f>
         <v>8183</v>
       </c>
-      <c r="AN24" s="4">
-        <f>+AN22+AN23</f>
+      <c r="AR24" s="4">
+        <f>+AR22+AR23</f>
         <v>11442</v>
       </c>
-      <c r="AO24" s="4">
-        <f>+AO22+AO23</f>
+      <c r="AS24" s="4">
+        <f>+AS22+AS23</f>
         <v>12044</v>
       </c>
-      <c r="AP24" s="4">
-        <f t="shared" ref="AP24:AS24" si="80">+AP22+AP23</f>
+      <c r="AT24" s="4">
+        <f t="shared" ref="AT24:AW24" si="91">+AT22+AT23</f>
         <v>12205</v>
       </c>
-      <c r="AQ24" s="4">
-        <f t="shared" si="80"/>
+      <c r="AU24" s="4">
+        <f t="shared" si="91"/>
         <v>12116</v>
       </c>
-      <c r="AR24" s="4">
-        <f t="shared" si="80"/>
+      <c r="AV24" s="4">
+        <f t="shared" si="91"/>
         <v>14066</v>
       </c>
-      <c r="AS24" s="4">
-        <f t="shared" si="80"/>
+      <c r="AW24" s="4">
+        <f t="shared" si="91"/>
         <v>13921</v>
       </c>
-      <c r="AT24" s="4">
-        <f t="shared" ref="AT24:AV24" si="81">+AT22+AT23</f>
+      <c r="AX24" s="4">
+        <f t="shared" ref="AX24:AZ24" si="92">+AX22+AX23</f>
         <v>13368</v>
       </c>
-      <c r="AU24" s="4">
-        <f t="shared" si="81"/>
+      <c r="AY24" s="4">
+        <f t="shared" si="92"/>
         <v>14388</v>
       </c>
-      <c r="AV24" s="4">
-        <f t="shared" si="81"/>
-        <v>14792.999999999998</v>
-      </c>
-      <c r="AW24" s="4">
-        <f t="shared" ref="AW24:BA24" si="82">+AW22+AW23</f>
-        <v>15236.789999999999</v>
-      </c>
-      <c r="AX24" s="4">
-        <f t="shared" si="82"/>
-        <v>15693.893699999999</v>
-      </c>
-      <c r="AY24" s="4">
-        <f t="shared" si="82"/>
-        <v>16164.710510999999</v>
-      </c>
       <c r="AZ24" s="4">
-        <f t="shared" si="82"/>
-        <v>16649.651826329999</v>
+        <f t="shared" si="92"/>
+        <v>15274</v>
       </c>
       <c r="BA24" s="4">
-        <f t="shared" si="82"/>
-        <v>17149.141381119902</v>
+        <f t="shared" ref="BA24:BE24" si="93">+BA22+BA23</f>
+        <v>15732.220000000001</v>
       </c>
       <c r="BB24" s="4">
-        <f t="shared" ref="BB24:BF24" si="83">+BB22+BB23</f>
-        <v>17663.615622553498</v>
+        <f t="shared" si="93"/>
+        <v>16204.186600000001</v>
       </c>
       <c r="BC24" s="4">
-        <f t="shared" si="83"/>
-        <v>18193.524091230101</v>
+        <f t="shared" si="93"/>
+        <v>16690.312198</v>
       </c>
       <c r="BD24" s="4">
-        <f t="shared" si="83"/>
-        <v>18739.329813967004</v>
+        <f t="shared" si="93"/>
+        <v>17191.021563940001</v>
       </c>
       <c r="BE24" s="4">
-        <f t="shared" si="83"/>
-        <v>19301.509708386016</v>
+        <f t="shared" si="93"/>
+        <v>17706.752210858202</v>
       </c>
       <c r="BF24" s="4">
-        <f t="shared" si="83"/>
-        <v>19880.554999637599</v>
-      </c>
-    </row>
-    <row r="25" spans="2:125" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF24:BJ24" si="94">+BF22+BF23</f>
+        <v>18237.95477718395</v>
+      </c>
+      <c r="BG24" s="4">
+        <f t="shared" si="94"/>
+        <v>18785.093420499466</v>
+      </c>
+      <c r="BH24" s="4">
+        <f t="shared" si="94"/>
+        <v>19348.646223114454</v>
+      </c>
+      <c r="BI24" s="4">
+        <f t="shared" si="94"/>
+        <v>19929.105609807884</v>
+      </c>
+      <c r="BJ24" s="4">
+        <f t="shared" si="94"/>
+        <v>20526.978778102122</v>
+      </c>
+    </row>
+    <row r="25" spans="2:129" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
         <v>36</v>
       </c>
@@ -4632,19 +4959,19 @@
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4">
-        <f t="shared" ref="G25:J25" si="84">+G21-G24</f>
+        <f t="shared" ref="G25:J25" si="95">+G21-G24</f>
         <v>2618</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="84"/>
+        <f t="shared" si="95"/>
         <v>1896</v>
       </c>
       <c r="I25" s="4">
-        <f t="shared" si="84"/>
+        <f t="shared" si="95"/>
         <v>3066</v>
       </c>
       <c r="J25" s="4">
-        <f t="shared" si="84"/>
+        <f t="shared" si="95"/>
         <v>2892</v>
       </c>
       <c r="K25" s="4">
@@ -4664,135 +4991,151 @@
         <v>2131</v>
       </c>
       <c r="O25" s="4">
-        <f t="shared" ref="O25" si="85">+O21-O24</f>
+        <f t="shared" ref="O25" si="96">+O21-O24</f>
         <v>2055</v>
       </c>
       <c r="P25" s="2">
-        <f t="shared" ref="P25:X25" si="86">+P21-P24</f>
+        <f t="shared" ref="P25:X25" si="97">+P21-P24</f>
         <v>2165</v>
       </c>
       <c r="Q25" s="2">
-        <f t="shared" si="86"/>
+        <f t="shared" si="97"/>
         <v>2278</v>
       </c>
       <c r="R25" s="2">
-        <f t="shared" si="86"/>
+        <f t="shared" si="97"/>
         <v>2411</v>
       </c>
       <c r="S25" s="2">
-        <f t="shared" si="86"/>
+        <f t="shared" si="97"/>
         <v>1959</v>
       </c>
       <c r="T25" s="2">
-        <f t="shared" si="86"/>
+        <f t="shared" si="97"/>
         <v>2273</v>
       </c>
       <c r="U25" s="2">
-        <f t="shared" si="86"/>
+        <f t="shared" si="97"/>
         <v>1934.3899999999994</v>
       </c>
       <c r="V25" s="2">
-        <f t="shared" si="86"/>
+        <f t="shared" si="97"/>
         <v>2376</v>
       </c>
       <c r="W25" s="2">
-        <f t="shared" si="86"/>
+        <f t="shared" si="97"/>
         <v>2113</v>
       </c>
       <c r="X25" s="2">
-        <f t="shared" si="86"/>
-        <v>2569.7885999999994</v>
+        <f t="shared" si="97"/>
+        <v>2472</v>
       </c>
       <c r="Y25" s="2">
-        <f t="shared" ref="Y25" si="87">+Y21-Y24</f>
-        <v>2648.3618999999999</v>
+        <f t="shared" ref="Y25" si="98">+Y21-Y24</f>
+        <v>2487</v>
       </c>
       <c r="Z25" s="2">
-        <f t="shared" ref="Z25" si="88">+Z21-Z24</f>
-        <v>2814.8162999999995</v>
-      </c>
-      <c r="AM25" s="4">
-        <f>+AM21-AM24</f>
+        <f t="shared" ref="Z25:AA25" si="99">+Z21-Z24</f>
+        <v>2663</v>
+      </c>
+      <c r="AA25" s="2">
+        <f t="shared" si="99"/>
+        <v>1856.4799999999996</v>
+      </c>
+      <c r="AB25" s="2">
+        <f t="shared" ref="AB25:AD25" si="100">+AB21-AB24</f>
+        <v>2588.2065000000002</v>
+      </c>
+      <c r="AC25" s="2">
+        <f t="shared" si="100"/>
+        <v>2718.5879999999988</v>
+      </c>
+      <c r="AD25" s="2">
+        <f t="shared" si="100"/>
+        <v>2703.6574999999993</v>
+      </c>
+      <c r="AQ25" s="4">
+        <f>+AQ21-AQ24</f>
         <v>3576</v>
       </c>
-      <c r="AN25" s="4">
-        <f>+AN21-AN24</f>
+      <c r="AR25" s="4">
+        <f>+AR21-AR24</f>
         <v>3539</v>
       </c>
-      <c r="AO25" s="4">
-        <f>+AO21-AO24</f>
+      <c r="AS25" s="4">
+        <f>+AS21-AS24</f>
         <v>5828</v>
       </c>
-      <c r="AP25" s="4">
-        <f t="shared" ref="AP25:AS25" si="89">+AP21-AP24</f>
+      <c r="AT25" s="4">
+        <f t="shared" ref="AT25:AW25" si="101">+AT21-AT24</f>
         <v>6468</v>
       </c>
-      <c r="AQ25" s="4">
-        <f t="shared" si="89"/>
+      <c r="AU25" s="4">
+        <f t="shared" si="101"/>
         <v>7489</v>
       </c>
-      <c r="AR25" s="4">
-        <f t="shared" si="89"/>
+      <c r="AV25" s="4">
+        <f t="shared" si="101"/>
         <v>10472</v>
       </c>
-      <c r="AS25" s="4">
-        <f t="shared" si="89"/>
+      <c r="AW25" s="4">
+        <f t="shared" si="101"/>
         <v>10706</v>
       </c>
-      <c r="AT25" s="4">
-        <f t="shared" ref="AT25:AV25" si="90">+AT21-AT24</f>
+      <c r="AX25" s="4">
+        <f t="shared" ref="AX25:AZ25" si="102">+AX21-AX24</f>
         <v>8909</v>
       </c>
-      <c r="AU25" s="4">
-        <f t="shared" si="90"/>
+      <c r="AY25" s="4">
+        <f t="shared" si="102"/>
         <v>8932.9999999999927</v>
       </c>
-      <c r="AV25" s="4">
-        <f t="shared" si="90"/>
-        <v>10145.966800000004</v>
-      </c>
-      <c r="AW25" s="4">
-        <f t="shared" ref="AW25:BA25" si="91">+AW21-AW24</f>
-        <v>10844.610395999995</v>
-      </c>
-      <c r="AX25" s="4">
-        <f t="shared" si="91"/>
-        <v>11585.710830119997</v>
-      </c>
-      <c r="AY25" s="4">
-        <f t="shared" si="91"/>
-        <v>12350.338336361992</v>
-      </c>
       <c r="AZ25" s="4">
-        <f t="shared" si="91"/>
-        <v>12839.935399012866</v>
+        <f t="shared" si="102"/>
+        <v>9735</v>
       </c>
       <c r="BA25" s="4">
-        <f t="shared" si="91"/>
-        <v>13350.174719171242</v>
+        <f t="shared" ref="BA25:BE25" si="103">+BA21-BA24</f>
+        <v>10680.155000000002</v>
       </c>
       <c r="BB25" s="4">
-        <f t="shared" ref="BB25:BF25" si="92">+BB21-BB24</f>
-        <v>13881.973281843784</v>
+        <f t="shared" si="103"/>
+        <v>11424.657889999995</v>
       </c>
       <c r="BC25" s="4">
-        <f t="shared" si="92"/>
-        <v>14436.290467451374</v>
+        <f t="shared" si="103"/>
+        <v>12192.623389399996</v>
       </c>
       <c r="BD25" s="4">
-        <f t="shared" si="92"/>
-        <v>15014.130067984795</v>
+        <f t="shared" si="103"/>
+        <v>12679.758944282003</v>
       </c>
       <c r="BE25" s="4">
-        <f t="shared" si="92"/>
-        <v>15616.542400859718</v>
+        <f t="shared" si="103"/>
+        <v>13187.576408470464</v>
       </c>
       <c r="BF25" s="4">
-        <f t="shared" si="92"/>
-        <v>16244.626525262654</v>
-      </c>
-    </row>
-    <row r="26" spans="2:125" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF25:BJ25" si="104">+BF21-BF24</f>
+        <v>13716.99963137757</v>
+      </c>
+      <c r="BG25" s="4">
+        <f t="shared" si="104"/>
+        <v>14268.995347504551</v>
+      </c>
+      <c r="BH25" s="4">
+        <f t="shared" si="104"/>
+        <v>14844.575221474617</v>
+      </c>
+      <c r="BI25" s="4">
+        <f t="shared" si="104"/>
+        <v>15444.797992341046</v>
+      </c>
+      <c r="BJ25" s="4">
+        <f t="shared" si="104"/>
+        <v>16070.771722044563</v>
+      </c>
+    </row>
+    <row r="26" spans="2:129" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
         <v>41</v>
       </c>
@@ -4858,264 +5201,284 @@
         <v>78</v>
       </c>
       <c r="X26">
-        <f>+W26</f>
-        <v>78</v>
+        <f>-121+71</f>
+        <v>-50</v>
       </c>
       <c r="Y26">
-        <f>+X26</f>
-        <v>78</v>
+        <f>-121+77</f>
+        <v>-44</v>
       </c>
       <c r="Z26">
-        <f>+Y26</f>
-        <v>78</v>
-      </c>
-      <c r="AM26">
+        <f>-493+308-Y26-X26-W26</f>
+        <v>-169</v>
+      </c>
+      <c r="AA26">
+        <f>-174+106</f>
+        <v>-68</v>
+      </c>
+      <c r="AQ26">
         <f>-99+786</f>
         <v>687</v>
       </c>
-      <c r="AN26" s="2">
+      <c r="AR26" s="2">
         <f>-904+124-1413</f>
         <v>-2193</v>
       </c>
-      <c r="AO26">
+      <c r="AS26">
         <f>-826+105+139</f>
         <v>-582</v>
       </c>
-      <c r="AP26">
+      <c r="AT26">
         <f>-670+94+191</f>
         <v>-385</v>
       </c>
-      <c r="AQ26">
+      <c r="AU26">
         <f>-546+46+103</f>
         <v>-397</v>
       </c>
-      <c r="AR26" s="2">
-        <f t="shared" ref="AR26" si="93">SUM(G26:J26)</f>
+      <c r="AV26" s="2">
+        <f t="shared" ref="AV26" si="105">SUM(G26:J26)</f>
         <v>-213</v>
       </c>
-      <c r="AS26" s="2">
-        <f t="shared" ref="AS26" si="94">SUM(K26:N26)</f>
+      <c r="AW26" s="2">
+        <f t="shared" ref="AW26" si="106">SUM(K26:N26)</f>
         <v>36</v>
       </c>
-      <c r="AT26" s="2">
+      <c r="AX26" s="2">
         <f>SUM(O26:R26)</f>
         <v>454</v>
       </c>
-      <c r="AU26" s="2">
-        <f t="shared" ref="AU26" si="95">SUM(S26:V26)</f>
+      <c r="AY26" s="2">
+        <f t="shared" ref="AY26" si="107">SUM(S26:V26)</f>
         <v>451</v>
       </c>
-      <c r="AV26" s="2">
-        <f t="shared" ref="AV26:AV28" si="96">SUM(W26:Z26)</f>
-        <v>312</v>
-      </c>
-      <c r="AW26" s="2">
-        <f t="shared" ref="AW26:BF26" si="97">+AV40*$BI$37</f>
-        <v>76.796088999999938</v>
-      </c>
-      <c r="AX26" s="2">
-        <f t="shared" si="97"/>
-        <v>540.95586461249968</v>
-      </c>
-      <c r="AY26" s="2">
-        <f t="shared" si="97"/>
-        <v>1056.3391991386306</v>
-      </c>
       <c r="AZ26" s="2">
-        <f t="shared" si="97"/>
-        <v>1626.1229943974072</v>
+        <f t="shared" ref="AZ26:AZ28" si="108">SUM(W26:Z26)</f>
+        <v>-185</v>
       </c>
       <c r="BA26" s="2">
-        <f t="shared" si="97"/>
-        <v>2240.9304761173439</v>
+        <f t="shared" ref="BA26:BJ26" si="109">+AZ40*$BM$37</f>
+        <v>18.95</v>
       </c>
       <c r="BB26" s="2">
-        <f t="shared" si="97"/>
-        <v>2903.5524469171087</v>
+        <f t="shared" si="109"/>
+        <v>473.66196250000013</v>
       </c>
       <c r="BC26" s="2">
-        <f t="shared" si="97"/>
+        <f t="shared" si="109"/>
+        <v>979.34055623124993</v>
+      </c>
+      <c r="BD26" s="2">
+        <f t="shared" si="109"/>
+        <v>1539.1490239205777</v>
+      </c>
+      <c r="BE26" s="2">
+        <f t="shared" si="109"/>
+        <v>2143.4526125691877</v>
+      </c>
+      <c r="BF26" s="2">
+        <f t="shared" si="109"/>
+        <v>2795.0213459633728</v>
+      </c>
+      <c r="BG26" s="2">
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
-      <c r="BD26" s="2">
-        <f t="shared" si="97"/>
+      <c r="BH26" s="2">
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
-      <c r="BE26" s="2">
-        <f t="shared" si="97"/>
+      <c r="BI26" s="2">
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
-      <c r="BF26" s="2">
-        <f t="shared" si="97"/>
+      <c r="BJ26" s="2">
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:125" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:129" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
         <v>42</v>
       </c>
       <c r="G27" s="4">
-        <f t="shared" ref="G27:J27" si="98">+G25+G26</f>
+        <f t="shared" ref="G27:J27" si="110">+G25+G26</f>
         <v>2555</v>
       </c>
       <c r="H27" s="4">
-        <f t="shared" si="98"/>
+        <f t="shared" si="110"/>
         <v>1852</v>
       </c>
       <c r="I27" s="4">
-        <f t="shared" si="98"/>
+        <f t="shared" si="110"/>
         <v>3017</v>
       </c>
       <c r="J27" s="4">
-        <f t="shared" si="98"/>
+        <f t="shared" si="110"/>
         <v>2835</v>
       </c>
       <c r="K27" s="4">
-        <f t="shared" ref="K27:X27" si="99">+K25+K26</f>
+        <f t="shared" ref="K27:X27" si="111">+K25+K26</f>
         <v>3385</v>
       </c>
       <c r="L27" s="4">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>2859</v>
       </c>
       <c r="M27" s="4">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>2272</v>
       </c>
       <c r="N27" s="4">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>2223</v>
       </c>
       <c r="O27" s="4">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>2166</v>
       </c>
       <c r="P27" s="2">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>2284</v>
       </c>
       <c r="Q27" s="2">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>2384</v>
       </c>
       <c r="R27" s="2">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>2529</v>
       </c>
       <c r="S27" s="2">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>2096</v>
       </c>
       <c r="T27" s="2">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>2408</v>
       </c>
       <c r="U27" s="2">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>2004.3899999999994</v>
       </c>
       <c r="V27" s="2">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>2485</v>
       </c>
       <c r="W27" s="2">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>2191</v>
       </c>
       <c r="X27" s="2">
-        <f t="shared" si="99"/>
-        <v>2647.7885999999994</v>
+        <f t="shared" si="111"/>
+        <v>2422</v>
       </c>
       <c r="Y27" s="2">
-        <f t="shared" ref="Y27" si="100">+Y25+Y26</f>
-        <v>2726.3618999999999</v>
+        <f t="shared" ref="Y27" si="112">+Y25+Y26</f>
+        <v>2443</v>
       </c>
       <c r="Z27" s="2">
-        <f t="shared" ref="Z27" si="101">+Z25+Z26</f>
-        <v>2892.8162999999995</v>
-      </c>
-      <c r="AM27" s="2">
-        <f>+AM25+AM26</f>
+        <f t="shared" ref="Z27:AD27" si="113">+Z25+Z26</f>
+        <v>2494</v>
+      </c>
+      <c r="AA27" s="2">
+        <f t="shared" si="113"/>
+        <v>1788.4799999999996</v>
+      </c>
+      <c r="AB27" s="2">
+        <f t="shared" si="113"/>
+        <v>2588.2065000000002</v>
+      </c>
+      <c r="AC27" s="2">
+        <f t="shared" si="113"/>
+        <v>2718.5879999999988</v>
+      </c>
+      <c r="AD27" s="2">
+        <f t="shared" si="113"/>
+        <v>2703.6574999999993</v>
+      </c>
+      <c r="AQ27" s="2">
+        <f>+AQ25+AQ26</f>
         <v>4263</v>
       </c>
-      <c r="AN27" s="2">
-        <f>+AN25+AN26</f>
+      <c r="AR27" s="2">
+        <f>+AR25+AR26</f>
         <v>1346</v>
       </c>
-      <c r="AO27" s="2">
-        <f>+AO25+AO26</f>
+      <c r="AS27" s="2">
+        <f>+AS25+AS26</f>
         <v>5246</v>
       </c>
-      <c r="AP27" s="2">
-        <f t="shared" ref="AP27:AW27" si="102">+AP25+AP26</f>
+      <c r="AT27" s="2">
+        <f t="shared" ref="AT27:BA27" si="114">+AT25+AT26</f>
         <v>6083</v>
       </c>
-      <c r="AQ27" s="2">
-        <f t="shared" si="102"/>
+      <c r="AU27" s="2">
+        <f t="shared" si="114"/>
         <v>7092</v>
       </c>
-      <c r="AR27" s="2">
-        <f t="shared" si="102"/>
+      <c r="AV27" s="2">
+        <f t="shared" si="114"/>
         <v>10259</v>
       </c>
-      <c r="AS27" s="2">
-        <f t="shared" si="102"/>
+      <c r="AW27" s="2">
+        <f t="shared" si="114"/>
         <v>10742</v>
       </c>
-      <c r="AT27" s="2">
-        <f t="shared" si="102"/>
+      <c r="AX27" s="2">
+        <f t="shared" si="114"/>
         <v>9363</v>
       </c>
-      <c r="AU27" s="2">
-        <f t="shared" si="102"/>
+      <c r="AY27" s="2">
+        <f t="shared" si="114"/>
         <v>9383.9999999999927</v>
       </c>
-      <c r="AV27" s="2">
-        <f t="shared" si="102"/>
-        <v>10457.966800000004</v>
-      </c>
-      <c r="AW27" s="2">
-        <f t="shared" si="102"/>
-        <v>10921.406484999994</v>
-      </c>
-      <c r="AX27" s="2">
-        <f t="shared" ref="AX27:BA27" si="103">+AX25+AX26</f>
-        <v>12126.666694732496</v>
-      </c>
-      <c r="AY27" s="2">
-        <f t="shared" si="103"/>
-        <v>13406.677535500623</v>
-      </c>
       <c r="AZ27" s="2">
-        <f t="shared" si="103"/>
-        <v>14466.058393410272</v>
+        <f t="shared" si="114"/>
+        <v>9550</v>
       </c>
       <c r="BA27" s="2">
-        <f t="shared" si="103"/>
-        <v>15591.105195288586</v>
+        <f t="shared" si="114"/>
+        <v>10699.105000000003</v>
       </c>
       <c r="BB27" s="2">
-        <f t="shared" ref="BB27:BF27" si="104">+BB25+BB26</f>
-        <v>16785.525728760891</v>
+        <f t="shared" ref="BB27:BE27" si="115">+BB25+BB26</f>
+        <v>11898.319852499995</v>
       </c>
       <c r="BC27" s="2">
-        <f t="shared" si="104"/>
-        <v>14436.290467451374</v>
+        <f t="shared" si="115"/>
+        <v>13171.963945631245</v>
       </c>
       <c r="BD27" s="2">
-        <f t="shared" si="104"/>
-        <v>15014.130067984795</v>
+        <f t="shared" si="115"/>
+        <v>14218.90796820258</v>
       </c>
       <c r="BE27" s="2">
-        <f t="shared" si="104"/>
-        <v>15616.542400859718</v>
+        <f t="shared" si="115"/>
+        <v>15331.029021039652</v>
       </c>
       <c r="BF27" s="2">
-        <f t="shared" si="104"/>
-        <v>16244.626525262654</v>
-      </c>
-    </row>
-    <row r="28" spans="2:125" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF27:BJ27" si="116">+BF25+BF26</f>
+        <v>16512.020977340944</v>
+      </c>
+      <c r="BG27" s="2">
+        <f t="shared" si="116"/>
+        <v>14268.995347504551</v>
+      </c>
+      <c r="BH27" s="2">
+        <f t="shared" si="116"/>
+        <v>14844.575221474617</v>
+      </c>
+      <c r="BI27" s="2">
+        <f t="shared" si="116"/>
+        <v>15444.797992341046</v>
+      </c>
+      <c r="BJ27" s="2">
+        <f t="shared" si="116"/>
+        <v>16070.771722044563</v>
+      </c>
+    </row>
+    <row r="28" spans="2:129" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
         <v>43</v>
       </c>
@@ -5171,692 +5534,737 @@
         <v>453</v>
       </c>
       <c r="X28" s="2">
-        <f>+X27*0.15</f>
-        <v>397.1682899999999</v>
+        <v>371</v>
       </c>
       <c r="Y28" s="2">
-        <f>+Y27*0.15</f>
-        <v>408.95428499999997</v>
+        <v>536</v>
       </c>
       <c r="Z28" s="2">
-        <f>+Z27*0.15</f>
-        <v>433.92244499999993</v>
-      </c>
-      <c r="AM28">
+        <f>1942-Y28-X28-W28</f>
+        <v>582</v>
+      </c>
+      <c r="AA28" s="2">
+        <v>372</v>
+      </c>
+      <c r="AB28" s="2">
+        <f>+AB27*0.2</f>
+        <v>517.64130000000011</v>
+      </c>
+      <c r="AC28" s="2">
+        <f>+AC27*0.2</f>
+        <v>543.71759999999983</v>
+      </c>
+      <c r="AD28" s="2">
+        <f>+AD27*0.2</f>
+        <v>540.73149999999987</v>
+      </c>
+      <c r="AQ28">
         <v>350</v>
       </c>
-      <c r="AN28">
+      <c r="AR28">
         <v>0</v>
       </c>
-      <c r="AO28">
+      <c r="AS28">
         <v>539</v>
       </c>
-      <c r="AP28">
+      <c r="AT28">
         <v>390</v>
       </c>
-      <c r="AQ28">
+      <c r="AU28">
         <v>497</v>
       </c>
-      <c r="AR28" s="2">
-        <f t="shared" ref="AR28" si="105">SUM(G28:J28)</f>
+      <c r="AV28" s="2">
+        <f t="shared" ref="AV28" si="117">SUM(G28:J28)</f>
         <v>1200</v>
       </c>
-      <c r="AS28" s="2">
+      <c r="AW28" s="2">
         <f>SUM(K28:N28)</f>
         <v>1446</v>
       </c>
-      <c r="AT28" s="2">
+      <c r="AX28" s="2">
         <f>SUM(O28:R28)</f>
         <v>1270</v>
       </c>
-      <c r="AU28" s="2">
-        <f t="shared" ref="AU28" si="106">SUM(S28:V28)</f>
+      <c r="AY28" s="2">
+        <f t="shared" ref="AY28" si="118">SUM(S28:V28)</f>
         <v>953</v>
       </c>
-      <c r="AV28" s="2">
-        <f t="shared" si="96"/>
-        <v>1693.0450199999998</v>
-      </c>
-      <c r="AW28" s="2">
-        <f>AW27*0.15</f>
-        <v>1638.210972749999</v>
-      </c>
-      <c r="AX28" s="2">
-        <f t="shared" ref="AX28:BA28" si="107">AX27*0.15</f>
-        <v>1819.0000042098743</v>
-      </c>
-      <c r="AY28" s="2">
-        <f t="shared" si="107"/>
-        <v>2011.0016303250934</v>
-      </c>
       <c r="AZ28" s="2">
-        <f t="shared" si="107"/>
-        <v>2169.908759011541</v>
+        <f t="shared" si="108"/>
+        <v>1942</v>
       </c>
       <c r="BA28" s="2">
-        <f t="shared" si="107"/>
-        <v>2338.6657792932879</v>
+        <f>BA27*0.15</f>
+        <v>1604.8657500000004</v>
       </c>
       <c r="BB28" s="2">
-        <f t="shared" ref="BB28" si="108">BB27*0.15</f>
-        <v>2517.8288593141338</v>
+        <f t="shared" ref="BB28:BE28" si="119">BB27*0.15</f>
+        <v>1784.7479778749992</v>
       </c>
       <c r="BC28" s="2">
-        <f t="shared" ref="BC28" si="109">BC27*0.15</f>
-        <v>2165.4435701177058</v>
+        <f t="shared" si="119"/>
+        <v>1975.7945918446867</v>
       </c>
       <c r="BD28" s="2">
-        <f t="shared" ref="BD28" si="110">BD27*0.15</f>
-        <v>2252.1195101977191</v>
+        <f t="shared" si="119"/>
+        <v>2132.8361952303871</v>
       </c>
       <c r="BE28" s="2">
-        <f t="shared" ref="BE28" si="111">BE27*0.15</f>
-        <v>2342.4813601289575</v>
+        <f t="shared" si="119"/>
+        <v>2299.6543531559478</v>
       </c>
       <c r="BF28" s="2">
-        <f t="shared" ref="BF28" si="112">BF27*0.15</f>
-        <v>2436.693978789398</v>
-      </c>
-    </row>
-    <row r="29" spans="2:125" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF28" si="120">BF27*0.15</f>
+        <v>2476.8031466011416</v>
+      </c>
+      <c r="BG28" s="2">
+        <f t="shared" ref="BG28" si="121">BG27*0.15</f>
+        <v>2140.3493021256827</v>
+      </c>
+      <c r="BH28" s="2">
+        <f t="shared" ref="BH28" si="122">BH27*0.15</f>
+        <v>2226.6862832211923</v>
+      </c>
+      <c r="BI28" s="2">
+        <f t="shared" ref="BI28" si="123">BI27*0.15</f>
+        <v>2316.7196988511569</v>
+      </c>
+      <c r="BJ28" s="2">
+        <f t="shared" ref="BJ28" si="124">BJ27*0.15</f>
+        <v>2410.6157583066843</v>
+      </c>
+    </row>
+    <row r="29" spans="2:129" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
         <v>44</v>
       </c>
       <c r="G29" s="4">
-        <f t="shared" ref="G29:J29" si="113">+G27-G28</f>
+        <f t="shared" ref="G29:J29" si="125">+G27-G28</f>
         <v>2305</v>
       </c>
       <c r="H29" s="4">
-        <f t="shared" si="113"/>
+        <f t="shared" si="125"/>
         <v>1693</v>
       </c>
       <c r="I29" s="4">
-        <f t="shared" si="113"/>
+        <f t="shared" si="125"/>
         <v>2624</v>
       </c>
       <c r="J29" s="4">
-        <f t="shared" si="113"/>
+        <f t="shared" si="125"/>
         <v>2437</v>
       </c>
       <c r="K29" s="4">
-        <f t="shared" ref="K29:X29" si="114">+K27-K28</f>
+        <f t="shared" ref="K29:X29" si="126">+K27-K28</f>
         <v>2956</v>
       </c>
       <c r="L29" s="4">
-        <f t="shared" si="114"/>
+        <f t="shared" si="126"/>
         <v>2525</v>
       </c>
       <c r="M29" s="4">
-        <f t="shared" si="114"/>
+        <f t="shared" si="126"/>
         <v>1949</v>
       </c>
       <c r="N29" s="4">
-        <f t="shared" si="114"/>
+        <f t="shared" si="126"/>
         <v>1863</v>
       </c>
       <c r="O29" s="4">
-        <f t="shared" si="114"/>
+        <f t="shared" si="126"/>
         <v>1871</v>
       </c>
       <c r="P29" s="2">
-        <f t="shared" si="114"/>
+        <f t="shared" si="126"/>
         <v>1975</v>
       </c>
       <c r="Q29" s="2">
-        <f t="shared" si="114"/>
+        <f t="shared" si="126"/>
         <v>2059</v>
       </c>
       <c r="R29" s="2">
-        <f t="shared" si="114"/>
+        <f t="shared" si="126"/>
         <v>2188</v>
       </c>
       <c r="S29" s="2">
-        <f t="shared" si="114"/>
+        <f t="shared" si="126"/>
         <v>1790</v>
       </c>
       <c r="T29" s="2">
-        <f t="shared" si="114"/>
+        <f t="shared" si="126"/>
         <v>2055</v>
       </c>
       <c r="U29" s="2">
-        <f t="shared" si="114"/>
+        <f t="shared" si="126"/>
         <v>1710.3899999999994</v>
       </c>
       <c r="V29" s="2">
-        <f t="shared" si="114"/>
+        <f t="shared" si="126"/>
         <v>2485</v>
       </c>
       <c r="W29" s="2">
-        <f t="shared" si="114"/>
+        <f t="shared" si="126"/>
         <v>1738</v>
       </c>
       <c r="X29" s="2">
-        <f t="shared" si="114"/>
-        <v>2250.6203099999993</v>
+        <f t="shared" si="126"/>
+        <v>2051</v>
       </c>
       <c r="Y29" s="2">
-        <f t="shared" ref="Y29" si="115">+Y27-Y28</f>
-        <v>2317.4076150000001</v>
+        <f t="shared" ref="Y29" si="127">+Y27-Y28</f>
+        <v>1907</v>
       </c>
       <c r="Z29" s="2">
-        <f t="shared" ref="Z29" si="116">+Z27-Z28</f>
-        <v>2458.8938549999993</v>
-      </c>
-      <c r="AM29" s="2">
-        <f t="shared" ref="AM29:AW29" si="117">+AM27-AM28</f>
+        <f t="shared" ref="Z29:AD29" si="128">+Z27-Z28</f>
+        <v>1912</v>
+      </c>
+      <c r="AA29" s="2">
+        <f t="shared" si="128"/>
+        <v>1416.4799999999996</v>
+      </c>
+      <c r="AB29" s="2">
+        <f t="shared" si="128"/>
+        <v>2070.5652</v>
+      </c>
+      <c r="AC29" s="2">
+        <f t="shared" si="128"/>
+        <v>2174.8703999999989</v>
+      </c>
+      <c r="AD29" s="2">
+        <f t="shared" si="128"/>
+        <v>2162.9259999999995</v>
+      </c>
+      <c r="AQ29" s="2">
+        <f t="shared" ref="AQ29:BA29" si="129">+AQ27-AQ28</f>
         <v>3913</v>
       </c>
-      <c r="AN29" s="2">
-        <f t="shared" si="117"/>
+      <c r="AR29" s="2">
+        <f t="shared" si="129"/>
         <v>1346</v>
       </c>
-      <c r="AO29" s="2">
-        <f t="shared" si="117"/>
+      <c r="AS29" s="2">
+        <f t="shared" si="129"/>
         <v>4707</v>
       </c>
-      <c r="AP29" s="2">
-        <f t="shared" si="117"/>
+      <c r="AT29" s="2">
+        <f t="shared" si="129"/>
         <v>5693</v>
       </c>
-      <c r="AQ29" s="2">
-        <f t="shared" si="117"/>
+      <c r="AU29" s="2">
+        <f t="shared" si="129"/>
         <v>6595</v>
       </c>
-      <c r="AR29" s="2">
-        <f t="shared" si="117"/>
+      <c r="AV29" s="2">
+        <f t="shared" si="129"/>
         <v>9059</v>
       </c>
-      <c r="AS29" s="2">
-        <f t="shared" si="117"/>
+      <c r="AW29" s="2">
+        <f t="shared" si="129"/>
         <v>9296</v>
       </c>
-      <c r="AT29" s="2">
-        <f t="shared" si="117"/>
+      <c r="AX29" s="2">
+        <f t="shared" si="129"/>
         <v>8093</v>
       </c>
-      <c r="AU29" s="2">
-        <f t="shared" si="117"/>
+      <c r="AY29" s="2">
+        <f t="shared" si="129"/>
         <v>8430.9999999999927</v>
       </c>
-      <c r="AV29" s="2">
-        <f t="shared" si="117"/>
-        <v>8764.9217800000042</v>
-      </c>
-      <c r="AW29" s="2">
-        <f t="shared" si="117"/>
-        <v>9283.1955122499949</v>
-      </c>
-      <c r="AX29" s="2">
-        <f t="shared" ref="AX29:BA29" si="118">+AX27-AX28</f>
-        <v>10307.666690522621</v>
-      </c>
-      <c r="AY29" s="2">
-        <f t="shared" si="118"/>
-        <v>11395.675905175529</v>
-      </c>
       <c r="AZ29" s="2">
-        <f t="shared" si="118"/>
-        <v>12296.149634398731</v>
+        <f t="shared" si="129"/>
+        <v>7608</v>
       </c>
       <c r="BA29" s="2">
-        <f t="shared" si="118"/>
-        <v>13252.439415995299</v>
+        <f t="shared" si="129"/>
+        <v>9094.2392500000024</v>
       </c>
       <c r="BB29" s="2">
-        <f t="shared" ref="BB29:BF29" si="119">+BB27-BB28</f>
-        <v>14267.696869446758</v>
+        <f t="shared" ref="BB29:BE29" si="130">+BB27-BB28</f>
+        <v>10113.571874624997</v>
       </c>
       <c r="BC29" s="2">
-        <f t="shared" si="119"/>
-        <v>12270.846897333668</v>
+        <f t="shared" si="130"/>
+        <v>11196.169353786558</v>
       </c>
       <c r="BD29" s="2">
-        <f t="shared" si="119"/>
-        <v>12762.010557787076</v>
+        <f t="shared" si="130"/>
+        <v>12086.071772972193</v>
       </c>
       <c r="BE29" s="2">
-        <f t="shared" si="119"/>
-        <v>13274.061040730761</v>
+        <f t="shared" si="130"/>
+        <v>13031.374667883705</v>
       </c>
       <c r="BF29" s="2">
-        <f t="shared" si="119"/>
-        <v>13807.932546473257</v>
+        <f t="shared" ref="BF29:BJ29" si="131">+BF27-BF28</f>
+        <v>14035.217830739803</v>
       </c>
       <c r="BG29" s="2">
-        <f t="shared" ref="BG29:CL29" si="120">BF29*(1+$BI$35)</f>
-        <v>13669.853221008525</v>
+        <f t="shared" si="131"/>
+        <v>12128.646045378868</v>
       </c>
       <c r="BH29" s="2">
-        <f t="shared" si="120"/>
-        <v>13533.15468879844</v>
+        <f t="shared" si="131"/>
+        <v>12617.888938253425</v>
       </c>
       <c r="BI29" s="2">
-        <f t="shared" si="120"/>
-        <v>13397.823141910456</v>
+        <f t="shared" si="131"/>
+        <v>13128.078293489889</v>
       </c>
       <c r="BJ29" s="2">
-        <f t="shared" si="120"/>
-        <v>13263.844910491351</v>
+        <f t="shared" si="131"/>
+        <v>13660.155963737878</v>
       </c>
       <c r="BK29" s="2">
-        <f t="shared" si="120"/>
-        <v>13131.206461386437</v>
+        <f t="shared" ref="BK29:CP29" si="132">BJ29*(1+$BM$35)</f>
+        <v>13523.5544041005</v>
       </c>
       <c r="BL29" s="2">
-        <f t="shared" si="120"/>
-        <v>12999.894396772572</v>
+        <f t="shared" si="132"/>
+        <v>13388.318860059495</v>
       </c>
       <c r="BM29" s="2">
-        <f t="shared" si="120"/>
-        <v>12869.895452804845</v>
+        <f t="shared" si="132"/>
+        <v>13254.435671458899</v>
       </c>
       <c r="BN29" s="2">
-        <f t="shared" si="120"/>
-        <v>12741.196498276797</v>
+        <f t="shared" si="132"/>
+        <v>13121.891314744311</v>
       </c>
       <c r="BO29" s="2">
-        <f t="shared" si="120"/>
-        <v>12613.784533294029</v>
+        <f t="shared" si="132"/>
+        <v>12990.672401596868</v>
       </c>
       <c r="BP29" s="2">
-        <f t="shared" si="120"/>
-        <v>12487.646687961089</v>
+        <f t="shared" si="132"/>
+        <v>12860.765677580899</v>
       </c>
       <c r="BQ29" s="2">
-        <f t="shared" si="120"/>
-        <v>12362.770221081479</v>
+        <f t="shared" si="132"/>
+        <v>12732.158020805091</v>
       </c>
       <c r="BR29" s="2">
-        <f t="shared" si="120"/>
-        <v>12239.142518870663</v>
+        <f t="shared" si="132"/>
+        <v>12604.836440597041</v>
       </c>
       <c r="BS29" s="2">
-        <f t="shared" si="120"/>
-        <v>12116.751093681956</v>
+        <f t="shared" si="132"/>
+        <v>12478.788076191069</v>
       </c>
       <c r="BT29" s="2">
-        <f t="shared" si="120"/>
-        <v>11995.583582745137</v>
+        <f t="shared" si="132"/>
+        <v>12354.000195429158</v>
       </c>
       <c r="BU29" s="2">
-        <f t="shared" si="120"/>
-        <v>11875.627746917686</v>
+        <f t="shared" si="132"/>
+        <v>12230.460193474866</v>
       </c>
       <c r="BV29" s="2">
-        <f t="shared" si="120"/>
-        <v>11756.871469448508</v>
+        <f t="shared" si="132"/>
+        <v>12108.155591540117</v>
       </c>
       <c r="BW29" s="2">
-        <f t="shared" si="120"/>
-        <v>11639.302754754022</v>
+        <f t="shared" si="132"/>
+        <v>11987.074035624715</v>
       </c>
       <c r="BX29" s="2">
-        <f t="shared" si="120"/>
-        <v>11522.909727206483</v>
+        <f t="shared" si="132"/>
+        <v>11867.203295268468</v>
       </c>
       <c r="BY29" s="2">
-        <f t="shared" si="120"/>
-        <v>11407.680629934417</v>
+        <f t="shared" si="132"/>
+        <v>11748.531262315782</v>
       </c>
       <c r="BZ29" s="2">
-        <f t="shared" si="120"/>
-        <v>11293.603823635072</v>
+        <f t="shared" si="132"/>
+        <v>11631.045949692625</v>
       </c>
       <c r="CA29" s="2">
-        <f t="shared" si="120"/>
-        <v>11180.667785398722</v>
+        <f t="shared" si="132"/>
+        <v>11514.735490195699</v>
       </c>
       <c r="CB29" s="2">
-        <f t="shared" si="120"/>
-        <v>11068.861107544735</v>
+        <f t="shared" si="132"/>
+        <v>11399.588135293741</v>
       </c>
       <c r="CC29" s="2">
-        <f t="shared" si="120"/>
-        <v>10958.172496469288</v>
+        <f t="shared" si="132"/>
+        <v>11285.592253940804</v>
       </c>
       <c r="CD29" s="2">
-        <f t="shared" si="120"/>
-        <v>10848.590771504594</v>
+        <f t="shared" si="132"/>
+        <v>11172.736331401396</v>
       </c>
       <c r="CE29" s="2">
-        <f t="shared" si="120"/>
-        <v>10740.104863789547</v>
+        <f t="shared" si="132"/>
+        <v>11061.008968087383</v>
       </c>
       <c r="CF29" s="2">
-        <f t="shared" si="120"/>
-        <v>10632.703815151652</v>
+        <f t="shared" si="132"/>
+        <v>10950.398878406508</v>
       </c>
       <c r="CG29" s="2">
-        <f t="shared" si="120"/>
-        <v>10526.376777000136</v>
+        <f t="shared" si="132"/>
+        <v>10840.894889622443</v>
       </c>
       <c r="CH29" s="2">
-        <f t="shared" si="120"/>
-        <v>10421.113009230134</v>
+        <f t="shared" si="132"/>
+        <v>10732.485940726217</v>
       </c>
       <c r="CI29" s="2">
-        <f t="shared" si="120"/>
-        <v>10316.901879137833</v>
+        <f t="shared" si="132"/>
+        <v>10625.161081318955</v>
       </c>
       <c r="CJ29" s="2">
-        <f t="shared" si="120"/>
-        <v>10213.732860346454</v>
+        <f t="shared" si="132"/>
+        <v>10518.909470505765</v>
       </c>
       <c r="CK29" s="2">
-        <f t="shared" si="120"/>
-        <v>10111.595531742989</v>
+        <f t="shared" si="132"/>
+        <v>10413.720375800707</v>
       </c>
       <c r="CL29" s="2">
-        <f t="shared" si="120"/>
-        <v>10010.47957642556</v>
+        <f t="shared" si="132"/>
+        <v>10309.5831720427</v>
       </c>
       <c r="CM29" s="2">
-        <f t="shared" ref="CM29:DU29" si="121">CL29*(1+$BI$35)</f>
-        <v>9910.3747806613046</v>
+        <f t="shared" si="132"/>
+        <v>10206.487340322272</v>
       </c>
       <c r="CN29" s="2">
-        <f t="shared" si="121"/>
-        <v>9811.2710328546909</v>
+        <f t="shared" si="132"/>
+        <v>10104.42246691905</v>
       </c>
       <c r="CO29" s="2">
-        <f t="shared" si="121"/>
-        <v>9713.1583225261438</v>
+        <f t="shared" si="132"/>
+        <v>10003.378242249859</v>
       </c>
       <c r="CP29" s="2">
-        <f t="shared" si="121"/>
-        <v>9616.0267393008817</v>
+        <f t="shared" si="132"/>
+        <v>9903.34445982736</v>
       </c>
       <c r="CQ29" s="2">
-        <f t="shared" si="121"/>
-        <v>9519.8664719078733</v>
+        <f t="shared" ref="CQ29:DY29" si="133">CP29*(1+$BM$35)</f>
+        <v>9804.3110152290865</v>
       </c>
       <c r="CR29" s="2">
-        <f t="shared" si="121"/>
-        <v>9424.6678071887945</v>
+        <f t="shared" si="133"/>
+        <v>9706.2679050767947</v>
       </c>
       <c r="CS29" s="2">
-        <f t="shared" si="121"/>
-        <v>9330.4211291169067</v>
+        <f t="shared" si="133"/>
+        <v>9609.2052260260261</v>
       </c>
       <c r="CT29" s="2">
-        <f t="shared" si="121"/>
-        <v>9237.1169178257369</v>
+        <f t="shared" si="133"/>
+        <v>9513.1131737657652</v>
       </c>
       <c r="CU29" s="2">
-        <f t="shared" si="121"/>
-        <v>9144.7457486474796</v>
+        <f t="shared" si="133"/>
+        <v>9417.9820420281067</v>
       </c>
       <c r="CV29" s="2">
-        <f t="shared" si="121"/>
-        <v>9053.2982911610052</v>
+        <f t="shared" si="133"/>
+        <v>9323.8022216078261</v>
       </c>
       <c r="CW29" s="2">
-        <f t="shared" si="121"/>
-        <v>8962.7653082493944</v>
+        <f t="shared" si="133"/>
+        <v>9230.564199391747</v>
       </c>
       <c r="CX29" s="2">
-        <f t="shared" si="121"/>
-        <v>8873.1376551669</v>
+        <f t="shared" si="133"/>
+        <v>9138.2585573978304</v>
       </c>
       <c r="CY29" s="2">
-        <f t="shared" si="121"/>
-        <v>8784.4062786152317</v>
+        <f t="shared" si="133"/>
+        <v>9046.8759718238525</v>
       </c>
       <c r="CZ29" s="2">
-        <f t="shared" si="121"/>
-        <v>8696.5622158290789</v>
+        <f t="shared" si="133"/>
+        <v>8956.4072121056142</v>
       </c>
       <c r="DA29" s="2">
-        <f t="shared" si="121"/>
-        <v>8609.5965936707889</v>
+        <f t="shared" si="133"/>
+        <v>8866.8431399845576</v>
       </c>
       <c r="DB29" s="2">
-        <f t="shared" si="121"/>
-        <v>8523.5006277340817</v>
+        <f t="shared" si="133"/>
+        <v>8778.1747085847128</v>
       </c>
       <c r="DC29" s="2">
-        <f t="shared" si="121"/>
-        <v>8438.2656214567414</v>
+        <f t="shared" si="133"/>
+        <v>8690.3929614988647</v>
       </c>
       <c r="DD29" s="2">
-        <f t="shared" si="121"/>
-        <v>8353.8829652421737</v>
+        <f t="shared" si="133"/>
+        <v>8603.4890318838752</v>
       </c>
       <c r="DE29" s="2">
-        <f t="shared" si="121"/>
-        <v>8270.3441355897521</v>
+        <f t="shared" si="133"/>
+        <v>8517.4541415650365</v>
       </c>
       <c r="DF29" s="2">
-        <f t="shared" si="121"/>
-        <v>8187.6406942338544</v>
+        <f t="shared" si="133"/>
+        <v>8432.2796001493862</v>
       </c>
       <c r="DG29" s="2">
-        <f t="shared" si="121"/>
-        <v>8105.7642872915158</v>
+        <f t="shared" si="133"/>
+        <v>8347.9568041478924</v>
       </c>
       <c r="DH29" s="2">
-        <f t="shared" si="121"/>
-        <v>8024.7066444186003</v>
+        <f t="shared" si="133"/>
+        <v>8264.4772361064133</v>
       </c>
       <c r="DI29" s="2">
-        <f t="shared" si="121"/>
-        <v>7944.4595779744141</v>
+        <f t="shared" si="133"/>
+        <v>8181.8324637453488</v>
       </c>
       <c r="DJ29" s="2">
-        <f t="shared" si="121"/>
-        <v>7865.0149821946698</v>
+        <f t="shared" si="133"/>
+        <v>8100.0141391078951</v>
       </c>
       <c r="DK29" s="2">
-        <f t="shared" si="121"/>
-        <v>7786.364832372723</v>
+        <f t="shared" si="133"/>
+        <v>8019.0139977168164</v>
       </c>
       <c r="DL29" s="2">
-        <f t="shared" si="121"/>
-        <v>7708.501184048996</v>
+        <f t="shared" si="133"/>
+        <v>7938.8238577396478</v>
       </c>
       <c r="DM29" s="2">
-        <f t="shared" si="121"/>
-        <v>7631.4161722085064</v>
+        <f t="shared" si="133"/>
+        <v>7859.435619162251</v>
       </c>
       <c r="DN29" s="2">
-        <f t="shared" si="121"/>
-        <v>7555.102010486421</v>
+        <f t="shared" si="133"/>
+        <v>7780.8412629706281</v>
       </c>
       <c r="DO29" s="2">
-        <f t="shared" si="121"/>
-        <v>7479.5509903815564</v>
+        <f t="shared" si="133"/>
+        <v>7703.0328503409219</v>
       </c>
       <c r="DP29" s="2">
-        <f t="shared" si="121"/>
-        <v>7404.755480477741</v>
+        <f t="shared" si="133"/>
+        <v>7626.0025218375122</v>
       </c>
       <c r="DQ29" s="2">
-        <f t="shared" si="121"/>
-        <v>7330.7079256729639</v>
+        <f t="shared" si="133"/>
+        <v>7549.7424966191365</v>
       </c>
       <c r="DR29" s="2">
-        <f t="shared" si="121"/>
-        <v>7257.4008464162343</v>
+        <f t="shared" si="133"/>
+        <v>7474.2450716529447</v>
       </c>
       <c r="DS29" s="2">
-        <f t="shared" si="121"/>
-        <v>7184.8268379520723</v>
+        <f t="shared" si="133"/>
+        <v>7399.502620936415</v>
       </c>
       <c r="DT29" s="2">
-        <f t="shared" si="121"/>
-        <v>7112.9785695725514</v>
+        <f t="shared" si="133"/>
+        <v>7325.5075947270507</v>
       </c>
       <c r="DU29" s="2">
-        <f t="shared" si="121"/>
-        <v>7041.848783876826</v>
-      </c>
-    </row>
-    <row r="30" spans="2:125" x14ac:dyDescent="0.2">
+        <f t="shared" si="133"/>
+        <v>7252.2525187797801</v>
+      </c>
+      <c r="DV29" s="2">
+        <f t="shared" si="133"/>
+        <v>7179.7299935919818</v>
+      </c>
+      <c r="DW29" s="2">
+        <f t="shared" si="133"/>
+        <v>7107.9326936560619</v>
+      </c>
+      <c r="DX29" s="2">
+        <f t="shared" si="133"/>
+        <v>7036.8533667195015</v>
+      </c>
+      <c r="DY29" s="2">
+        <f t="shared" si="133"/>
+        <v>6966.4848330523064</v>
+      </c>
+    </row>
+    <row r="30" spans="2:129" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
         <v>45</v>
       </c>
       <c r="G30" s="7" t="e">
-        <f t="shared" ref="G30:O30" si="122">+G29/G31</f>
+        <f t="shared" ref="G30:O30" si="134">+G29/G31</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H30" s="7">
-        <f t="shared" si="122"/>
+        <f t="shared" si="134"/>
         <v>0.94408064779657819</v>
       </c>
       <c r="I30" s="7">
-        <f t="shared" si="122"/>
+        <f t="shared" si="134"/>
         <v>1.4667420160659677</v>
       </c>
       <c r="J30" s="7">
-        <f t="shared" si="122"/>
+        <f t="shared" si="134"/>
         <v>1.3675645342312008</v>
       </c>
       <c r="K30" s="7">
-        <f t="shared" si="122"/>
+        <f t="shared" si="134"/>
         <v>1.6657819313377762</v>
       </c>
       <c r="L30" s="7">
-        <f t="shared" si="122"/>
+        <f t="shared" si="134"/>
         <v>1.4302197213988626</v>
       </c>
       <c r="M30" s="7">
-        <f t="shared" si="122"/>
+        <f t="shared" si="134"/>
         <v>1.1050926684557563</v>
       </c>
       <c r="N30" s="7">
-        <f t="shared" si="122"/>
+        <f t="shared" si="134"/>
         <v>1.0621436716077537</v>
       </c>
       <c r="O30" s="7">
-        <f t="shared" si="122"/>
+        <f t="shared" si="134"/>
         <v>1.0679223744292237</v>
       </c>
       <c r="P30" s="1">
-        <f t="shared" ref="P30:X30" si="123">+P29/P31</f>
+        <f t="shared" ref="P30:X30" si="135">+P29/P31</f>
         <v>1.1279268989149058</v>
       </c>
       <c r="Q30" s="1">
-        <f t="shared" si="123"/>
+        <f t="shared" si="135"/>
         <v>1.1779176201372998</v>
       </c>
       <c r="R30" s="1">
-        <f t="shared" si="123"/>
+        <f t="shared" si="135"/>
         <v>1.2517162471395882</v>
       </c>
       <c r="S30" s="1">
-        <f t="shared" si="123"/>
+        <f t="shared" si="135"/>
         <v>1.0228571428571429</v>
       </c>
       <c r="T30" s="1">
-        <f t="shared" si="123"/>
+        <f t="shared" si="135"/>
         <v>1.1736150770988008</v>
       </c>
       <c r="U30" s="1">
-        <f t="shared" si="123"/>
+        <f t="shared" si="135"/>
         <v>0.97870962241294723</v>
       </c>
       <c r="V30" s="1">
-        <f t="shared" si="123"/>
+        <f t="shared" si="135"/>
         <v>1.4232531500572738</v>
       </c>
       <c r="W30" s="1">
-        <f t="shared" si="123"/>
+        <f t="shared" si="135"/>
         <v>0.99472304575268133</v>
       </c>
       <c r="X30" s="1">
-        <f t="shared" si="123"/>
-        <v>1.2881150112750537</v>
+        <f t="shared" si="135"/>
+        <v>1.1714410552679151</v>
       </c>
       <c r="Y30" s="1">
-        <f t="shared" ref="Y30" si="124">+Y29/Y31</f>
-        <v>1.3263399085404242</v>
+        <f t="shared" ref="Y30" si="136">+Y29/Y31</f>
+        <v>1.0901123324459616</v>
       </c>
       <c r="Z30" s="1">
-        <f t="shared" ref="Z30" si="125">+Z29/Z31</f>
-        <v>1.407317827749224</v>
-      </c>
-      <c r="AM30" s="1">
-        <f>+AM29/AM31</f>
+        <f t="shared" ref="Z30:AB30" si="137">+Z29/Z31</f>
+        <v>1.0938215102974829</v>
+      </c>
+      <c r="AA30" s="1">
+        <f t="shared" si="137"/>
+        <v>0.81077321897825649</v>
+      </c>
+      <c r="AB30" s="1">
+        <f t="shared" si="137"/>
+        <v>1.1851623830257807</v>
+      </c>
+      <c r="AC30" s="1">
+        <f t="shared" ref="AC30:AD30" si="138">+AC29/AC31</f>
+        <v>1.2448652116997967</v>
+      </c>
+      <c r="AD30" s="1">
+        <f t="shared" si="138"/>
+        <v>1.2380284052240516</v>
+      </c>
+      <c r="AQ30" s="1">
+        <f>+AQ29/AQ31</f>
         <v>2.6385704652730952</v>
       </c>
-      <c r="AN30" s="1">
-        <f>+AN29/AN31</f>
+      <c r="AR30" s="1">
+        <f>+AR29/AR31</f>
         <v>0.76958261863922239</v>
       </c>
-      <c r="AO30" s="1">
-        <f>+AO29/AO31</f>
+      <c r="AS30" s="1">
+        <f>+AS29/AS31</f>
         <v>2.659322033898305</v>
       </c>
-      <c r="AP30" s="1">
-        <f t="shared" ref="AP30:AW30" si="126">+AP29/AP31</f>
+      <c r="AT30" s="1">
+        <f t="shared" ref="AT30:BA30" si="139">+AT29/AT31</f>
         <v>3.1965188096574959</v>
       </c>
-      <c r="AQ30" s="1">
-        <f t="shared" si="126"/>
+      <c r="AU30" s="1">
+        <f t="shared" si="139"/>
         <v>3.692609182530795</v>
       </c>
-      <c r="AR30" s="1">
-        <f t="shared" si="126"/>
+      <c r="AV30" s="1">
+        <f t="shared" si="139"/>
         <v>5.0662922391419682</v>
       </c>
-      <c r="AS30" s="1">
-        <f t="shared" si="126"/>
+      <c r="AW30" s="1">
+        <f t="shared" si="139"/>
         <v>5.2686032675428587</v>
       </c>
-      <c r="AT30" s="1">
-        <f t="shared" si="126"/>
+      <c r="AX30" s="1">
+        <f t="shared" si="139"/>
         <v>4.625232176025146</v>
       </c>
-      <c r="AU30" s="1">
-        <f t="shared" si="126"/>
+      <c r="AY30" s="1">
+        <f t="shared" si="139"/>
         <v>4.8214357453331438</v>
       </c>
-      <c r="AV30" s="1">
-        <f t="shared" si="126"/>
-        <v>5.0164957933173868</v>
-      </c>
-      <c r="AW30" s="1">
-        <f t="shared" si="126"/>
-        <v>5.3131234259280431</v>
-      </c>
-      <c r="AX30" s="1">
-        <f t="shared" ref="AX30:BA30" si="127">+AX29/AX31</f>
-        <v>5.8994669764097374</v>
-      </c>
-      <c r="AY30" s="1">
-        <f t="shared" si="127"/>
-        <v>6.5221757449980702</v>
-      </c>
       <c r="AZ30" s="1">
-        <f t="shared" si="127"/>
-        <v>7.0375508718986337</v>
+        <f t="shared" si="139"/>
+        <v>4.3502773816453519</v>
       </c>
       <c r="BA30" s="1">
-        <f t="shared" si="127"/>
-        <v>7.5848716337927096</v>
+        <f t="shared" si="139"/>
+        <v>5.2001134743094637</v>
       </c>
       <c r="BB30" s="1">
-        <f t="shared" ref="BB30:BF30" si="128">+BB29/BB31</f>
-        <v>8.1659418215489499</v>
+        <f t="shared" ref="BB30:BE30" si="140">+BB29/BB31</f>
+        <v>5.7829709481894982</v>
       </c>
       <c r="BC30" s="1">
-        <f t="shared" si="128"/>
-        <v>7.0230691597701878</v>
+        <f t="shared" si="140"/>
+        <v>6.4020034569990161</v>
       </c>
       <c r="BD30" s="1">
-        <f t="shared" si="128"/>
-        <v>7.304180674320965</v>
+        <f t="shared" si="140"/>
+        <v>6.9108523484362863</v>
       </c>
       <c r="BE30" s="1">
-        <f t="shared" si="128"/>
-        <v>7.5972465062961509</v>
+        <f t="shared" si="140"/>
+        <v>7.4513793992429926</v>
       </c>
       <c r="BF30" s="1">
-        <f t="shared" si="128"/>
-        <v>7.9028013338178686</v>
-      </c>
-    </row>
-    <row r="31" spans="2:125" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF30:BJ30" si="141">+BF29/BF31</f>
+        <v>8.0253799520942302</v>
+      </c>
+      <c r="BG30" s="1">
+        <f t="shared" si="141"/>
+        <v>6.9351964460034212</v>
+      </c>
+      <c r="BH30" s="1">
+        <f t="shared" si="141"/>
+        <v>7.214947010015373</v>
+      </c>
+      <c r="BI30" s="1">
+        <f t="shared" si="141"/>
+        <v>7.5066748244792807</v>
+      </c>
+      <c r="BJ30" s="1">
+        <f t="shared" si="141"/>
+        <v>7.8109184435852717</v>
+      </c>
+    </row>
+    <row r="31" spans="2:129" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
         <v>1</v>
       </c>
@@ -5914,94 +6322,106 @@
         <v>1747.22</v>
       </c>
       <c r="X31" s="2">
-        <f>+W31</f>
-        <v>1747.22</v>
+        <v>1750.835</v>
       </c>
       <c r="Y31" s="2">
-        <f t="shared" ref="Y31:Z31" si="129">+X31</f>
-        <v>1747.22</v>
+        <v>1749.3610000000001</v>
       </c>
       <c r="Z31" s="2">
-        <f t="shared" si="129"/>
-        <v>1747.22</v>
-      </c>
-      <c r="AM31" s="2">
+        <v>1748</v>
+      </c>
+      <c r="AA31" s="2">
+        <v>1747.0730000000001</v>
+      </c>
+      <c r="AB31" s="2">
+        <f>+AA31</f>
+        <v>1747.0730000000001</v>
+      </c>
+      <c r="AC31" s="2">
+        <f t="shared" ref="AC31:AD31" si="142">+AB31</f>
+        <v>1747.0730000000001</v>
+      </c>
+      <c r="AD31" s="2">
+        <f t="shared" si="142"/>
+        <v>1747.0730000000001</v>
+      </c>
+      <c r="AQ31" s="2">
         <v>1483</v>
       </c>
-      <c r="AN31" s="2">
+      <c r="AR31" s="2">
         <v>1749</v>
       </c>
-      <c r="AO31" s="2">
+      <c r="AS31" s="2">
         <v>1770</v>
       </c>
-      <c r="AP31" s="2">
+      <c r="AT31" s="2">
         <v>1781</v>
       </c>
-      <c r="AQ31" s="2">
+      <c r="AU31" s="2">
         <v>1786</v>
       </c>
-      <c r="AR31" s="2">
+      <c r="AV31" s="2">
         <f>AVERAGE(G31:J31)</f>
         <v>1788.0926666666667</v>
       </c>
-      <c r="AS31" s="2">
+      <c r="AW31" s="2">
         <f>AVERAGE(K31:N31)</f>
         <v>1764.4145000000001</v>
       </c>
-      <c r="AT31" s="2">
+      <c r="AX31" s="2">
         <f>AVERAGE(O31:R31)</f>
         <v>1749.75</v>
       </c>
-      <c r="AU31" s="2">
+      <c r="AY31" s="2">
         <f>AVERAGE(S31:V31)</f>
         <v>1748.6492499999999</v>
       </c>
-      <c r="AV31" s="2">
+      <c r="AZ31" s="2">
         <f>AVERAGE(W31:Z31)</f>
-        <v>1747.22</v>
-      </c>
-      <c r="AW31" s="2">
-        <f>+AV31</f>
-        <v>1747.22</v>
-      </c>
-      <c r="AX31" s="2">
-        <f t="shared" ref="AX31:BA31" si="130">+AW31</f>
-        <v>1747.22</v>
-      </c>
-      <c r="AY31" s="2">
-        <f t="shared" si="130"/>
-        <v>1747.22</v>
-      </c>
-      <c r="AZ31" s="2">
-        <f t="shared" si="130"/>
-        <v>1747.22</v>
+        <v>1748.854</v>
       </c>
       <c r="BA31" s="2">
-        <f t="shared" si="130"/>
-        <v>1747.22</v>
+        <f>+AZ31</f>
+        <v>1748.854</v>
       </c>
       <c r="BB31" s="2">
-        <f t="shared" ref="BB31:BF31" si="131">+BA31</f>
-        <v>1747.22</v>
+        <f t="shared" ref="BB31:BE31" si="143">+BA31</f>
+        <v>1748.854</v>
       </c>
       <c r="BC31" s="2">
-        <f t="shared" si="131"/>
-        <v>1747.22</v>
+        <f t="shared" si="143"/>
+        <v>1748.854</v>
       </c>
       <c r="BD31" s="2">
-        <f t="shared" si="131"/>
-        <v>1747.22</v>
+        <f t="shared" si="143"/>
+        <v>1748.854</v>
       </c>
       <c r="BE31" s="2">
-        <f t="shared" si="131"/>
-        <v>1747.22</v>
+        <f t="shared" si="143"/>
+        <v>1748.854</v>
       </c>
       <c r="BF31" s="2">
-        <f t="shared" si="131"/>
-        <v>1747.22</v>
-      </c>
-    </row>
-    <row r="33" spans="2:61" s="10" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BF31:BJ31" si="144">+BE31</f>
+        <v>1748.854</v>
+      </c>
+      <c r="BG31" s="2">
+        <f t="shared" si="144"/>
+        <v>1748.854</v>
+      </c>
+      <c r="BH31" s="2">
+        <f t="shared" si="144"/>
+        <v>1748.854</v>
+      </c>
+      <c r="BI31" s="2">
+        <f t="shared" si="144"/>
+        <v>1748.854</v>
+      </c>
+      <c r="BJ31" s="2">
+        <f t="shared" si="144"/>
+        <v>1748.854</v>
+      </c>
+    </row>
+    <row r="33" spans="2:65" s="10" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B33" s="5" t="s">
         <v>46</v>
       </c>
@@ -6030,170 +6450,186 @@
         <v>-0.12033484478549006</v>
       </c>
       <c r="O33" s="13">
-        <f t="shared" ref="O33" si="132">+O19/K19-1</f>
+        <f t="shared" ref="O33" si="145">+O19/K19-1</f>
         <v>-0.18083228247162675</v>
       </c>
       <c r="P33" s="13">
-        <f t="shared" ref="P33:Z33" si="133">+P19/L19-1</f>
+        <f t="shared" ref="P33:Z33" si="146">+P19/L19-1</f>
         <v>-0.11388469396819756</v>
       </c>
       <c r="Q33" s="13">
-        <f t="shared" si="133"/>
+        <f t="shared" si="146"/>
         <v>-2.57518977611223E-2</v>
       </c>
       <c r="R33" s="13">
-        <f t="shared" si="133"/>
+        <f t="shared" si="146"/>
         <v>1.4770023790642295E-2</v>
       </c>
       <c r="S33" s="13">
-        <f t="shared" si="133"/>
+        <f t="shared" si="146"/>
         <v>2.2557471264367912E-2</v>
       </c>
       <c r="T33" s="13">
-        <f t="shared" si="133"/>
+        <f t="shared" si="146"/>
         <v>3.9899749373433657E-2</v>
       </c>
       <c r="U33" s="13">
-        <f t="shared" si="133"/>
+        <f t="shared" si="146"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="V33" s="13">
-        <f t="shared" si="133"/>
+        <f t="shared" si="146"/>
         <v>7.1993748168408755E-2</v>
       </c>
       <c r="W33" s="13">
-        <f t="shared" si="133"/>
+        <f t="shared" si="146"/>
         <v>3.9563218852245008E-2</v>
       </c>
       <c r="X33" s="13">
-        <f t="shared" si="133"/>
-        <v>4.4633182300202412E-2</v>
+        <f t="shared" si="146"/>
+        <v>7.413477296828308E-2</v>
       </c>
       <c r="Y33" s="13">
-        <f t="shared" si="133"/>
-        <v>8.4203824268411775E-2</v>
+        <f t="shared" si="146"/>
+        <v>0.11021162279952246</v>
       </c>
       <c r="Z33" s="13">
-        <f t="shared" si="133"/>
-        <v>4.6162748314197311E-2</v>
-      </c>
-      <c r="AL33" s="13">
-        <f t="shared" ref="AL33:AQ33" si="134">+AL19/AK19-1</f>
+        <f t="shared" si="146"/>
+        <v>4.4195370876617401E-2</v>
+      </c>
+      <c r="AA33" s="13">
+        <f t="shared" ref="AA33:AD33" si="147">+AA19/W19-1</f>
+        <v>7.781424985518437E-2</v>
+      </c>
+      <c r="AB33" s="13">
+        <f t="shared" si="147"/>
+        <v>8.3871836295099644E-3</v>
+      </c>
+      <c r="AC33" s="13">
+        <f t="shared" si="147"/>
+        <v>6.9839035975018948E-3</v>
+      </c>
+      <c r="AD33" s="13">
+        <f t="shared" si="147"/>
+        <v>7.0468627279867135E-3</v>
+      </c>
+      <c r="AP33" s="13">
+        <f t="shared" ref="AP33:AU33" si="148">+AP19/AO19-1</f>
         <v>7.8036252284288121E-3</v>
       </c>
-      <c r="AM33" s="13">
-        <f t="shared" si="134"/>
+      <c r="AQ33" s="13">
+        <f t="shared" si="148"/>
         <v>2.1955403087478453E-2</v>
       </c>
-      <c r="AN33" s="13">
-        <f t="shared" si="134"/>
+      <c r="AR33" s="13">
+        <f t="shared" si="148"/>
         <v>0.31348007480938</v>
       </c>
-      <c r="AO33" s="13">
-        <f t="shared" si="134"/>
+      <c r="AS33" s="13">
+        <f t="shared" si="148"/>
         <v>0.11639284410368744</v>
       </c>
-      <c r="AP33" s="13">
-        <f t="shared" si="134"/>
+      <c r="AT33" s="13">
+        <f t="shared" si="148"/>
         <v>4.3364510432337022E-2</v>
       </c>
-      <c r="AQ33" s="13">
-        <f t="shared" si="134"/>
+      <c r="AU33" s="13">
+        <f t="shared" si="148"/>
         <v>8.4754262788365065E-2</v>
       </c>
-      <c r="AR33" s="13">
-        <f t="shared" ref="AR33:AV33" si="135">+AR19/AQ19-1</f>
+      <c r="AV33" s="13">
+        <f t="shared" ref="AV33:AZ33" si="149">+AV19/AU19-1</f>
         <v>0.2446544151641239</v>
       </c>
-      <c r="AS33" s="13">
-        <f t="shared" si="135"/>
+      <c r="AW33" s="13">
+        <f t="shared" si="149"/>
         <v>1.3348810214741658E-2</v>
       </c>
-      <c r="AT33" s="13">
-        <f t="shared" si="135"/>
+      <c r="AX33" s="13">
+        <f t="shared" si="149"/>
         <v>-8.1443298969072209E-2</v>
       </c>
-      <c r="AU33" s="13">
-        <f t="shared" si="135"/>
+      <c r="AY33" s="13">
+        <f t="shared" si="149"/>
         <v>4.6060606060605913E-2</v>
       </c>
-      <c r="AV33" s="13">
-        <f t="shared" si="135"/>
-        <v>4.3761593446156599E-2</v>
-      </c>
-      <c r="AW33" s="13">
-        <f t="shared" ref="AW33" si="136">+AW19/AV19-1</f>
-        <v>4.5219908792787811E-2</v>
-      </c>
-      <c r="AX33" s="13">
-        <f t="shared" ref="AX33" si="137">+AX19/AW19-1</f>
-        <v>4.5940943198117923E-2</v>
-      </c>
-      <c r="AY33" s="13">
-        <f t="shared" ref="AY33" si="138">+AY19/AX19-1</f>
-        <v>4.5288204815356226E-2</v>
-      </c>
       <c r="AZ33" s="13">
-        <f t="shared" ref="AZ33" si="139">+AZ19/AY19-1</f>
-        <v>3.4176282958429116E-2</v>
+        <f t="shared" si="149"/>
+        <v>5.6893123328040307E-2</v>
       </c>
       <c r="BA33" s="13">
-        <f t="shared" ref="BA33" si="140">+BA19/AZ19-1</f>
-        <v>3.4240183398719592E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="2:61" x14ac:dyDescent="0.2">
+        <f t="shared" ref="BA33" si="150">+BA19/AZ19-1</f>
+        <v>4.533252120555864E-2</v>
+      </c>
+      <c r="BB33" s="13">
+        <f t="shared" ref="BB33" si="151">+BB19/BA19-1</f>
+        <v>4.6056800647423568E-2</v>
+      </c>
+      <c r="BC33" s="13">
+        <f t="shared" ref="BC33" si="152">+BC19/BB19-1</f>
+        <v>4.5390645919119343E-2</v>
+      </c>
+      <c r="BD33" s="13">
+        <f t="shared" ref="BD33" si="153">+BD19/BC19-1</f>
+        <v>3.4201680013888458E-2</v>
+      </c>
+      <c r="BE33" s="13">
+        <f t="shared" ref="BE33" si="154">+BE19/BD19-1</f>
+        <v>3.4265864289181547E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14"/>
       <c r="K34" s="14">
-        <f t="shared" ref="K34" si="141">+K18/G18-1</f>
+        <f t="shared" ref="K34" si="155">+K18/G18-1</f>
         <v>0.1489795918367347</v>
       </c>
       <c r="L34" s="14">
-        <f t="shared" ref="L34" si="142">+L18/H18-1</f>
+        <f t="shared" ref="L34" si="156">+L18/H18-1</f>
         <v>0.1287878787878789</v>
       </c>
       <c r="M34" s="14">
-        <f t="shared" ref="M34" si="143">+M18/I18-1</f>
+        <f t="shared" ref="M34" si="157">+M18/I18-1</f>
         <v>4.1034790365744866E-2</v>
       </c>
       <c r="N34" s="14">
-        <f t="shared" ref="N34" si="144">+N18/J18-1</f>
+        <f t="shared" ref="N34" si="158">+N18/J18-1</f>
         <v>8.5397096498718961E-2</v>
       </c>
       <c r="O34" s="14">
-        <f t="shared" ref="O34" si="145">+O18/K18-1</f>
+        <f t="shared" ref="O34" si="159">+O18/K18-1</f>
         <v>0.1660746003552398</v>
       </c>
       <c r="P34" s="14">
-        <f t="shared" ref="P34" si="146">+P18/L18-1</f>
+        <f t="shared" ref="P34" si="160">+P18/L18-1</f>
         <v>0.19463087248322153</v>
       </c>
       <c r="Q34" s="14">
-        <f t="shared" ref="Q34" si="147">+Q18/M18-1</f>
+        <f t="shared" ref="Q34" si="161">+Q18/M18-1</f>
         <v>0.26135389888603267</v>
       </c>
       <c r="R34" s="14">
-        <f t="shared" ref="R34" si="148">+R18/N18-1</f>
+        <f t="shared" ref="R34" si="162">+R18/N18-1</f>
         <v>0.22108575924468932</v>
       </c>
       <c r="S34" s="14">
-        <f t="shared" ref="S34" si="149">+S18/O18-1</f>
+        <f t="shared" ref="S34" si="163">+S18/O18-1</f>
         <v>0.19497334348819506</v>
       </c>
       <c r="T34" s="14">
-        <f t="shared" ref="T34" si="150">+T18/P18-1</f>
+        <f t="shared" ref="T34" si="164">+T18/P18-1</f>
         <v>0.15730337078651679</v>
       </c>
       <c r="U34" s="14">
-        <f t="shared" ref="U34:V34" si="151">+U18/Q18-1</f>
+        <f t="shared" ref="U34:V34" si="165">+U18/Q18-1</f>
         <v>0.171875</v>
       </c>
       <c r="V34" s="14">
-        <f t="shared" si="151"/>
+        <f t="shared" si="165"/>
         <v>0.20038659793814428</v>
       </c>
       <c r="W34" s="14">
@@ -6201,35 +6637,51 @@
         <v>0.1644359464627152</v>
       </c>
       <c r="X34" s="14">
-        <f t="shared" ref="X34:Z34" si="152">+X18/T18-1</f>
-        <v>0.14999999999999991</v>
+        <f t="shared" ref="X34:Z34" si="166">+X18/T18-1</f>
+        <v>0.2020631067961165</v>
       </c>
       <c r="Y34" s="14">
-        <f t="shared" si="152"/>
-        <v>0.14999999999999991</v>
+        <f t="shared" si="166"/>
+        <v>0.19246376811594201</v>
       </c>
       <c r="Z34" s="14">
-        <f t="shared" si="152"/>
-        <v>0.14999999999999991</v>
-      </c>
-      <c r="AL34" s="14"/>
-      <c r="AM34" s="14"/>
-      <c r="AN34" s="14"/>
-      <c r="AO34" s="14"/>
+        <f t="shared" si="166"/>
+        <v>0.14492753623188404</v>
+      </c>
+      <c r="AA34" s="14">
+        <f t="shared" ref="AA34" si="167">+AA18/W18-1</f>
+        <v>0.13847837985769029</v>
+      </c>
+      <c r="AB34" s="14">
+        <f t="shared" ref="AB34" si="168">+AB18/X18-1</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AC34" s="14">
+        <f t="shared" ref="AC34" si="169">+AC18/Y18-1</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AD34" s="14">
+        <f t="shared" ref="AD34" si="170">+AD18/Z18-1</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
       <c r="AP34" s="14"/>
       <c r="AQ34" s="14"/>
       <c r="AR34" s="14"/>
       <c r="AS34" s="14"/>
       <c r="AT34" s="14"/>
       <c r="AU34" s="14"/>
-      <c r="BH34" t="s">
+      <c r="AV34" s="14"/>
+      <c r="AW34" s="14"/>
+      <c r="AX34" s="14"/>
+      <c r="AY34" s="14"/>
+      <c r="BL34" t="s">
         <v>140</v>
       </c>
-      <c r="BI34" s="14">
+      <c r="BM34" s="14">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="35" spans="2:61" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
         <v>136</v>
       </c>
@@ -6239,39 +6691,39 @@
       <c r="L35" s="14"/>
       <c r="M35" s="14"/>
       <c r="N35" s="14">
-        <f t="shared" ref="N35" si="153">+N17/J17-1</f>
+        <f t="shared" ref="N35" si="171">+N17/J17-1</f>
         <v>-0.10766961651917406</v>
       </c>
       <c r="O35" s="14">
-        <f t="shared" ref="O35" si="154">+O17/K17-1</f>
+        <f t="shared" ref="O35" si="172">+O17/K17-1</f>
         <v>-3.231017770597755E-3</v>
       </c>
       <c r="P35" s="14">
-        <f t="shared" ref="P35" si="155">+P17/L17-1</f>
+        <f t="shared" ref="P35" si="173">+P17/L17-1</f>
         <v>9.4946401225114885E-2</v>
       </c>
       <c r="Q35" s="14">
-        <f t="shared" ref="Q35" si="156">+Q17/M17-1</f>
+        <f t="shared" ref="Q35" si="174">+Q17/M17-1</f>
         <v>0.10891089108910901</v>
       </c>
       <c r="R35" s="14">
-        <f t="shared" ref="R35" si="157">+R17/N17-1</f>
+        <f t="shared" ref="R35" si="175">+R17/N17-1</f>
         <v>0.11900826446280988</v>
       </c>
       <c r="S35" s="14">
-        <f t="shared" ref="S35:V35" si="158">+S17/O17-1</f>
+        <f t="shared" ref="S35:V35" si="176">+S17/O17-1</f>
         <v>0.11669367909238249</v>
       </c>
       <c r="T35" s="14">
-        <f t="shared" si="158"/>
+        <f t="shared" si="176"/>
         <v>1.2587412587412583E-2</v>
       </c>
       <c r="U35" s="14">
-        <f t="shared" si="158"/>
+        <f t="shared" si="176"/>
         <v>4.0178571428571397E-2</v>
       </c>
       <c r="V35" s="14">
-        <f t="shared" si="158"/>
+        <f t="shared" si="176"/>
         <v>7.0901033973412186E-2</v>
       </c>
       <c r="W35" s="14">
@@ -6279,35 +6731,51 @@
         <v>3.0478955007256836E-2</v>
       </c>
       <c r="X35" s="14">
-        <f t="shared" ref="X35:Z35" si="159">+X17/T17-1</f>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" ref="X35:Z35" si="177">+X17/T17-1</f>
+        <v>4.5580110497237536E-2</v>
       </c>
       <c r="Y35" s="14">
-        <f t="shared" si="159"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="177"/>
+        <v>6.5808297567954144E-2</v>
       </c>
       <c r="Z35" s="14">
-        <f t="shared" si="159"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AL35" s="14"/>
-      <c r="AM35" s="14"/>
-      <c r="AN35" s="14"/>
-      <c r="AO35" s="14"/>
+        <f t="shared" si="177"/>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="AA35" s="14">
+        <f t="shared" ref="AA35" si="178">+AA17/W17-1</f>
+        <v>9.4366197183098688E-2</v>
+      </c>
+      <c r="AB35" s="14">
+        <f t="shared" ref="AB35" si="179">+AB17/X17-1</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AC35" s="14">
+        <f t="shared" ref="AC35" si="180">+AC17/Y17-1</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AD35" s="14">
+        <f t="shared" ref="AD35" si="181">+AD17/Z17-1</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
       <c r="AP35" s="14"/>
       <c r="AQ35" s="14"/>
       <c r="AR35" s="14"/>
       <c r="AS35" s="14"/>
       <c r="AT35" s="14"/>
       <c r="AU35" s="14"/>
-      <c r="BH35" t="s">
+      <c r="AV35" s="14"/>
+      <c r="AW35" s="14"/>
+      <c r="AX35" s="14"/>
+      <c r="AY35" s="14"/>
+      <c r="BL35" t="s">
         <v>141</v>
       </c>
-      <c r="BI35" s="14">
+      <c r="BM35" s="14">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="36" spans="2:61" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
         <v>137</v>
       </c>
@@ -6319,31 +6787,31 @@
       <c r="N36" s="14"/>
       <c r="O36" s="14"/>
       <c r="P36" s="14">
-        <f t="shared" ref="P36:P37" si="160">+P22/L22-1</f>
+        <f t="shared" ref="P36:P37" si="182">+P22/L22-1</f>
         <v>-1.4145810663764968E-2</v>
       </c>
       <c r="Q36" s="14">
-        <f t="shared" ref="Q36:Q37" si="161">+Q22/M22-1</f>
+        <f t="shared" ref="Q36:Q37" si="183">+Q22/M22-1</f>
         <v>-1.8674478213108747E-2</v>
       </c>
       <c r="R36" s="14">
-        <f t="shared" ref="R36:R37" si="162">+R22/N22-1</f>
+        <f t="shared" ref="R36:R37" si="184">+R22/N22-1</f>
         <v>-4.9487451396253102E-2</v>
       </c>
       <c r="S36" s="14">
-        <f t="shared" ref="S36:V37" si="163">+S22/O22-1</f>
+        <f t="shared" ref="S36:V37" si="185">+S22/O22-1</f>
         <v>5.901520637219404E-2</v>
       </c>
       <c r="T36" s="14">
-        <f t="shared" si="163"/>
+        <f t="shared" si="185"/>
         <v>5.9234731420161779E-2</v>
       </c>
       <c r="U36" s="14">
-        <f t="shared" si="163"/>
+        <f t="shared" si="185"/>
         <v>8.0223880597015018E-2</v>
       </c>
       <c r="V36" s="14">
-        <f t="shared" si="163"/>
+        <f t="shared" si="185"/>
         <v>8.107103012272221E-2</v>
       </c>
       <c r="W36" s="14">
@@ -6351,36 +6819,52 @@
         <v>4.6495726495726419E-2</v>
       </c>
       <c r="X36" s="14">
-        <f t="shared" ref="X36:Z37" si="164">+X22/T22-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="X36:Z37" si="186">+X22/T22-1</f>
+        <v>7.3636679402570238E-2</v>
       </c>
       <c r="Y36" s="14">
-        <f t="shared" si="164"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="186"/>
+        <v>5.3886010362694359E-2</v>
       </c>
       <c r="Z36" s="14">
-        <f t="shared" si="164"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AL36" s="14"/>
-      <c r="AM36" s="14"/>
-      <c r="AN36" s="14"/>
-      <c r="AO36" s="14"/>
+        <f t="shared" si="186"/>
+        <v>7.636738906088758E-2</v>
+      </c>
+      <c r="AA36" s="14">
+        <f t="shared" ref="AA36:AA37" si="187">+AA22/W22-1</f>
+        <v>0.22182293368180339</v>
+      </c>
+      <c r="AB36" s="14">
+        <f t="shared" ref="AB36:AB37" si="188">+AB22/X22-1</f>
+        <v>0</v>
+      </c>
+      <c r="AC36" s="14">
+        <f t="shared" ref="AC36:AC37" si="189">+AC22/Y22-1</f>
+        <v>0</v>
+      </c>
+      <c r="AD36" s="14">
+        <f t="shared" ref="AD36:AD37" si="190">+AD22/Z22-1</f>
+        <v>0</v>
+      </c>
       <c r="AP36" s="14"/>
       <c r="AQ36" s="14"/>
       <c r="AR36" s="14"/>
       <c r="AS36" s="14"/>
       <c r="AT36" s="14"/>
       <c r="AU36" s="14"/>
-      <c r="BH36" t="s">
+      <c r="AV36" s="14"/>
+      <c r="AW36" s="14"/>
+      <c r="AX36" s="14"/>
+      <c r="AY36" s="14"/>
+      <c r="BL36" t="s">
         <v>139</v>
       </c>
-      <c r="BI36" s="2">
-        <f>NPV(BI34,AW29:DU29)+Main!L5-Main!L6</f>
-        <v>165522.8206111856</v>
-      </c>
-    </row>
-    <row r="37" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BM36" s="2">
+        <f>NPV(BM34,BA29:DY29)+Main!L5-Main!L6</f>
+        <v>143118.54137540385</v>
+      </c>
+    </row>
+    <row r="37" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
         <v>138</v>
       </c>
@@ -6392,67 +6876,83 @@
       <c r="N37" s="14"/>
       <c r="O37" s="14"/>
       <c r="P37" s="14">
-        <f t="shared" si="160"/>
+        <f t="shared" si="182"/>
         <v>-5.9941520467836296E-2</v>
       </c>
       <c r="Q37" s="14">
-        <f t="shared" si="161"/>
+        <f t="shared" si="183"/>
         <v>-0.19948849104859334</v>
       </c>
       <c r="R37" s="14">
-        <f t="shared" si="162"/>
+        <f t="shared" si="184"/>
         <v>-4.8929663608562657E-2</v>
       </c>
       <c r="S37" s="14">
-        <f t="shared" si="163"/>
+        <f t="shared" si="185"/>
         <v>5.5732484076433053E-2</v>
       </c>
       <c r="T37" s="14">
-        <f t="shared" si="163"/>
+        <f t="shared" si="185"/>
         <v>2.1772939346811793E-2</v>
       </c>
       <c r="U37" s="14">
-        <f t="shared" si="163"/>
+        <f t="shared" si="185"/>
         <v>0.13897763578274769</v>
       </c>
       <c r="V37" s="14">
-        <f t="shared" si="163"/>
+        <f t="shared" si="185"/>
         <v>0.20418006430868174</v>
       </c>
       <c r="W37" s="14">
-        <f t="shared" ref="W37" si="165">+W23/S23-1</f>
+        <f t="shared" ref="W37" si="191">+W23/S23-1</f>
         <v>7.9939668174962231E-2</v>
       </c>
       <c r="X37" s="14">
-        <f t="shared" si="164"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="186"/>
+        <v>0.1035007610350076</v>
       </c>
       <c r="Y37" s="14">
-        <f t="shared" si="164"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="186"/>
+        <v>6.0308555399719577E-2</v>
       </c>
       <c r="Z37" s="14">
-        <f t="shared" si="164"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AL37" s="14"/>
-      <c r="AM37" s="14"/>
-      <c r="AN37" s="14"/>
-      <c r="AO37" s="14"/>
+        <f t="shared" si="186"/>
+        <v>-5.3404539385847327E-3</v>
+      </c>
+      <c r="AA37" s="14">
+        <f t="shared" si="187"/>
+        <v>7.1229050279329575E-2</v>
+      </c>
+      <c r="AB37" s="14">
+        <f t="shared" si="188"/>
+        <v>0</v>
+      </c>
+      <c r="AC37" s="14">
+        <f t="shared" si="189"/>
+        <v>0</v>
+      </c>
+      <c r="AD37" s="14">
+        <f t="shared" si="190"/>
+        <v>0</v>
+      </c>
       <c r="AP37" s="14"/>
       <c r="AQ37" s="14"/>
       <c r="AR37" s="14"/>
       <c r="AS37" s="14"/>
       <c r="AT37" s="14"/>
       <c r="AU37" s="14"/>
-      <c r="BH37" t="s">
+      <c r="AV37" s="14"/>
+      <c r="AW37" s="14"/>
+      <c r="AX37" s="14"/>
+      <c r="AY37" s="14"/>
+      <c r="BL37" t="s">
         <v>142</v>
       </c>
-      <c r="BI37" s="14">
+      <c r="BM37" s="14">
         <v>0.05</v>
       </c>
     </row>
-    <row r="38" spans="2:61" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="s">
         <v>66</v>
       </c>
@@ -6473,138 +6973,154 @@
         <v>0.58440878967561916</v>
       </c>
       <c r="K38" s="12">
-        <f t="shared" ref="K38:O38" si="166">+K21/K19</f>
+        <f t="shared" ref="K38:O38" si="192">+K21/K19</f>
         <v>0.58074821353509876</v>
       </c>
       <c r="L38" s="12">
-        <f t="shared" si="166"/>
+        <f t="shared" si="192"/>
         <v>0.56178377898196674</v>
       </c>
       <c r="M38" s="12">
-        <f t="shared" si="166"/>
+        <f t="shared" si="192"/>
         <v>0.55520322859613724</v>
       </c>
       <c r="N38" s="12">
-        <f t="shared" si="166"/>
+        <f t="shared" si="192"/>
         <v>0.55650277557494054</v>
       </c>
       <c r="O38" s="14">
-        <f t="shared" si="166"/>
+        <f t="shared" si="192"/>
         <v>0.55880541871921185</v>
       </c>
       <c r="P38" s="14">
-        <f t="shared" ref="P38:W38" si="167">+P21/P19</f>
+        <f t="shared" ref="P38:W38" si="193">+P21/P19</f>
         <v>0.55398496240601502</v>
       </c>
       <c r="Q38" s="14">
-        <f t="shared" si="167"/>
+        <f t="shared" si="193"/>
         <v>0.55074464937370549</v>
       </c>
       <c r="R38" s="14">
-        <f t="shared" si="167"/>
+        <f t="shared" si="193"/>
         <v>0.55895281820845955</v>
       </c>
       <c r="S38" s="14">
-        <f t="shared" si="167"/>
+        <f t="shared" si="193"/>
         <v>0.55671530942010072</v>
       </c>
       <c r="T38" s="14">
-        <f t="shared" si="167"/>
+        <f t="shared" si="193"/>
         <v>0.56001156849513156</v>
       </c>
       <c r="U38" s="14">
-        <f t="shared" si="167"/>
+        <f t="shared" si="193"/>
         <v>0.54122841024609414</v>
       </c>
       <c r="V38" s="14">
-        <f t="shared" si="167"/>
+        <f t="shared" si="193"/>
         <v>0.54966283943867322</v>
       </c>
       <c r="W38" s="14">
-        <f t="shared" si="167"/>
+        <f t="shared" si="193"/>
         <v>0.56864259509557835</v>
       </c>
       <c r="X38" s="14">
-        <f t="shared" ref="X38:Z38" si="168">+X21/X19</f>
+        <f t="shared" ref="X38:Z38" si="194">+X21/X19</f>
+        <v>0.56435110393107157</v>
+      </c>
+      <c r="Y38" s="14">
+        <f t="shared" si="194"/>
+        <v>0.55361069575160526</v>
+      </c>
+      <c r="Z38" s="14">
+        <f t="shared" si="194"/>
+        <v>0.57046862727986736</v>
+      </c>
+      <c r="AA38" s="14">
+        <f t="shared" ref="AA38:AD38" si="195">+AA21/AA19</f>
         <v>0.56999999999999995</v>
       </c>
-      <c r="Y38" s="14">
-        <f t="shared" si="168"/>
+      <c r="AB38" s="14">
+        <f t="shared" si="195"/>
         <v>0.56999999999999995</v>
       </c>
-      <c r="Z38" s="14">
-        <f t="shared" si="168"/>
+      <c r="AC38" s="14">
+        <f t="shared" si="195"/>
         <v>0.56999999999999995</v>
       </c>
-      <c r="AM38" s="14">
-        <f>+AM21/AM19</f>
-        <v>0.56389967870330404</v>
-      </c>
-      <c r="AN38" s="14">
-        <f>+AN21/AN19</f>
-        <v>0.54695144213216507</v>
-      </c>
-      <c r="AO38" s="14">
-        <f>+AO21/AO19</f>
-        <v>0.58447249656615863</v>
-      </c>
-      <c r="AP38" s="14">
-        <f>+AP21/AP19</f>
-        <v>0.58528711133400202</v>
+      <c r="AD38" s="14">
+        <f t="shared" si="195"/>
+        <v>0.56999999999999995</v>
       </c>
       <c r="AQ38" s="14">
         <f>+AQ21/AQ19</f>
+        <v>0.56389967870330404</v>
+      </c>
+      <c r="AR38" s="14">
+        <f>+AR21/AR19</f>
+        <v>0.54695144213216507</v>
+      </c>
+      <c r="AS38" s="14">
+        <f>+AS21/AS19</f>
+        <v>0.58447249656615863</v>
+      </c>
+      <c r="AT38" s="14">
+        <f>+AT21/AT19</f>
+        <v>0.58528711133400202</v>
+      </c>
+      <c r="AU38" s="14">
+        <f>+AU21/AU19</f>
         <v>0.56648751733703195</v>
       </c>
-      <c r="AR38" s="14">
-        <f t="shared" ref="AR38:BA38" si="169">+AR21/AR19</f>
+      <c r="AV38" s="14">
+        <f t="shared" ref="AV38:BE38" si="196">+AV21/AV19</f>
         <v>0.56965757399883921</v>
       </c>
-      <c r="AS38" s="14">
-        <f t="shared" si="169"/>
+      <c r="AW38" s="14">
+        <f t="shared" si="196"/>
         <v>0.56419243986254297</v>
       </c>
-      <c r="AT38" s="14">
-        <f t="shared" si="169"/>
+      <c r="AX38" s="14">
+        <f t="shared" si="196"/>
         <v>0.55560543708691856</v>
       </c>
-      <c r="AU38" s="14">
-        <f t="shared" si="169"/>
+      <c r="AY38" s="14">
+        <f t="shared" si="196"/>
         <v>0.55603240681134325</v>
       </c>
-      <c r="AV38" s="14">
-        <f t="shared" si="169"/>
-        <v>0.56967882854195462</v>
-      </c>
-      <c r="AW38" s="14">
-        <f t="shared" si="169"/>
+      <c r="AZ38" s="14">
+        <f t="shared" si="196"/>
+        <v>0.56418065331167655</v>
+      </c>
+      <c r="BA38" s="14">
+        <f t="shared" si="196"/>
         <v>0.56999999999999995</v>
       </c>
-      <c r="AX38" s="14">
-        <f t="shared" si="169"/>
+      <c r="BB38" s="14">
+        <f t="shared" si="196"/>
         <v>0.56999999999999995</v>
       </c>
-      <c r="AY38" s="14">
-        <f t="shared" si="169"/>
+      <c r="BC38" s="14">
+        <f t="shared" si="196"/>
         <v>0.56999999999999995</v>
       </c>
-      <c r="AZ38" s="14">
-        <f t="shared" si="169"/>
+      <c r="BD38" s="14">
+        <f t="shared" si="196"/>
         <v>0.56999999999999995</v>
       </c>
-      <c r="BA38" s="14">
-        <f t="shared" si="169"/>
+      <c r="BE38" s="14">
+        <f t="shared" si="196"/>
         <v>0.56999999999999995</v>
       </c>
-      <c r="BH38" t="s">
+      <c r="BL38" t="s">
         <v>143</v>
       </c>
-      <c r="BI38" s="1">
-        <f>BI36/Main!L3</f>
-        <v>94.746892164387859</v>
-      </c>
-    </row>
-    <row r="40" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BM38" s="1">
+        <f>BM36/Main!L3</f>
+        <v>82.166448575390106</v>
+      </c>
+    </row>
+    <row r="40" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>65</v>
       </c>
@@ -6618,42 +7134,46 @@
       </c>
       <c r="X40" s="2">
         <f>+W40+X29</f>
-        <v>-3240.3796900000007</v>
+        <v>-3440</v>
       </c>
       <c r="Y40" s="2">
         <f>+X40+Y29</f>
-        <v>-922.97207500000059</v>
+        <v>-1533</v>
       </c>
       <c r="Z40" s="2">
         <f>+Y40+Z29</f>
-        <v>1535.9217799999988</v>
-      </c>
-      <c r="AV40" s="2">
+        <v>379</v>
+      </c>
+      <c r="AA40" s="2"/>
+      <c r="AB40" s="2"/>
+      <c r="AC40" s="2"/>
+      <c r="AD40" s="2"/>
+      <c r="AZ40" s="2">
         <f>+Z40</f>
-        <v>1535.9217799999988</v>
-      </c>
-      <c r="AW40" s="2">
-        <f>+AV40+AW29</f>
-        <v>10819.117292249994</v>
-      </c>
-      <c r="AX40" s="2">
-        <f>+AW40+AX29</f>
-        <v>21126.783982772613</v>
-      </c>
-      <c r="AY40" s="2">
-        <f>+AX40+AY29</f>
-        <v>32522.459887948142</v>
-      </c>
-      <c r="AZ40" s="2">
-        <f>+AY40+AZ29</f>
-        <v>44818.609522346873</v>
+        <v>379</v>
       </c>
       <c r="BA40" s="2">
         <f>+AZ40+BA29</f>
-        <v>58071.048938342174</v>
-      </c>
-    </row>
-    <row r="41" spans="2:61" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <v>9473.2392500000024</v>
+      </c>
+      <c r="BB40" s="2">
+        <f>+BA40+BB29</f>
+        <v>19586.811124624997</v>
+      </c>
+      <c r="BC40" s="2">
+        <f>+BB40+BC29</f>
+        <v>30782.980478411555</v>
+      </c>
+      <c r="BD40" s="2">
+        <f>+BC40+BD29</f>
+        <v>42869.05225138375</v>
+      </c>
+      <c r="BE40" s="2">
+        <f>+BD40+BE29</f>
+        <v>55900.426919267455</v>
+      </c>
+    </row>
+    <row r="41" spans="2:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
         <v>3</v>
       </c>
@@ -6677,7 +7197,7 @@
         <v>7751</v>
       </c>
     </row>
-    <row r="42" spans="2:61" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
         <v>57</v>
       </c>
@@ -6699,7 +7219,7 @@
         <v>7327</v>
       </c>
     </row>
-    <row r="43" spans="2:61" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
         <v>58</v>
       </c>
@@ -6721,7 +7241,7 @@
         <v>6639</v>
       </c>
     </row>
-    <row r="44" spans="2:61" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
         <v>59</v>
       </c>
@@ -6743,7 +7263,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="45" spans="2:61" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="2" t="s">
         <v>61</v>
       </c>
@@ -6765,7 +7285,7 @@
         <v>10932</v>
       </c>
     </row>
-    <row r="46" spans="2:61" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="2" t="s">
         <v>60</v>
       </c>
@@ -6789,7 +7309,7 @@
         <v>29620</v>
       </c>
     </row>
-    <row r="47" spans="2:61" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
         <v>62</v>
       </c>
@@ -6811,7 +7331,7 @@
         <v>16836</v>
       </c>
     </row>
-    <row r="48" spans="2:61" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
         <v>63</v>
       </c>
@@ -6835,7 +7355,7 @@
         <v>81448</v>
       </c>
     </row>
-    <row r="49" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
@@ -6849,7 +7369,7 @@
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
     </row>
-    <row r="50" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B50" s="2" t="s">
         <v>51</v>
       </c>
@@ -6871,7 +7391,7 @@
         <v>4214</v>
       </c>
     </row>
-    <row r="51" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B51" s="2" t="s">
         <v>52</v>
       </c>
@@ -6893,7 +7413,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="52" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B52" s="2" t="s">
         <v>53</v>
       </c>
@@ -6915,7 +7435,7 @@
         <v>5600</v>
       </c>
     </row>
-    <row r="53" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B53" s="2" t="s">
         <v>54</v>
       </c>
@@ -6938,7 +7458,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="54" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B54" s="2" t="s">
         <v>43</v>
       </c>
@@ -6960,7 +7480,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="55" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B55" s="2" t="s">
         <v>4</v>
       </c>
@@ -6984,7 +7504,7 @@
         <v>13242</v>
       </c>
     </row>
-    <row r="56" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B56" s="2" t="s">
         <v>55</v>
       </c>
@@ -7006,7 +7526,7 @@
         <v>6644</v>
       </c>
     </row>
-    <row r="57" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B57" s="2" t="s">
         <v>56</v>
       </c>
@@ -7030,7 +7550,7 @@
         <v>49064</v>
       </c>
     </row>
-    <row r="58" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
         <v>64</v>
       </c>
@@ -7054,7 +7574,7 @@
         <v>81448</v>
       </c>
     </row>
-    <row r="60" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B60" s="2" t="s">
         <v>130</v>
       </c>
@@ -7075,7 +7595,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="61" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B61" s="2" t="s">
         <v>131</v>
       </c>
@@ -7095,7 +7615,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="62" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B62" s="2" t="s">
         <v>132</v>
       </c>
@@ -7115,7 +7635,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="63" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B63" s="2" t="s">
         <v>133</v>
       </c>
@@ -7135,7 +7655,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="64" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B64" s="2" t="s">
         <v>134</v>
       </c>
@@ -7155,7 +7675,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="65" spans="2:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B65" s="2" t="s">
         <v>57</v>
       </c>
@@ -7175,7 +7695,7 @@
         <v>-262</v>
       </c>
     </row>
-    <row r="66" spans="2:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B66" s="2" t="s">
         <v>58</v>
       </c>
@@ -7195,7 +7715,7 @@
         <v>-255</v>
       </c>
     </row>
-    <row r="67" spans="2:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B67" s="2" t="s">
         <v>34</v>
       </c>
@@ -7214,17 +7734,17 @@
       <c r="W67" s="2">
         <v>-436</v>
       </c>
-      <c r="AR67" s="2">
+      <c r="AV67" s="2">
         <v>10533</v>
       </c>
-      <c r="AS67" s="2">
+      <c r="AW67" s="2">
         <v>9581</v>
       </c>
-      <c r="AT67" s="2">
+      <c r="AX67" s="2">
         <v>7261</v>
       </c>
     </row>
-    <row r="68" spans="2:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B68" s="2" t="s">
         <v>129</v>
       </c>
@@ -7244,17 +7764,17 @@
         <f>SUM(W61:W67)</f>
         <v>1417</v>
       </c>
-      <c r="AR68" s="2">
+      <c r="AV68" s="2">
         <v>1885</v>
       </c>
-      <c r="AS68" s="2">
+      <c r="AW68" s="2">
         <v>1777</v>
       </c>
-      <c r="AT68" s="2">
+      <c r="AX68" s="2">
         <v>2202</v>
       </c>
     </row>
-    <row r="69" spans="2:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
@@ -7267,20 +7787,20 @@
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
       <c r="N69" s="4"/>
-      <c r="AR69" s="2">
-        <f>+AR67-AR68</f>
+      <c r="AV69" s="2">
+        <f>+AV67-AV68</f>
         <v>8648</v>
       </c>
-      <c r="AS69" s="2">
-        <f>+AS67-AS68</f>
+      <c r="AW69" s="2">
+        <f>+AW67-AW68</f>
         <v>7804</v>
       </c>
-      <c r="AT69" s="2">
-        <f>+AT67-AT68</f>
+      <c r="AX69" s="2">
+        <f>+AX67-AX68</f>
         <v>5059</v>
       </c>
     </row>
-    <row r="70" spans="2:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B70" s="2" t="s">
         <v>127</v>
       </c>
@@ -7300,7 +7820,7 @@
         <v>-484</v>
       </c>
     </row>
-    <row r="71" spans="2:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B71" s="2" t="s">
         <v>128</v>
       </c>
@@ -7320,7 +7840,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="2:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B72" s="2" t="s">
         <v>34</v>
       </c>
@@ -7340,7 +7860,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="2:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B73" s="2" t="s">
         <v>126</v>
       </c>
@@ -7361,7 +7881,7 @@
         <v>-470</v>
       </c>
     </row>
-    <row r="74" spans="2:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
@@ -7375,7 +7895,7 @@
       <c r="M74" s="4"/>
       <c r="N74" s="4"/>
     </row>
-    <row r="75" spans="2:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B75" s="2" t="s">
         <v>4</v>
       </c>
@@ -7396,7 +7916,7 @@
         <v>-1036</v>
       </c>
     </row>
-    <row r="76" spans="2:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B76" s="2" t="s">
         <v>125</v>
       </c>
@@ -7416,7 +7936,7 @@
         <v>-280</v>
       </c>
     </row>
-    <row r="77" spans="2:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B77" s="2" t="s">
         <v>124</v>
       </c>
@@ -7436,7 +7956,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="78" spans="2:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B78" s="2" t="s">
         <v>54</v>
       </c>
@@ -7456,7 +7976,7 @@
         <v>-1026</v>
       </c>
     </row>
-    <row r="79" spans="2:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B79" s="2" t="s">
         <v>123</v>
       </c>
@@ -7477,7 +7997,7 @@
         <v>-2055</v>
       </c>
     </row>
-    <row r="80" spans="2:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B80" s="2" t="s">
         <v>122</v>
       </c>
@@ -7497,7 +8017,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="81" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B81" s="2" t="s">
         <v>121</v>
       </c>
